--- a/docs/perechen-otchetov/obrazcy/ФО-01.xlsx
+++ b/docs/perechen-otchetov/obrazcy/ФО-01.xlsx
@@ -7,10 +7,13 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Образец" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Описание" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ФО-01" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Параметры" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Описание" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm.Print_Titles" localSheetId="0">'ФО-01'!$5:$7</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -18,7 +21,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="7">
+  <fonts count="13">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -27,14 +30,46 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="Arial"/>
+      <color rgb="00808080"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Arial"/>
       <b val="1"/>
       <sz val="12"/>
     </font>
     <font>
+      <name val="Arial"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Arial"/>
       <b val="1"/>
       <sz val="9"/>
     </font>
     <font>
+      <name val="Arial"/>
       <sz val="9"/>
     </font>
     <font>
@@ -50,12 +85,47 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="10">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C0C0C0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0044546A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="009BC2E6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00DDEBF7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00A9D08E"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E2EFDA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FCE4D6"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -89,50 +159,154 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="53">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="3" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="4" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="3" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="4" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="3" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="4" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="3" fontId="6" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="4" fontId="6" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="3"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="3" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="4" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="4"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="3" fontId="6" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="4" fontId="6" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="5"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="4" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="4" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="4" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1" indent="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -498,692 +672,1364 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J23"/>
+  <dimension ref="A1:L40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="38" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="40" customWidth="1" min="1" max="1"/>
+    <col width="7" customWidth="1" min="2" max="2"/>
+    <col width="7" customWidth="1" min="3" max="3"/>
+    <col width="7" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="8" customWidth="1" min="11" max="11"/>
+    <col width="28" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>ОАО «Государственный финансовый холдинг»</t>
+        </is>
+      </c>
+      <c r="L1" s="2" t="inlineStr">
+        <is>
+          <t>ФО-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
           <t>Просроченная задолженность</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="1" t="inlineStr">
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t>по состоянию на 01.10.2026, сом</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="2" t="inlineStr">
+    <row r="5" ht="14" customHeight="1">
+      <c r="A5" s="5" t="inlineStr">
         <is>
           <t>Наименование</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>Категория риска</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>Группа</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>Валюта</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
         <is>
           <t>Кредитов с просрочкой</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>Валюта</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>Группа платёжеспособности</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="F5" s="5" t="inlineStr">
         <is>
           <t>Остаток основного долга</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="G5" s="5" t="inlineStr">
         <is>
           <t>Просроченная задолженность</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="H5" s="5" t="inlineStr">
         <is>
           <t>в том числе</t>
         </is>
       </c>
-      <c r="H4" s="2" t="n"/>
-      <c r="I4" s="2" t="n"/>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="I5" s="5" t="n"/>
+      <c r="J5" s="5" t="n"/>
+      <c r="K5" s="5" t="inlineStr">
         <is>
           <t>Дни просрочки</t>
         </is>
       </c>
-    </row>
-    <row r="5" ht="32" customHeight="1">
-      <c r="A5" s="2" t="n"/>
-      <c r="B5" s="2" t="n"/>
-      <c r="C5" s="2" t="n"/>
-      <c r="D5" s="2" t="n"/>
-      <c r="E5" s="2" t="n"/>
-      <c r="F5" s="2" t="n"/>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="5" t="inlineStr">
+        <is>
+          <t>Стадия взыскания</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="27" customHeight="1">
+      <c r="A6" s="5" t="n"/>
+      <c r="B6" s="5" t="n"/>
+      <c r="C6" s="5" t="n"/>
+      <c r="D6" s="5" t="n"/>
+      <c r="E6" s="5" t="n"/>
+      <c r="F6" s="5" t="n"/>
+      <c r="G6" s="5" t="n"/>
+      <c r="H6" s="5" t="inlineStr">
         <is>
           <t>основная сумма</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="I6" s="5" t="inlineStr">
         <is>
           <t>проценты</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="J6" s="5" t="inlineStr">
         <is>
           <t>штрафы</t>
         </is>
       </c>
-      <c r="J5" s="2" t="n"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="3" t="inlineStr">
+      <c r="K6" s="5" t="n"/>
+      <c r="L6" s="5" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="G7" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="H7" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="I7" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="J7" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="K7" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="L7" s="5" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="8" ht="14" customHeight="1">
+      <c r="A8" s="6" t="inlineStr">
         <is>
           <t>ИТОГО</t>
         </is>
       </c>
-      <c r="B6" s="4" t="n">
+      <c r="B8" s="7" t="n"/>
+      <c r="C8" s="7" t="n"/>
+      <c r="D8" s="7" t="n"/>
+      <c r="E8" s="8" t="n">
         <v>7</v>
       </c>
-      <c r="C6" s="5" t="inlineStr"/>
-      <c r="D6" s="5" t="inlineStr"/>
-      <c r="E6" s="6" t="n">
+      <c r="F8" s="9" t="n">
         <v>13170000</v>
       </c>
-      <c r="F6" s="6" t="n">
+      <c r="G8" s="9" t="n">
         <v>4560750</v>
       </c>
-      <c r="G6" s="6" t="n">
+      <c r="H8" s="9" t="n">
         <v>3180000</v>
       </c>
-      <c r="H6" s="6" t="n">
+      <c r="I8" s="9" t="n">
         <v>1085000</v>
       </c>
-      <c r="I6" s="6" t="n">
+      <c r="J8" s="9" t="n">
         <v>295750</v>
       </c>
-      <c r="J6" s="5" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="K8" s="10" t="n"/>
+      <c r="L8" s="6" t="n"/>
+    </row>
+    <row r="9" ht="13" customHeight="1">
+      <c r="A9" s="11" t="inlineStr">
         <is>
           <t>Департамент администрирования кредитов</t>
         </is>
       </c>
-      <c r="B7" s="4" t="n">
+      <c r="B9" s="12" t="n"/>
+      <c r="C9" s="12" t="n"/>
+      <c r="D9" s="12" t="n"/>
+      <c r="E9" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="C7" s="5" t="inlineStr"/>
-      <c r="D7" s="5" t="inlineStr"/>
-      <c r="E7" s="6" t="n">
+      <c r="F9" s="14" t="n">
         <v>2550000</v>
       </c>
-      <c r="F7" s="6" t="n">
+      <c r="G9" s="14" t="n">
         <v>330250</v>
       </c>
-      <c r="G7" s="6" t="n">
+      <c r="H9" s="14" t="n">
         <v>240000</v>
       </c>
-      <c r="H7" s="6" t="n">
+      <c r="I9" s="14" t="n">
         <v>69500</v>
       </c>
-      <c r="I7" s="6" t="n">
+      <c r="J9" s="14" t="n">
         <v>20750</v>
       </c>
-      <c r="J7" s="5" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="7" t="inlineStr">
+      <c r="K9" s="15" t="n"/>
+      <c r="L9" s="11" t="n"/>
+    </row>
+    <row r="10" ht="24" customHeight="1">
+      <c r="A10" s="16" t="inlineStr">
+        <is>
+          <t>Отдел администрирования кредитов корпоративного сектора</t>
+        </is>
+      </c>
+      <c r="B10" s="17" t="n"/>
+      <c r="C10" s="17" t="n"/>
+      <c r="D10" s="17" t="n"/>
+      <c r="E10" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="F10" s="19" t="n">
+        <v>2550000</v>
+      </c>
+      <c r="G10" s="19" t="n">
+        <v>330250</v>
+      </c>
+      <c r="H10" s="19" t="n">
+        <v>240000</v>
+      </c>
+      <c r="I10" s="19" t="n">
+        <v>69500</v>
+      </c>
+      <c r="J10" s="19" t="n">
+        <v>20750</v>
+      </c>
+      <c r="K10" s="20" t="n"/>
+      <c r="L10" s="21" t="n"/>
+    </row>
+    <row r="11" ht="13" customHeight="1">
+      <c r="A11" s="22" t="inlineStr">
+        <is>
+          <t>Чуйская обл.</t>
+        </is>
+      </c>
+      <c r="B11" s="23" t="n"/>
+      <c r="C11" s="23" t="n"/>
+      <c r="D11" s="23" t="n"/>
+      <c r="E11" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="F11" s="25" t="n">
+        <v>650000</v>
+      </c>
+      <c r="G11" s="25" t="n">
+        <v>149400</v>
+      </c>
+      <c r="H11" s="25" t="n">
+        <v>90000</v>
+      </c>
+      <c r="I11" s="25" t="n">
+        <v>41000</v>
+      </c>
+      <c r="J11" s="25" t="n">
+        <v>18400</v>
+      </c>
+      <c r="K11" s="26" t="n"/>
+      <c r="L11" s="27" t="n"/>
+    </row>
+    <row r="12" ht="13" customHeight="1">
+      <c r="A12" s="28" t="inlineStr">
+        <is>
+          <t>Жайылский р-н</t>
+        </is>
+      </c>
+      <c r="B12" s="29" t="n"/>
+      <c r="C12" s="29" t="n"/>
+      <c r="D12" s="29" t="n"/>
+      <c r="E12" s="30" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" s="31" t="n">
+        <v>650000</v>
+      </c>
+      <c r="G12" s="31" t="n">
+        <v>149400</v>
+      </c>
+      <c r="H12" s="31" t="n">
+        <v>90000</v>
+      </c>
+      <c r="I12" s="31" t="n">
+        <v>41000</v>
+      </c>
+      <c r="J12" s="31" t="n">
+        <v>18400</v>
+      </c>
+      <c r="K12" s="32" t="n"/>
+      <c r="L12" s="33" t="n"/>
+    </row>
+    <row r="13" ht="13" customHeight="1">
+      <c r="A13" s="34" t="inlineStr">
         <is>
           <t>КФХ «Жайыл»</t>
         </is>
       </c>
-      <c r="B8" s="8" t="n">
+      <c r="B13" s="35" t="inlineStr">
+        <is>
+          <t>средний</t>
+        </is>
+      </c>
+      <c r="C13" s="35" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
+      <c r="D13" s="35" t="n"/>
+      <c r="E13" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="C8" s="9" t="inlineStr"/>
-      <c r="D8" s="9" t="inlineStr"/>
-      <c r="E8" s="10" t="n">
+      <c r="F13" s="37" t="n">
         <v>650000</v>
       </c>
-      <c r="F8" s="10" t="n">
+      <c r="G13" s="37" t="n">
         <v>149400</v>
       </c>
-      <c r="G8" s="10" t="n">
+      <c r="H13" s="37" t="n">
         <v>90000</v>
       </c>
-      <c r="H8" s="10" t="n">
+      <c r="I13" s="37" t="n">
         <v>41000</v>
       </c>
-      <c r="I8" s="10" t="n">
+      <c r="J13" s="37" t="n">
         <v>18400</v>
       </c>
-      <c r="J8" s="8" t="n">
+      <c r="K13" s="36" t="n">
         <v>75</v>
       </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="11" t="inlineStr">
+      <c r="L13" s="38" t="n"/>
+    </row>
+    <row r="14" ht="13" customHeight="1">
+      <c r="A14" s="39" t="inlineStr">
         <is>
           <t>№ 23-4/008 от 20.06.2023</t>
         </is>
       </c>
-      <c r="B9" s="9" t="inlineStr"/>
-      <c r="C9" s="9" t="inlineStr">
+      <c r="B14" s="40" t="inlineStr">
+        <is>
+          <t>средний</t>
+        </is>
+      </c>
+      <c r="C14" s="40" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
+      <c r="D14" s="40" t="inlineStr">
         <is>
           <t>KGS</t>
         </is>
       </c>
-      <c r="D9" s="9" t="inlineStr">
+      <c r="E14" s="41" t="n"/>
+      <c r="F14" s="42" t="n">
+        <v>650000</v>
+      </c>
+      <c r="G14" s="42" t="n">
+        <v>149400</v>
+      </c>
+      <c r="H14" s="42" t="n">
+        <v>90000</v>
+      </c>
+      <c r="I14" s="42" t="n">
+        <v>41000</v>
+      </c>
+      <c r="J14" s="42" t="n">
+        <v>18400</v>
+      </c>
+      <c r="K14" s="43" t="n">
+        <v>75</v>
+      </c>
+      <c r="L14" s="44" t="inlineStr">
+        <is>
+          <t>Повторная претензия, 15.09.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="13" customHeight="1">
+      <c r="A15" s="22" t="inlineStr">
+        <is>
+          <t>г. Бишкек</t>
+        </is>
+      </c>
+      <c r="B15" s="23" t="n"/>
+      <c r="C15" s="23" t="n"/>
+      <c r="D15" s="23" t="n"/>
+      <c r="E15" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="F15" s="25" t="n">
+        <v>1900000</v>
+      </c>
+      <c r="G15" s="25" t="n">
+        <v>180850</v>
+      </c>
+      <c r="H15" s="25" t="n">
+        <v>150000</v>
+      </c>
+      <c r="I15" s="25" t="n">
+        <v>28500</v>
+      </c>
+      <c r="J15" s="25" t="n">
+        <v>2350</v>
+      </c>
+      <c r="K15" s="26" t="n"/>
+      <c r="L15" s="27" t="n"/>
+    </row>
+    <row r="16" ht="13" customHeight="1">
+      <c r="A16" s="28" t="inlineStr">
+        <is>
+          <t>г. Бишкек</t>
+        </is>
+      </c>
+      <c r="B16" s="29" t="n"/>
+      <c r="C16" s="29" t="n"/>
+      <c r="D16" s="29" t="n"/>
+      <c r="E16" s="30" t="n">
+        <v>1</v>
+      </c>
+      <c r="F16" s="31" t="n">
+        <v>1900000</v>
+      </c>
+      <c r="G16" s="31" t="n">
+        <v>180850</v>
+      </c>
+      <c r="H16" s="31" t="n">
+        <v>150000</v>
+      </c>
+      <c r="I16" s="31" t="n">
+        <v>28500</v>
+      </c>
+      <c r="J16" s="31" t="n">
+        <v>2350</v>
+      </c>
+      <c r="K16" s="32" t="n"/>
+      <c r="L16" s="33" t="n"/>
+    </row>
+    <row r="17" ht="13" customHeight="1">
+      <c r="A17" s="34" t="inlineStr">
+        <is>
+          <t>ОсОО «Тянь-Шань Строй»</t>
+        </is>
+      </c>
+      <c r="B17" s="35" t="inlineStr">
+        <is>
+          <t>средний</t>
+        </is>
+      </c>
+      <c r="C17" s="35" t="inlineStr">
         <is>
           <t>1.2</t>
         </is>
       </c>
-      <c r="E9" s="10" t="n">
-        <v>650000</v>
-      </c>
-      <c r="F9" s="10" t="n">
-        <v>149400</v>
-      </c>
-      <c r="G9" s="10" t="n">
-        <v>90000</v>
-      </c>
-      <c r="H9" s="10" t="n">
-        <v>41000</v>
-      </c>
-      <c r="I9" s="10" t="n">
-        <v>18400</v>
-      </c>
-      <c r="J9" s="8" t="n">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="7" t="inlineStr">
-        <is>
-          <t>ОсОО «Тянь-Шань Строй»</t>
-        </is>
-      </c>
-      <c r="B10" s="8" t="n">
+      <c r="D17" s="35" t="n"/>
+      <c r="E17" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="C10" s="9" t="inlineStr"/>
-      <c r="D10" s="9" t="inlineStr"/>
-      <c r="E10" s="10" t="n">
+      <c r="F17" s="37" t="n">
         <v>1900000</v>
       </c>
-      <c r="F10" s="10" t="n">
+      <c r="G17" s="37" t="n">
         <v>180850</v>
       </c>
-      <c r="G10" s="10" t="n">
+      <c r="H17" s="37" t="n">
         <v>150000</v>
       </c>
-      <c r="H10" s="10" t="n">
+      <c r="I17" s="37" t="n">
         <v>28500</v>
       </c>
-      <c r="I10" s="10" t="n">
+      <c r="J17" s="37" t="n">
         <v>2350</v>
       </c>
-      <c r="J10" s="8" t="n">
+      <c r="K17" s="36" t="n">
         <v>20</v>
       </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="11" t="inlineStr">
+      <c r="L17" s="38" t="n"/>
+    </row>
+    <row r="18" ht="13" customHeight="1">
+      <c r="A18" s="39" t="inlineStr">
         <is>
           <t>№ 22-1/045 от 03.02.2022</t>
         </is>
       </c>
-      <c r="B11" s="9" t="inlineStr"/>
-      <c r="C11" s="9" t="inlineStr">
+      <c r="B18" s="40" t="inlineStr">
+        <is>
+          <t>средний</t>
+        </is>
+      </c>
+      <c r="C18" s="40" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
+      <c r="D18" s="40" t="inlineStr">
         <is>
           <t>KGS</t>
         </is>
       </c>
-      <c r="D11" s="9" t="inlineStr">
+      <c r="E18" s="41" t="n"/>
+      <c r="F18" s="42" t="n">
+        <v>1900000</v>
+      </c>
+      <c r="G18" s="42" t="n">
+        <v>180850</v>
+      </c>
+      <c r="H18" s="42" t="n">
+        <v>150000</v>
+      </c>
+      <c r="I18" s="42" t="n">
+        <v>28500</v>
+      </c>
+      <c r="J18" s="42" t="n">
+        <v>2350</v>
+      </c>
+      <c r="K18" s="43" t="n">
+        <v>20</v>
+      </c>
+      <c r="L18" s="44" t="inlineStr">
+        <is>
+          <t>Первичная претензия, 25.09.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="13" customHeight="1">
+      <c r="A19" s="11" t="inlineStr">
+        <is>
+          <t>Департамент регионального развития</t>
+        </is>
+      </c>
+      <c r="B19" s="12" t="n"/>
+      <c r="C19" s="12" t="n"/>
+      <c r="D19" s="12" t="n"/>
+      <c r="E19" s="13" t="n">
+        <v>5</v>
+      </c>
+      <c r="F19" s="14" t="n">
+        <v>10620000</v>
+      </c>
+      <c r="G19" s="14" t="n">
+        <v>4230500</v>
+      </c>
+      <c r="H19" s="14" t="n">
+        <v>2940000</v>
+      </c>
+      <c r="I19" s="14" t="n">
+        <v>1015500</v>
+      </c>
+      <c r="J19" s="14" t="n">
+        <v>275000</v>
+      </c>
+      <c r="K19" s="15" t="n"/>
+      <c r="L19" s="11" t="n"/>
+    </row>
+    <row r="20" ht="13" customHeight="1">
+      <c r="A20" s="16" t="inlineStr">
+        <is>
+          <t>Отдел развития регионов</t>
+        </is>
+      </c>
+      <c r="B20" s="17" t="n"/>
+      <c r="C20" s="17" t="n"/>
+      <c r="D20" s="17" t="n"/>
+      <c r="E20" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="F20" s="19" t="n">
+        <v>5800000</v>
+      </c>
+      <c r="G20" s="19" t="n">
+        <v>2281500</v>
+      </c>
+      <c r="H20" s="19" t="n">
+        <v>1600000</v>
+      </c>
+      <c r="I20" s="19" t="n">
+        <v>530000</v>
+      </c>
+      <c r="J20" s="19" t="n">
+        <v>151500</v>
+      </c>
+      <c r="K20" s="20" t="n"/>
+      <c r="L20" s="21" t="n"/>
+    </row>
+    <row r="21" ht="13" customHeight="1">
+      <c r="A21" s="22" t="inlineStr">
+        <is>
+          <t>Нарынская обл.</t>
+        </is>
+      </c>
+      <c r="B21" s="23" t="n"/>
+      <c r="C21" s="23" t="n"/>
+      <c r="D21" s="23" t="n"/>
+      <c r="E21" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="F21" s="25" t="n">
+        <v>2200000</v>
+      </c>
+      <c r="G21" s="25" t="n">
+        <v>551000</v>
+      </c>
+      <c r="H21" s="25" t="n">
+        <v>400000</v>
+      </c>
+      <c r="I21" s="25" t="n">
+        <v>120000</v>
+      </c>
+      <c r="J21" s="25" t="n">
+        <v>31000</v>
+      </c>
+      <c r="K21" s="26" t="n"/>
+      <c r="L21" s="27" t="n"/>
+    </row>
+    <row r="22" ht="13" customHeight="1">
+      <c r="A22" s="28" t="inlineStr">
+        <is>
+          <t>г. Нарын</t>
+        </is>
+      </c>
+      <c r="B22" s="29" t="n"/>
+      <c r="C22" s="29" t="n"/>
+      <c r="D22" s="29" t="n"/>
+      <c r="E22" s="30" t="n">
+        <v>1</v>
+      </c>
+      <c r="F22" s="31" t="n">
+        <v>2200000</v>
+      </c>
+      <c r="G22" s="31" t="n">
+        <v>551000</v>
+      </c>
+      <c r="H22" s="31" t="n">
+        <v>400000</v>
+      </c>
+      <c r="I22" s="31" t="n">
+        <v>120000</v>
+      </c>
+      <c r="J22" s="31" t="n">
+        <v>31000</v>
+      </c>
+      <c r="K22" s="32" t="n"/>
+      <c r="L22" s="33" t="n"/>
+    </row>
+    <row r="23" ht="13" customHeight="1">
+      <c r="A23" s="34" t="inlineStr">
+        <is>
+          <t>ОсОО «Нарын-Сүт»</t>
+        </is>
+      </c>
+      <c r="B23" s="35" t="inlineStr">
+        <is>
+          <t>высокий</t>
+        </is>
+      </c>
+      <c r="C23" s="35" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
+      </c>
+      <c r="D23" s="35" t="n"/>
+      <c r="E23" s="36" t="n">
+        <v>1</v>
+      </c>
+      <c r="F23" s="37" t="n">
+        <v>2200000</v>
+      </c>
+      <c r="G23" s="37" t="n">
+        <v>551000</v>
+      </c>
+      <c r="H23" s="37" t="n">
+        <v>400000</v>
+      </c>
+      <c r="I23" s="37" t="n">
+        <v>120000</v>
+      </c>
+      <c r="J23" s="37" t="n">
+        <v>31000</v>
+      </c>
+      <c r="K23" s="36" t="n">
+        <v>190</v>
+      </c>
+      <c r="L23" s="38" t="n"/>
+    </row>
+    <row r="24" ht="13" customHeight="1">
+      <c r="A24" s="39" t="inlineStr">
+        <is>
+          <t>№ 23-5/071 от 09.08.2023</t>
+        </is>
+      </c>
+      <c r="B24" s="40" t="inlineStr">
+        <is>
+          <t>высокий</t>
+        </is>
+      </c>
+      <c r="C24" s="40" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
+      </c>
+      <c r="D24" s="40" t="inlineStr">
+        <is>
+          <t>KGS</t>
+        </is>
+      </c>
+      <c r="E24" s="41" t="n"/>
+      <c r="F24" s="42" t="n">
+        <v>2200000</v>
+      </c>
+      <c r="G24" s="42" t="n">
+        <v>551000</v>
+      </c>
+      <c r="H24" s="42" t="n">
+        <v>400000</v>
+      </c>
+      <c r="I24" s="42" t="n">
+        <v>120000</v>
+      </c>
+      <c r="J24" s="42" t="n">
+        <v>31000</v>
+      </c>
+      <c r="K24" s="43" t="n">
+        <v>190</v>
+      </c>
+      <c r="L24" s="44" t="inlineStr">
+        <is>
+          <t>мер нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="13" customHeight="1">
+      <c r="A25" s="22" t="inlineStr">
+        <is>
+          <t>Ошская обл.</t>
+        </is>
+      </c>
+      <c r="B25" s="23" t="n"/>
+      <c r="C25" s="23" t="n"/>
+      <c r="D25" s="23" t="n"/>
+      <c r="E25" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="F25" s="25" t="n">
+        <v>3600000</v>
+      </c>
+      <c r="G25" s="25" t="n">
+        <v>1730500</v>
+      </c>
+      <c r="H25" s="25" t="n">
+        <v>1200000</v>
+      </c>
+      <c r="I25" s="25" t="n">
+        <v>410000</v>
+      </c>
+      <c r="J25" s="25" t="n">
+        <v>120500</v>
+      </c>
+      <c r="K25" s="26" t="n"/>
+      <c r="L25" s="27" t="n"/>
+    </row>
+    <row r="26" ht="13" customHeight="1">
+      <c r="A26" s="28" t="inlineStr">
+        <is>
+          <t>Кара-Суйский р-н</t>
+        </is>
+      </c>
+      <c r="B26" s="29" t="n"/>
+      <c r="C26" s="29" t="n"/>
+      <c r="D26" s="29" t="n"/>
+      <c r="E26" s="30" t="n">
+        <v>1</v>
+      </c>
+      <c r="F26" s="31" t="n">
+        <v>3600000</v>
+      </c>
+      <c r="G26" s="31" t="n">
+        <v>1730500</v>
+      </c>
+      <c r="H26" s="31" t="n">
+        <v>1200000</v>
+      </c>
+      <c r="I26" s="31" t="n">
+        <v>410000</v>
+      </c>
+      <c r="J26" s="31" t="n">
+        <v>120500</v>
+      </c>
+      <c r="K26" s="32" t="n"/>
+      <c r="L26" s="33" t="n"/>
+    </row>
+    <row r="27" ht="13" customHeight="1">
+      <c r="A27" s="34" t="inlineStr">
+        <is>
+          <t>ОсОО «Ош-Текстиль»</t>
+        </is>
+      </c>
+      <c r="B27" s="35" t="inlineStr">
+        <is>
+          <t>высокий</t>
+        </is>
+      </c>
+      <c r="C27" s="35" t="inlineStr">
         <is>
           <t>1.2</t>
         </is>
       </c>
-      <c r="E11" s="10" t="n">
-        <v>1900000</v>
-      </c>
-      <c r="F11" s="10" t="n">
-        <v>180850</v>
-      </c>
-      <c r="G11" s="10" t="n">
-        <v>150000</v>
-      </c>
-      <c r="H11" s="10" t="n">
-        <v>28500</v>
-      </c>
-      <c r="I11" s="10" t="n">
-        <v>2350</v>
-      </c>
-      <c r="J11" s="8" t="n">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="3" t="inlineStr">
-        <is>
-          <t>Отраслевой департамент промышленности</t>
-        </is>
-      </c>
-      <c r="B12" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="C12" s="5" t="inlineStr"/>
-      <c r="D12" s="5" t="inlineStr"/>
-      <c r="E12" s="6" t="n">
-        <v>7020000</v>
-      </c>
-      <c r="F12" s="6" t="n">
-        <v>2500000</v>
-      </c>
-      <c r="G12" s="6" t="n">
-        <v>1740000</v>
-      </c>
-      <c r="H12" s="6" t="n">
-        <v>605500</v>
-      </c>
-      <c r="I12" s="6" t="n">
-        <v>154500</v>
-      </c>
-      <c r="J12" s="5" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="7" t="inlineStr">
+      <c r="D27" s="35" t="n"/>
+      <c r="E27" s="36" t="n">
+        <v>1</v>
+      </c>
+      <c r="F27" s="37" t="n">
+        <v>3600000</v>
+      </c>
+      <c r="G27" s="37" t="n">
+        <v>1730500</v>
+      </c>
+      <c r="H27" s="37" t="n">
+        <v>1200000</v>
+      </c>
+      <c r="I27" s="37" t="n">
+        <v>410000</v>
+      </c>
+      <c r="J27" s="37" t="n">
+        <v>120500</v>
+      </c>
+      <c r="K27" s="36" t="n">
+        <v>212</v>
+      </c>
+      <c r="L27" s="38" t="n"/>
+    </row>
+    <row r="28" ht="24" customHeight="1">
+      <c r="A28" s="39" t="inlineStr">
+        <is>
+          <t>№ 21-5/203 от 09.09.2021</t>
+        </is>
+      </c>
+      <c r="B28" s="40" t="inlineStr">
+        <is>
+          <t>высокий</t>
+        </is>
+      </c>
+      <c r="C28" s="40" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
+      <c r="D28" s="40" t="inlineStr">
+        <is>
+          <t>KGS</t>
+        </is>
+      </c>
+      <c r="E28" s="41" t="n"/>
+      <c r="F28" s="42" t="n">
+        <v>3600000</v>
+      </c>
+      <c r="G28" s="42" t="n">
+        <v>1730500</v>
+      </c>
+      <c r="H28" s="42" t="n">
+        <v>1200000</v>
+      </c>
+      <c r="I28" s="42" t="n">
+        <v>410000</v>
+      </c>
+      <c r="J28" s="42" t="n">
+        <v>120500</v>
+      </c>
+      <c r="K28" s="43" t="n">
+        <v>212</v>
+      </c>
+      <c r="L28" s="44" t="inlineStr">
+        <is>
+          <t>Извещение о внесудебном обращении взыскания на залог, 14.07.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="13" customHeight="1">
+      <c r="A29" s="16" t="inlineStr">
+        <is>
+          <t>Отдел развития АПК</t>
+        </is>
+      </c>
+      <c r="B29" s="17" t="n"/>
+      <c r="C29" s="17" t="n"/>
+      <c r="D29" s="17" t="n"/>
+      <c r="E29" s="18" t="n">
+        <v>3</v>
+      </c>
+      <c r="F29" s="19" t="n">
+        <v>4820000</v>
+      </c>
+      <c r="G29" s="19" t="n">
+        <v>1949000</v>
+      </c>
+      <c r="H29" s="19" t="n">
+        <v>1340000</v>
+      </c>
+      <c r="I29" s="19" t="n">
+        <v>485500</v>
+      </c>
+      <c r="J29" s="19" t="n">
+        <v>123500</v>
+      </c>
+      <c r="K29" s="20" t="n"/>
+      <c r="L29" s="21" t="n"/>
+    </row>
+    <row r="30" ht="13" customHeight="1">
+      <c r="A30" s="22" t="inlineStr">
+        <is>
+          <t>Нарынская обл.</t>
+        </is>
+      </c>
+      <c r="B30" s="23" t="n"/>
+      <c r="C30" s="23" t="n"/>
+      <c r="D30" s="23" t="n"/>
+      <c r="E30" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="F30" s="25" t="n">
+        <v>2100000</v>
+      </c>
+      <c r="G30" s="25" t="n">
+        <v>1024300</v>
+      </c>
+      <c r="H30" s="25" t="n">
+        <v>700000</v>
+      </c>
+      <c r="I30" s="25" t="n">
+        <v>260000</v>
+      </c>
+      <c r="J30" s="25" t="n">
+        <v>64300</v>
+      </c>
+      <c r="K30" s="26" t="n"/>
+      <c r="L30" s="27" t="n"/>
+    </row>
+    <row r="31" ht="13" customHeight="1">
+      <c r="A31" s="28" t="inlineStr">
+        <is>
+          <t>Кочкорский р-н</t>
+        </is>
+      </c>
+      <c r="B31" s="29" t="n"/>
+      <c r="C31" s="29" t="n"/>
+      <c r="D31" s="29" t="n"/>
+      <c r="E31" s="30" t="n">
+        <v>1</v>
+      </c>
+      <c r="F31" s="31" t="n">
+        <v>2100000</v>
+      </c>
+      <c r="G31" s="31" t="n">
+        <v>1024300</v>
+      </c>
+      <c r="H31" s="31" t="n">
+        <v>700000</v>
+      </c>
+      <c r="I31" s="31" t="n">
+        <v>260000</v>
+      </c>
+      <c r="J31" s="31" t="n">
+        <v>64300</v>
+      </c>
+      <c r="K31" s="32" t="n"/>
+      <c r="L31" s="33" t="n"/>
+    </row>
+    <row r="32" ht="13" customHeight="1">
+      <c r="A32" s="34" t="inlineStr">
         <is>
           <t>ОсОО «Нарын-Агро»</t>
         </is>
       </c>
-      <c r="B13" s="8" t="n">
+      <c r="B32" s="35" t="inlineStr">
+        <is>
+          <t>высокий</t>
+        </is>
+      </c>
+      <c r="C32" s="35" t="inlineStr">
+        <is>
+          <t>2.1</t>
+        </is>
+      </c>
+      <c r="D32" s="35" t="n"/>
+      <c r="E32" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="C13" s="9" t="inlineStr"/>
-      <c r="D13" s="9" t="inlineStr"/>
-      <c r="E13" s="10" t="n">
+      <c r="F32" s="37" t="n">
         <v>2100000</v>
       </c>
-      <c r="F13" s="10" t="n">
+      <c r="G32" s="37" t="n">
         <v>1024300</v>
       </c>
-      <c r="G13" s="10" t="n">
+      <c r="H32" s="37" t="n">
         <v>700000</v>
       </c>
-      <c r="H13" s="10" t="n">
+      <c r="I32" s="37" t="n">
         <v>260000</v>
       </c>
-      <c r="I13" s="10" t="n">
+      <c r="J32" s="37" t="n">
         <v>64300</v>
       </c>
-      <c r="J13" s="8" t="n">
+      <c r="K32" s="36" t="n">
         <v>409</v>
       </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="11" t="inlineStr">
+      <c r="L32" s="38" t="n"/>
+    </row>
+    <row r="33" ht="24" customHeight="1">
+      <c r="A33" s="39" t="inlineStr">
         <is>
           <t>№ 21-2/077 от 18.05.2021</t>
         </is>
       </c>
-      <c r="B14" s="9" t="inlineStr"/>
-      <c r="C14" s="9" t="inlineStr">
+      <c r="B33" s="40" t="inlineStr">
+        <is>
+          <t>высокий</t>
+        </is>
+      </c>
+      <c r="C33" s="40" t="inlineStr">
+        <is>
+          <t>2.1</t>
+        </is>
+      </c>
+      <c r="D33" s="40" t="inlineStr">
         <is>
           <t>KGS</t>
         </is>
       </c>
-      <c r="D14" s="9" t="inlineStr">
-        <is>
-          <t>2.1</t>
-        </is>
-      </c>
-      <c r="E14" s="10" t="n">
+      <c r="E33" s="41" t="n"/>
+      <c r="F33" s="42" t="n">
         <v>2100000</v>
       </c>
-      <c r="F14" s="10" t="n">
+      <c r="G33" s="42" t="n">
         <v>1024300</v>
       </c>
-      <c r="G14" s="10" t="n">
+      <c r="H33" s="42" t="n">
         <v>700000</v>
       </c>
-      <c r="H14" s="10" t="n">
+      <c r="I33" s="42" t="n">
         <v>260000</v>
       </c>
-      <c r="I14" s="10" t="n">
+      <c r="J33" s="42" t="n">
         <v>64300</v>
       </c>
-      <c r="J14" s="8" t="n">
+      <c r="K33" s="43" t="n">
         <v>409</v>
       </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="7" t="inlineStr">
+      <c r="L33" s="44" t="inlineStr">
+        <is>
+          <t>Соглашение о добровольном исполнении № 3, 10.09.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="13" customHeight="1">
+      <c r="A34" s="22" t="inlineStr">
+        <is>
+          <t>Таласская обл.</t>
+        </is>
+      </c>
+      <c r="B34" s="23" t="n"/>
+      <c r="C34" s="23" t="n"/>
+      <c r="D34" s="23" t="n"/>
+      <c r="E34" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="F34" s="25" t="n">
+        <v>2720000</v>
+      </c>
+      <c r="G34" s="25" t="n">
+        <v>924700</v>
+      </c>
+      <c r="H34" s="25" t="n">
+        <v>640000</v>
+      </c>
+      <c r="I34" s="25" t="n">
+        <v>225500</v>
+      </c>
+      <c r="J34" s="25" t="n">
+        <v>59200</v>
+      </c>
+      <c r="K34" s="26" t="n"/>
+      <c r="L34" s="27" t="n"/>
+    </row>
+    <row r="35" ht="13" customHeight="1">
+      <c r="A35" s="28" t="inlineStr">
+        <is>
+          <t>Бакай-Атинский р-н</t>
+        </is>
+      </c>
+      <c r="B35" s="29" t="n"/>
+      <c r="C35" s="29" t="n"/>
+      <c r="D35" s="29" t="n"/>
+      <c r="E35" s="30" t="n">
+        <v>1</v>
+      </c>
+      <c r="F35" s="31" t="n">
+        <v>420000</v>
+      </c>
+      <c r="G35" s="31" t="n">
+        <v>51700</v>
+      </c>
+      <c r="H35" s="31" t="n">
+        <v>40000</v>
+      </c>
+      <c r="I35" s="31" t="n">
+        <v>10500</v>
+      </c>
+      <c r="J35" s="31" t="n">
+        <v>1200</v>
+      </c>
+      <c r="K35" s="32" t="n"/>
+      <c r="L35" s="33" t="n"/>
+    </row>
+    <row r="36" ht="13" customHeight="1">
+      <c r="A36" s="34" t="inlineStr">
+        <is>
+          <t>Иманалиев Бакыт Тологонович</t>
+        </is>
+      </c>
+      <c r="B36" s="35" t="inlineStr">
+        <is>
+          <t>средний</t>
+        </is>
+      </c>
+      <c r="C36" s="35" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
+      <c r="D36" s="35" t="n"/>
+      <c r="E36" s="36" t="n">
+        <v>1</v>
+      </c>
+      <c r="F36" s="37" t="n">
+        <v>420000</v>
+      </c>
+      <c r="G36" s="37" t="n">
+        <v>51700</v>
+      </c>
+      <c r="H36" s="37" t="n">
+        <v>40000</v>
+      </c>
+      <c r="I36" s="37" t="n">
+        <v>10500</v>
+      </c>
+      <c r="J36" s="37" t="n">
+        <v>1200</v>
+      </c>
+      <c r="K36" s="36" t="n">
+        <v>95</v>
+      </c>
+      <c r="L36" s="38" t="n"/>
+    </row>
+    <row r="37" ht="24" customHeight="1">
+      <c r="A37" s="39" t="inlineStr">
+        <is>
+          <t>№ 24-2/077 от 14.05.2024</t>
+        </is>
+      </c>
+      <c r="B37" s="40" t="inlineStr">
+        <is>
+          <t>средний</t>
+        </is>
+      </c>
+      <c r="C37" s="40" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
+      <c r="D37" s="40" t="inlineStr">
+        <is>
+          <t>KGS</t>
+        </is>
+      </c>
+      <c r="E37" s="41" t="n"/>
+      <c r="F37" s="42" t="n">
+        <v>420000</v>
+      </c>
+      <c r="G37" s="42" t="n">
+        <v>51700</v>
+      </c>
+      <c r="H37" s="42" t="n">
+        <v>40000</v>
+      </c>
+      <c r="I37" s="42" t="n">
+        <v>10500</v>
+      </c>
+      <c r="J37" s="42" t="n">
+        <v>1200</v>
+      </c>
+      <c r="K37" s="43" t="n">
+        <v>95</v>
+      </c>
+      <c r="L37" s="44" t="inlineStr">
+        <is>
+          <t>Запросы нотариату, ЦОН и органу регистрации, 24.08.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="13" customHeight="1">
+      <c r="A38" s="28" t="inlineStr">
+        <is>
+          <t>Таласский р-н</t>
+        </is>
+      </c>
+      <c r="B38" s="29" t="n"/>
+      <c r="C38" s="29" t="n"/>
+      <c r="D38" s="29" t="n"/>
+      <c r="E38" s="30" t="n">
+        <v>1</v>
+      </c>
+      <c r="F38" s="31" t="n">
+        <v>2300000</v>
+      </c>
+      <c r="G38" s="31" t="n">
+        <v>873000</v>
+      </c>
+      <c r="H38" s="31" t="n">
+        <v>600000</v>
+      </c>
+      <c r="I38" s="31" t="n">
+        <v>215000</v>
+      </c>
+      <c r="J38" s="31" t="n">
+        <v>58000</v>
+      </c>
+      <c r="K38" s="32" t="n"/>
+      <c r="L38" s="33" t="n"/>
+    </row>
+    <row r="39" ht="13" customHeight="1">
+      <c r="A39" s="34" t="inlineStr">
         <is>
           <t>ОсОО «Талас-Бал»</t>
         </is>
       </c>
-      <c r="B15" s="8" t="n">
+      <c r="B39" s="35" t="inlineStr">
+        <is>
+          <t>высокий</t>
+        </is>
+      </c>
+      <c r="C39" s="35" t="inlineStr">
+        <is>
+          <t>2.3</t>
+        </is>
+      </c>
+      <c r="D39" s="35" t="n"/>
+      <c r="E39" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="C15" s="9" t="inlineStr"/>
-      <c r="D15" s="9" t="inlineStr"/>
-      <c r="E15" s="10" t="n">
+      <c r="F39" s="37" t="n">
         <v>2300000</v>
       </c>
-      <c r="F15" s="10" t="n">
+      <c r="G39" s="37" t="n">
         <v>873000</v>
       </c>
-      <c r="G15" s="10" t="n">
+      <c r="H39" s="37" t="n">
         <v>600000</v>
       </c>
-      <c r="H15" s="10" t="n">
+      <c r="I39" s="37" t="n">
         <v>215000</v>
       </c>
-      <c r="I15" s="10" t="n">
+      <c r="J39" s="37" t="n">
         <v>58000</v>
       </c>
-      <c r="J15" s="8" t="n">
+      <c r="K39" s="36" t="n">
         <v>260</v>
       </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="11" t="inlineStr">
+      <c r="L39" s="38" t="n"/>
+    </row>
+    <row r="40" ht="35" customHeight="1">
+      <c r="A40" s="39" t="inlineStr">
         <is>
           <t>№ 23-4/021 от 21.08.2023</t>
         </is>
       </c>
-      <c r="B16" s="9" t="inlineStr"/>
-      <c r="C16" s="9" t="inlineStr">
+      <c r="B40" s="40" t="inlineStr">
+        <is>
+          <t>высокий</t>
+        </is>
+      </c>
+      <c r="C40" s="40" t="inlineStr">
+        <is>
+          <t>2.3</t>
+        </is>
+      </c>
+      <c r="D40" s="40" t="inlineStr">
         <is>
           <t>KGS</t>
         </is>
       </c>
-      <c r="D16" s="9" t="inlineStr">
-        <is>
-          <t>2.3</t>
-        </is>
-      </c>
-      <c r="E16" s="10" t="n">
+      <c r="E40" s="41" t="n"/>
+      <c r="F40" s="42" t="n">
         <v>2300000</v>
       </c>
-      <c r="F16" s="10" t="n">
+      <c r="G40" s="42" t="n">
         <v>873000</v>
       </c>
-      <c r="G16" s="10" t="n">
+      <c r="H40" s="42" t="n">
         <v>600000</v>
       </c>
-      <c r="H16" s="10" t="n">
+      <c r="I40" s="42" t="n">
         <v>215000</v>
       </c>
-      <c r="I16" s="10" t="n">
+      <c r="J40" s="42" t="n">
         <v>58000</v>
       </c>
-      <c r="J16" s="8" t="n">
+      <c r="K40" s="43" t="n">
         <v>260</v>
       </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="7" t="inlineStr">
-        <is>
-          <t>ОсОО «Нарын-Сүт»</t>
-        </is>
-      </c>
-      <c r="B17" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="C17" s="9" t="inlineStr"/>
-      <c r="D17" s="9" t="inlineStr"/>
-      <c r="E17" s="10" t="n">
-        <v>2200000</v>
-      </c>
-      <c r="F17" s="10" t="n">
-        <v>551000</v>
-      </c>
-      <c r="G17" s="10" t="n">
-        <v>400000</v>
-      </c>
-      <c r="H17" s="10" t="n">
-        <v>120000</v>
-      </c>
-      <c r="I17" s="10" t="n">
-        <v>31000</v>
-      </c>
-      <c r="J17" s="8" t="n">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="11" t="inlineStr">
-        <is>
-          <t>№ 23-5/071 от 09.08.2023</t>
-        </is>
-      </c>
-      <c r="B18" s="9" t="inlineStr"/>
-      <c r="C18" s="9" t="inlineStr">
-        <is>
-          <t>KGS</t>
-        </is>
-      </c>
-      <c r="D18" s="9" t="inlineStr">
-        <is>
-          <t>3.1</t>
-        </is>
-      </c>
-      <c r="E18" s="10" t="n">
-        <v>2200000</v>
-      </c>
-      <c r="F18" s="10" t="n">
-        <v>551000</v>
-      </c>
-      <c r="G18" s="10" t="n">
-        <v>400000</v>
-      </c>
-      <c r="H18" s="10" t="n">
-        <v>120000</v>
-      </c>
-      <c r="I18" s="10" t="n">
-        <v>31000</v>
-      </c>
-      <c r="J18" s="8" t="n">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="7" t="inlineStr">
-        <is>
-          <t>Иманалиев Бакыт Тологонович</t>
-        </is>
-      </c>
-      <c r="B19" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="C19" s="9" t="inlineStr"/>
-      <c r="D19" s="9" t="inlineStr"/>
-      <c r="E19" s="10" t="n">
-        <v>420000</v>
-      </c>
-      <c r="F19" s="10" t="n">
-        <v>51700</v>
-      </c>
-      <c r="G19" s="10" t="n">
-        <v>40000</v>
-      </c>
-      <c r="H19" s="10" t="n">
-        <v>10500</v>
-      </c>
-      <c r="I19" s="10" t="n">
-        <v>1200</v>
-      </c>
-      <c r="J19" s="8" t="n">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="11" t="inlineStr">
-        <is>
-          <t>№ 24-2/077 от 14.05.2024</t>
-        </is>
-      </c>
-      <c r="B20" s="9" t="inlineStr"/>
-      <c r="C20" s="9" t="inlineStr">
-        <is>
-          <t>KGS</t>
-        </is>
-      </c>
-      <c r="D20" s="9" t="inlineStr">
-        <is>
-          <t>1.2</t>
-        </is>
-      </c>
-      <c r="E20" s="10" t="n">
-        <v>420000</v>
-      </c>
-      <c r="F20" s="10" t="n">
-        <v>51700</v>
-      </c>
-      <c r="G20" s="10" t="n">
-        <v>40000</v>
-      </c>
-      <c r="H20" s="10" t="n">
-        <v>10500</v>
-      </c>
-      <c r="I20" s="10" t="n">
-        <v>1200</v>
-      </c>
-      <c r="J20" s="8" t="n">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="3" t="inlineStr">
-        <is>
-          <t>Региональное представительство «Ош»</t>
-        </is>
-      </c>
-      <c r="B21" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="C21" s="5" t="inlineStr"/>
-      <c r="D21" s="5" t="inlineStr"/>
-      <c r="E21" s="6" t="n">
-        <v>3600000</v>
-      </c>
-      <c r="F21" s="6" t="n">
-        <v>1730500</v>
-      </c>
-      <c r="G21" s="6" t="n">
-        <v>1200000</v>
-      </c>
-      <c r="H21" s="6" t="n">
-        <v>410000</v>
-      </c>
-      <c r="I21" s="6" t="n">
-        <v>120500</v>
-      </c>
-      <c r="J21" s="5" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="7" t="inlineStr">
-        <is>
-          <t>ОсОО «Ош-Текстиль»</t>
-        </is>
-      </c>
-      <c r="B22" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="C22" s="9" t="inlineStr"/>
-      <c r="D22" s="9" t="inlineStr"/>
-      <c r="E22" s="10" t="n">
-        <v>3600000</v>
-      </c>
-      <c r="F22" s="10" t="n">
-        <v>1730500</v>
-      </c>
-      <c r="G22" s="10" t="n">
-        <v>1200000</v>
-      </c>
-      <c r="H22" s="10" t="n">
-        <v>410000</v>
-      </c>
-      <c r="I22" s="10" t="n">
-        <v>120500</v>
-      </c>
-      <c r="J22" s="8" t="n">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="11" t="inlineStr">
-        <is>
-          <t>№ 21-5/203 от 09.09.2021</t>
-        </is>
-      </c>
-      <c r="B23" s="9" t="inlineStr"/>
-      <c r="C23" s="9" t="inlineStr">
-        <is>
-          <t>KGS</t>
-        </is>
-      </c>
-      <c r="D23" s="9" t="inlineStr">
-        <is>
-          <t>1.2</t>
-        </is>
-      </c>
-      <c r="E23" s="10" t="n">
-        <v>3600000</v>
-      </c>
-      <c r="F23" s="10" t="n">
-        <v>1730500</v>
-      </c>
-      <c r="G23" s="10" t="n">
-        <v>1200000</v>
-      </c>
-      <c r="H23" s="10" t="n">
-        <v>410000</v>
-      </c>
-      <c r="I23" s="10" t="n">
-        <v>120500</v>
-      </c>
-      <c r="J23" s="8" t="n">
-        <v>212</v>
+      <c r="L40" s="44" t="inlineStr">
+        <is>
+          <t>Уведомление о намерении инициировать банкротство, 15.06.2026</t>
+        </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
-    <mergeCell ref="A1:J1"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="C4:C5"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="F4:F5"/>
-    <mergeCell ref="D4:D5"/>
-    <mergeCell ref="E4:E5"/>
-    <mergeCell ref="J4:J5"/>
-    <mergeCell ref="G4:I4"/>
-    <mergeCell ref="A2:J2"/>
+  <mergeCells count="12">
+    <mergeCell ref="A5:A6"/>
+    <mergeCell ref="G5:G6"/>
+    <mergeCell ref="A2:L2"/>
+    <mergeCell ref="E5:E6"/>
+    <mergeCell ref="K5:K6"/>
+    <mergeCell ref="H5:J5"/>
+    <mergeCell ref="L5:L6"/>
+    <mergeCell ref="F5:F6"/>
+    <mergeCell ref="A3:L3"/>
+    <mergeCell ref="D5:D6"/>
+    <mergeCell ref="B5:B6"/>
+    <mergeCell ref="C5:C6"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.39" right="0.39" top="0.39" bottom="0.39" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;"Arial"&amp;8 ФО-01 · сформировал Асанов А. К. 06.10.2026 09:12 · Страница &amp;P из &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -1193,7 +2039,201 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:C36"/>
+  <dimension ref="A1:B16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="80" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="45" t="inlineStr">
+        <is>
+          <t>Параметры отчёта</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="15" customHeight="1">
+      <c r="A3" s="46" t="inlineStr">
+        <is>
+          <t>Отчёт</t>
+        </is>
+      </c>
+      <c r="B3" s="47" t="inlineStr">
+        <is>
+          <t>ФО-01 «Просроченная задолженность по состоянию на дату»</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="15" customHeight="1">
+      <c r="A4" s="46" t="inlineStr">
+        <is>
+          <t>Дата состояния</t>
+        </is>
+      </c>
+      <c r="B4" s="47" t="inlineStr">
+        <is>
+          <t>01.10.2026 (данные на конец 30.09.2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="15" customHeight="1">
+      <c r="A5" s="46" t="inlineStr">
+        <is>
+          <t>Департамент</t>
+        </is>
+      </c>
+      <c r="B5" s="47" t="inlineStr">
+        <is>
+          <t>все</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="15" customHeight="1">
+      <c r="A6" s="46" t="inlineStr">
+        <is>
+          <t>Отдел</t>
+        </is>
+      </c>
+      <c r="B6" s="47" t="inlineStr">
+        <is>
+          <t>все</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="15" customHeight="1">
+      <c r="A7" s="46" t="inlineStr">
+        <is>
+          <t>Область</t>
+        </is>
+      </c>
+      <c r="B7" s="47" t="inlineStr">
+        <is>
+          <t>все</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="15" customHeight="1">
+      <c r="A8" s="46" t="inlineStr">
+        <is>
+          <t>Категория риска</t>
+        </is>
+      </c>
+      <c r="B8" s="47" t="inlineStr">
+        <is>
+          <t>все</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="15" customHeight="1">
+      <c r="A9" s="46" t="inlineStr">
+        <is>
+          <t>Просрочка от, дней</t>
+        </is>
+      </c>
+      <c r="B9" s="47" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="15" customHeight="1">
+      <c r="A10" s="46" t="inlineStr">
+        <is>
+          <t>Единица</t>
+        </is>
+      </c>
+      <c r="B10" s="47" t="inlineStr">
+        <is>
+          <t>сом</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" s="46" t="inlineStr">
+        <is>
+          <t>Разрезы</t>
+        </is>
+      </c>
+      <c r="B11" s="47" t="inlineStr">
+        <is>
+          <t>Департамент → Отдел → Область → Район → Заёмщик → кредит</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="15" customHeight="1">
+      <c r="A12" s="46" t="inlineStr">
+        <is>
+          <t>Курсы валют</t>
+        </is>
+      </c>
+      <c r="B12" s="47" t="inlineStr">
+        <is>
+          <t>USD — 87,50000 на 30.09.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="15" customHeight="1">
+      <c r="A13" s="46" t="inlineStr">
+        <is>
+          <t>Период</t>
+        </is>
+      </c>
+      <c r="B13" s="47" t="inlineStr">
+        <is>
+          <t>сентябрь 2026 — закрыт 05.10.2026; исправлений после закрытия нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="15" customHeight="1">
+      <c r="A14" s="46" t="inlineStr">
+        <is>
+          <t>Рассчитан</t>
+        </is>
+      </c>
+      <c r="B14" s="47" t="inlineStr">
+        <is>
+          <t>06.10.2026 09:12</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="15" customHeight="1">
+      <c r="A15" s="46" t="inlineStr">
+        <is>
+          <t>Сформировал</t>
+        </is>
+      </c>
+      <c r="B15" s="47" t="inlineStr">
+        <is>
+          <t>Асанов А. К.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="27" customHeight="1">
+      <c r="A16" s="46" t="inlineStr">
+        <is>
+          <t>Округление</t>
+        </is>
+      </c>
+      <c r="B16" s="47" t="inlineStr">
+        <is>
+          <t>В ячейках — точные суммы, на экране и в печати — до копеек. Итоги считаются по точным суммам, поэтому сумма округлённых строк может отличаться от итога на копейки.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:C45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -1202,436 +2242,557 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="12" t="inlineStr">
-        <is>
-          <t>ФО-01 «Просроченная задолженность по состоянию на 1-е число» — карточка</t>
+      <c r="A1" s="48" t="inlineStr">
+        <is>
+          <t>ФО-01 «Просроченная задолженность по состоянию на дату» — карточка</t>
         </is>
       </c>
     </row>
     <row r="3" ht="15" customHeight="1">
-      <c r="A3" s="13" t="inlineStr">
+      <c r="A3" s="49" t="inlineStr">
         <is>
           <t>Номер</t>
         </is>
       </c>
-      <c r="B3" s="14" t="inlineStr">
+      <c r="B3" s="50" t="inlineStr">
         <is>
           <t>ФО-01</t>
         </is>
       </c>
     </row>
     <row r="4" ht="15" customHeight="1">
-      <c r="A4" s="13" t="inlineStr">
+      <c r="A4" s="49" t="inlineStr">
         <is>
           <t>Название</t>
         </is>
       </c>
-      <c r="B4" s="14" t="inlineStr">
-        <is>
-          <t>Просроченная задолженность по состоянию на 1-е число</t>
+      <c r="B4" s="50" t="inlineStr">
+        <is>
+          <t>Просроченная задолженность по состоянию на дату</t>
         </is>
       </c>
     </row>
     <row r="5" ht="15" customHeight="1">
-      <c r="A5" s="13" t="inlineStr">
+      <c r="A5" s="49" t="inlineStr">
         <is>
           <t>Часть</t>
         </is>
       </c>
-      <c r="B5" s="14" t="inlineStr">
+      <c r="B5" s="50" t="inlineStr">
         <is>
           <t>Отчёт</t>
         </is>
       </c>
     </row>
     <row r="6" ht="15" customHeight="1">
-      <c r="A6" s="13" t="inlineStr">
+      <c r="A6" s="49" t="inlineStr">
         <is>
           <t>Модуль</t>
         </is>
       </c>
-      <c r="B6" s="14" t="inlineStr">
+      <c r="B6" s="50" t="inlineStr">
         <is>
           <t>Кредит</t>
         </is>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
-      <c r="A7" s="13" t="inlineStr">
+      <c r="A7" s="49" t="inlineStr">
         <is>
           <t>Получатель</t>
         </is>
       </c>
-      <c r="B7" s="14" t="inlineStr">
+      <c r="B7" s="50" t="inlineStr">
         <is>
           <t>Комитет</t>
         </is>
       </c>
     </row>
     <row r="8" ht="15" customHeight="1">
-      <c r="A8" s="13" t="inlineStr">
+      <c r="A8" s="49" t="inlineStr">
         <is>
           <t>Язык</t>
         </is>
       </c>
-      <c r="B8" s="14" t="inlineStr">
+      <c r="B8" s="50" t="inlineStr">
         <is>
           <t>язык интерфейса</t>
         </is>
       </c>
     </row>
     <row r="9" ht="15" customHeight="1">
-      <c r="A9" s="13" t="inlineStr">
+      <c r="A9" s="49" t="inlineStr">
         <is>
           <t>Основание</t>
         </is>
       </c>
-      <c r="B9" s="14" t="inlineStr">
+      <c r="B9" s="50" t="inlineStr">
         <is>
           <t>Порядок №41 п. 12, п. 6 пп. 1; оф. ТЗ ¶76, ¶477, ¶644–670; ТЗ 17</t>
         </is>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1">
-      <c r="A10" s="13" t="inlineStr">
+      <c r="A10" s="49" t="inlineStr">
         <is>
           <t>Образец-основа</t>
         </is>
       </c>
-      <c r="B10" s="14" t="inlineStr">
+      <c r="B10" s="50" t="inlineStr">
         <is>
           <t>старая система «Отчет по задолженности»</t>
         </is>
       </c>
     </row>
     <row r="11" ht="45" customHeight="1">
-      <c r="A11" s="13" t="inlineStr">
+      <c r="A11" s="49" t="inlineStr">
         <is>
           <t>Кому и зачем</t>
         </is>
       </c>
-      <c r="B11" s="14" t="inlineStr">
-        <is>
-          <t>Соответствующему комитету (по администрированию бюджетных кредитов или по региональному развитию — в зависимости от департамента) — актуальная просроченная задолженность заёмщиков на 1-е число месяца, следующего за отчётным: сколько кредитов с просрочкой, на какую сумму и как давно.</t>
+      <c r="B11" s="50" t="inlineStr">
+        <is>
+          <t>Соответствующему комитету (по администрированию бюджетных кредитов или по региональному развитию — в зависимости от департамента) — актуальная просроченная задолженность заёмщиков: сколько кредитов с просрочкой, на какую сумму, как давно и что по ним делается.</t>
         </is>
       </c>
     </row>
     <row r="12" ht="30" customHeight="1">
-      <c r="A12" s="13" t="inlineStr">
+      <c r="A12" s="49" t="inlineStr">
         <is>
           <t>Когда</t>
         </is>
       </c>
-      <c r="B12" s="14" t="inlineStr">
-        <is>
-          <t>На дату: 1-е число месяца, следующего за отчётным. Формируется ежемесячно; отраслевой департамент выносит на соответствующий комитет не позднее 15-го числа (Порядок №41 п. 12).</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="75" customHeight="1">
-      <c r="A13" s="13" t="inlineStr">
+      <c r="B12" s="50" t="inlineStr">
+        <is>
+          <t>На любую дату. Для комитета — на 1-е число месяца, следующего за отчётным, ежемесячно; отраслевой департамент выносит на соответствующий комитет не позднее 15-го числа (Порядок №41 п. 12).</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="180" customHeight="1">
+      <c r="A13" s="49" t="inlineStr">
         <is>
           <t>Параметры</t>
         </is>
       </c>
-      <c r="B13" s="14" t="inlineStr">
-        <is>
-          <t>• Дата состояния — 1-е число текущего месяца
-• Подразделение — все
-• Просрочка от, дней — 1
-• Единица — сом (можно выбрать «тыс. сом»)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="60" customHeight="1">
-      <c r="A14" s="13" t="inlineStr">
+      <c r="B13" s="50" t="inlineStr">
+        <is>
+          <t>• Дата состояния — 1-е число текущего месяца; можно выбрать любую дату
+• Департамент — все
+• Отдел — все (в пределах выбранных департаментов)
+• Область — все
+• Категория риска — все (низкий, средний, высокий)
+• Просрочка от, дней — 1; 0 — все кредиты с остатком
+• Единица — сом (можно выбрать «тыс. сом»)
+• Разрезы — департамент → отдел → область → район → заёмщик; можно выбрать другие и их порядок</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="180" customHeight="1">
+      <c r="A14" s="49" t="inlineStr">
         <is>
           <t>Строки</t>
         </is>
       </c>
-      <c r="B14" s="14" t="inlineStr">
-        <is>
-          <t>Подразделение → заёмщик → кредит. Подразделения разных комитетов выводятся в одной таблице. Подытоги по подразделению и заёмщику, сверху ИТОГО. Внутри подразделения — по убыванию дней просрочки. В отчёт попадают только кредиты с просрочкой не меньше заданного числа дней на дату состояния; колонки сокращены: отчёт показывает только кредиты с просрочкой.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="15" customHeight="1">
-      <c r="A15" s="13" t="inlineStr">
+      <c r="B14" s="50" t="inlineStr">
+        <is>
+          <t>Строка детали — кредит: договор, признаки, суммы, дни просрочки, стадия взыскания. Над кредитами разрезы, по умолчанию департамент → отдел → область → район → заёмщик; область и район — кредита на дату состояния; у городов республиканского значения показываются обе строки — области и района; подразделение — то, за которым кредит закреплён на дату состояния. Первая строка — ИТОГО; строка разреза несёт его итог (число кредитов и суммы) и стоит над его строками; строка заёмщика есть всегда, даже при одном кредите. Признак, выбранный разрезом, колонкой не повторяется. Порядок: департаменты и отделы — по оргструктуре; области — по справочнику (области по алфавиту, затем г. Бишкек, г. Ош); районы — по алфавиту; заёмщики — по убыванию наибольших дней просрочки, при равных — по алфавиту; кредиты заёмщика — по убыванию дней. В отчёт попадают кредиты с просрочкой не меньше заданного числа дней на дату состояния. Кредит в иностранной валюте: суммы в сомах по курсу на дату, под ним курсивом строка «в &lt;валюта&gt; (курс …)» с теми же суммами в валюте договора; в итоги она не входит.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="45" customHeight="1">
+      <c r="A15" s="49" t="inlineStr">
+        <is>
+          <t>Разрезы</t>
+        </is>
+      </c>
+      <c r="B15" s="50" t="inlineStr">
+        <is>
+          <t>по умолчанию: Департамент → Отдел → Область → Район → Заёмщик → кредит; можно выбрать: Департамент, Отдел, Куратор, Область, Район, Категория риска, Группа платёжеспособности, Тип проекта, Заёмщик</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="15" customHeight="1">
+      <c r="A16" s="49" t="inlineStr">
+        <is>
+          <t>Если строк нет</t>
+        </is>
+      </c>
+      <c r="B16" s="50" t="inlineStr">
+        <is>
+          <t>Кредитов с просрочкой от {N} дней на {дата} нет.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="15" customHeight="1">
+      <c r="A17" s="49" t="inlineStr">
         <is>
           <t>Выгрузка</t>
         </is>
       </c>
-      <c r="B15" s="14" t="inlineStr">
+      <c r="B17" s="50" t="inlineStr">
         <is>
           <t>xlsx, pdf</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="15" customHeight="1">
-      <c r="A16" s="13" t="inlineStr">
+    <row r="18" ht="15" customHeight="1">
+      <c r="A18" s="49" t="inlineStr">
         <is>
           <t>Примечание</t>
         </is>
       </c>
-      <c r="B16" s="14" t="inlineStr">
-        <is>
-          <t>Ежемесячно до 15-го, данные на 1-е число</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="15" t="inlineStr">
+      <c r="B18" s="50" t="inlineStr">
+        <is>
+          <t>Для комитета — на 1-е число, ежемесячно до 15-го</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="51" t="inlineStr">
         <is>
           <t>Колонки</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="16" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="52" t="inlineStr">
         <is>
           <t>Колонка</t>
         </is>
       </c>
-      <c r="B19" s="16" t="inlineStr">
+      <c r="B21" s="52" t="inlineStr">
         <is>
           <t>Общая шапка</t>
         </is>
       </c>
-      <c r="C19" s="16" t="inlineStr">
+      <c r="C21" s="52" t="inlineStr">
         <is>
           <t>Что в ней</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="14" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="50" t="inlineStr">
         <is>
           <t>Наименование</t>
         </is>
       </c>
-      <c r="B20" s="14" t="inlineStr"/>
-      <c r="C20" s="14" t="inlineStr">
-        <is>
-          <t>подразделение, заёмщик или номер договора — по уровню строки</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="14" t="inlineStr">
+      <c r="B22" s="50" t="inlineStr"/>
+      <c r="C22" s="50" t="inlineStr">
+        <is>
+          <t>департамент, отдел, область, район, заёмщик или договор — по уровню строки</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="50" t="inlineStr">
+        <is>
+          <t>Категория риска</t>
+        </is>
+      </c>
+      <c r="B23" s="50" t="inlineStr"/>
+      <c r="C23" s="50" t="inlineStr">
+        <is>
+          <t>категория кредитного риска на дату состояния: у кредита — его категория, у заёмщика — худшая по его кредитам; выше заёмщика пусто</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="50" t="inlineStr">
+        <is>
+          <t>Группа</t>
+        </is>
+      </c>
+      <c r="B24" s="50" t="inlineStr"/>
+      <c r="C24" s="50" t="inlineStr">
+        <is>
+          <t>группа платёжеспособности заёмщика на дату состояния по Инструкции №14; у заёмщика и у каждого его кредита одна и та же; выше заёмщика пусто</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="50" t="inlineStr">
+        <is>
+          <t>Валюта</t>
+        </is>
+      </c>
+      <c r="B25" s="50" t="inlineStr"/>
+      <c r="C25" s="50" t="inlineStr">
+        <is>
+          <t>валюта кредита; заполняется у кредита</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="50" t="inlineStr">
         <is>
           <t>Кредитов с просрочкой</t>
         </is>
       </c>
-      <c r="B21" s="14" t="inlineStr"/>
-      <c r="C21" s="14" t="inlineStr">
-        <is>
-          <t>число кредитов с просроченной задолженностью; у кредита не заполняется</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="14" t="inlineStr">
-        <is>
-          <t>Валюта</t>
-        </is>
-      </c>
-      <c r="B22" s="14" t="inlineStr"/>
-      <c r="C22" s="14" t="inlineStr">
-        <is>
-          <t>валюта кредита; заполняется у кредита</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="14" t="inlineStr">
-        <is>
-          <t>Группа платёжеспособности</t>
-        </is>
-      </c>
-      <c r="B23" s="14" t="inlineStr"/>
-      <c r="C23" s="14" t="inlineStr">
-        <is>
-          <t>группа заёмщика на дату состояния по Инструкции №14 (1.1, 1.2, 2.1, 2.2, 2.3 и т. д.); заполняется у кредита</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="14" t="inlineStr">
+      <c r="B26" s="50" t="inlineStr"/>
+      <c r="C26" s="50" t="inlineStr">
+        <is>
+          <t>число кредитов разреза с просрочкой не меньше заданной; у кредита пусто</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="50" t="inlineStr">
         <is>
           <t>Остаток основного долга</t>
         </is>
       </c>
-      <c r="B24" s="14" t="inlineStr"/>
-      <c r="C24" s="14" t="inlineStr">
-        <is>
-          <t>остаток основной суммы по кредиту на дату состояния; для валютных кредитов — в сомах по курсу на эту дату</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="14" t="inlineStr">
+      <c r="B27" s="50" t="inlineStr"/>
+      <c r="C27" s="50" t="inlineStr">
+        <is>
+          <t>остаток основной суммы на дату состояния; валютный кредит — в сомах по курсу на эту дату</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="50" t="inlineStr">
         <is>
           <t>Просроченная задолженность</t>
         </is>
       </c>
-      <c r="B25" s="14" t="inlineStr"/>
-      <c r="C25" s="14" t="inlineStr">
-        <is>
-          <t>основная сумма + проценты + штрафы, срок оплаты которых наступил</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="14" t="inlineStr">
+      <c r="B28" s="50" t="inlineStr"/>
+      <c r="C28" s="50" t="inlineStr">
+        <is>
+          <t>основная сумма + проценты + штрафы, срок уплаты которых наступил и которые не оплачены</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="50" t="inlineStr">
         <is>
           <t>основная сумма</t>
         </is>
       </c>
-      <c r="B26" s="14" t="inlineStr">
+      <c r="B29" s="50" t="inlineStr">
         <is>
           <t>в том числе</t>
         </is>
       </c>
-      <c r="C26" s="14" t="inlineStr">
+      <c r="C29" s="50" t="inlineStr">
         <is>
           <t>просроченная основная сумма</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="14" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="50" t="inlineStr">
         <is>
           <t>проценты</t>
         </is>
       </c>
-      <c r="B27" s="14" t="inlineStr">
+      <c r="B30" s="50" t="inlineStr">
         <is>
           <t>в том числе</t>
         </is>
       </c>
-      <c r="C27" s="14" t="inlineStr">
-        <is>
-          <t>просроченные проценты, включая накопленные</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="14" t="inlineStr">
+      <c r="C30" s="50" t="inlineStr">
+        <is>
+          <t>просроченные проценты — начисленные и ранее накопленные (накопленные бывают только после реструктуризации)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="50" t="inlineStr">
         <is>
           <t>штрафы</t>
         </is>
       </c>
-      <c r="B28" s="14" t="inlineStr">
+      <c r="B31" s="50" t="inlineStr">
         <is>
           <t>в том числе</t>
         </is>
       </c>
-      <c r="C28" s="14" t="inlineStr">
-        <is>
-          <t>начисленные и неоплаченные штрафы</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="14" t="inlineStr">
+      <c r="C31" s="50" t="inlineStr">
+        <is>
+          <t>неоплаченные штрафы — начисленные и ранее накопленные</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="50" t="inlineStr">
         <is>
           <t>Дни просрочки</t>
         </is>
       </c>
-      <c r="B29" s="14" t="inlineStr"/>
-      <c r="C29" s="14" t="inlineStr">
-        <is>
-          <t>число дней от наиболее ранней неоплаченной даты платежа до даты состояния; у подразделения и заёмщика не заполняется</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="15" t="inlineStr">
+      <c r="B32" s="50" t="inlineStr"/>
+      <c r="C32" s="50" t="inlineStr">
+        <is>
+          <t>дни от самой ранней неоплаченной даты платежа до даты состояния; у заёмщика — наибольшие по его кредитам; выше заёмщика пусто</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="50" t="inlineStr">
+        <is>
+          <t>Стадия взыскания</t>
+        </is>
+      </c>
+      <c r="B33" s="50" t="inlineStr"/>
+      <c r="C33" s="50" t="inlineStr">
+        <is>
+          <t>последняя зарегистрированная мера взыскания по кредиту и её дата; если мер нет — «мер нет»; заполняется у кредита</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="51" t="inlineStr">
         <is>
           <t>Правила проверки</t>
         </is>
       </c>
     </row>
-    <row r="32" ht="30" customHeight="1">
-      <c r="A32" s="13" t="inlineStr">
+    <row r="36" ht="30" customHeight="1">
+      <c r="A36" s="49" t="inlineStr">
         <is>
           <t>1.</t>
         </is>
       </c>
-      <c r="B32" s="14" t="inlineStr">
-        <is>
-          <t>ИТОГО по «Просроченная задолженность» = сумма просроченной задолженности по карточкам кредитов набора на дату отчёта: 4 560 750,00 сом по 7 кредитам (КЗ-02, 03, 04, 05, 09, 10, 19).</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="30" customHeight="1">
-      <c r="A33" s="13" t="inlineStr">
+      <c r="B36" s="50" t="inlineStr">
+        <is>
+          <t>ИТОГО: «Просроченная задолженность» = 4 560 750,00 сом по 7 кредитам (КЗ-02, 03, 04, 05, 09, 10, 19); «Остаток основного долга» = 13 170 000,00 сом.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="45" customHeight="1">
+      <c r="A37" s="49" t="inlineStr">
         <is>
           <t>2.</t>
         </is>
       </c>
-      <c r="B33" s="14" t="inlineStr">
-        <is>
-          <t>«Кредитов с просрочкой» у подразделения = число его кредитов, у которых дней просрочки не меньше заданного; в ИТОГО — 7.</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="30" customHeight="1">
-      <c r="A34" s="13" t="inlineStr">
+      <c r="B37" s="50" t="inlineStr">
+        <is>
+          <t>Строка разреза = сумма строк на уровень ниже по каждой суммовой колонке (заёмщик — его кредитов, район — его заёмщиков и т. д.), ИТОГО — сумма департаментов; «Кредитов с просрочкой» = число кредитов разреза, в ИТОГО — 7.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="15" customHeight="1">
+      <c r="A38" s="49" t="inlineStr">
         <is>
           <t>3.</t>
         </is>
       </c>
-      <c r="B34" s="14" t="inlineStr">
+      <c r="B38" s="50" t="inlineStr">
+        <is>
+          <t>У КЗ-02 (г. Бишкек) две строки: область и район.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="30" customHeight="1">
+      <c r="A39" s="49" t="inlineStr">
+        <is>
+          <t>4.</t>
+        </is>
+      </c>
+      <c r="B39" s="50" t="inlineStr">
         <is>
           <t>Дни просрочки на 01.10.2026: КЗ-02 — 20, КЗ-03 — 75, КЗ-09 — 95, КЗ-19 — 190, КЗ-04 — 212, КЗ-10 — 260, КЗ-05 — 409 (считается от 18.08.2025).</t>
         </is>
       </c>
     </row>
-    <row r="35" ht="15" customHeight="1">
-      <c r="A35" s="13" t="inlineStr">
-        <is>
-          <t>4.</t>
-        </is>
-      </c>
-      <c r="B35" s="14" t="inlineStr">
+    <row r="40" ht="30" customHeight="1">
+      <c r="A40" s="49" t="inlineStr">
+        <is>
+          <t>5.</t>
+        </is>
+      </c>
+      <c r="B40" s="50" t="inlineStr">
+        <is>
+          <t>Категория риска: средний — КЗ-02, 03, 09; высокий — КЗ-04, 05, 10, 19 (Порядок №41 п. 11: 1–180 дней — средний, более 180 — высокий).</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="15" customHeight="1">
+      <c r="A41" s="49" t="inlineStr">
+        <is>
+          <t>6.</t>
+        </is>
+      </c>
+      <c r="B41" s="50" t="inlineStr">
+        <is>
+          <t>Группа = группе заёмщика в контрольном наборе.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="30" customHeight="1">
+      <c r="A42" s="49" t="inlineStr">
+        <is>
+          <t>7.</t>
+        </is>
+      </c>
+      <c r="B42" s="50" t="inlineStr">
+        <is>
+          <t>Стадия взыскания: КЗ-05 — «Соглашение о добровольном исполнении № 3, 10.09.2026»; КЗ-19 — «мер нет».</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="15" customHeight="1">
+      <c r="A43" s="49" t="inlineStr">
+        <is>
+          <t>8.</t>
+        </is>
+      </c>
+      <c r="B43" s="50" t="inlineStr">
         <is>
           <t>КЗ-01 (платит по графику) и КЗ-15 (кредит погашен) в отчёте на 01.10.2026 не показаны.</t>
         </is>
       </c>
     </row>
-    <row r="36" ht="15" customHeight="1">
-      <c r="A36" s="13" t="inlineStr">
-        <is>
-          <t>5.</t>
-        </is>
-      </c>
-      <c r="B36" s="14" t="inlineStr">
-        <is>
-          <t>Подытог подразделения и заёмщика и ИТОГО = сумма строк ниже по каждой числовой колонке.</t>
+    <row r="44" ht="15" customHeight="1">
+      <c r="A44" s="49" t="inlineStr">
+        <is>
+          <t>9.</t>
+        </is>
+      </c>
+      <c r="B44" s="50" t="inlineStr">
+        <is>
+          <t>Строка заёмщика есть и при одном кредите; в районе заёмщики — по убыванию дней.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="30" customHeight="1">
+      <c r="A45" s="49" t="inlineStr">
+        <is>
+          <t>10.</t>
+        </is>
+      </c>
+      <c r="B45" s="50" t="inlineStr">
+        <is>
+          <t>Отбор «Отдел развития регионов», категория «средний» на 01.10.2026: только ИТОГО с нулями и под таблицей «Кредитов с просрочкой от 1 дня на 01.10.2026 нет.»</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="19">
+  <mergeCells count="26">
     <mergeCell ref="B16:C16"/>
     <mergeCell ref="B7:C7"/>
     <mergeCell ref="B3:C3"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="B43:C43"/>
     <mergeCell ref="B12:C12"/>
+    <mergeCell ref="B39:C39"/>
     <mergeCell ref="B11:C11"/>
+    <mergeCell ref="B42:C42"/>
     <mergeCell ref="B14:C14"/>
+    <mergeCell ref="B17:C17"/>
     <mergeCell ref="B8:C8"/>
     <mergeCell ref="B13:C13"/>
-    <mergeCell ref="B34:C34"/>
+    <mergeCell ref="B38:C38"/>
+    <mergeCell ref="B44:C44"/>
+    <mergeCell ref="B37:C37"/>
     <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B40:C40"/>
     <mergeCell ref="B9:C9"/>
     <mergeCell ref="B6:C6"/>
     <mergeCell ref="B15:C15"/>
-    <mergeCell ref="B33:C33"/>
     <mergeCell ref="B5:C5"/>
+    <mergeCell ref="B45:C45"/>
     <mergeCell ref="B36:C36"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="B41:C41"/>
     <mergeCell ref="B4:C4"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/perechen-otchetov/obrazcy/ФО-01.xlsx
+++ b/docs/perechen-otchetov/obrazcy/ФО-01.xlsx
@@ -21,7 +21,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="13">
+  <fonts count="14">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -60,6 +60,12 @@
     </font>
     <font>
       <name val="Arial"/>
+      <i val="1"/>
+      <color rgb="00555555"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Arial"/>
       <b val="1"/>
       <sz val="11"/>
     </font>
@@ -85,7 +91,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -124,11 +130,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FCE4D6"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="00DCE6F2"/>
       </patternFill>
     </fill>
@@ -159,7 +160,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="53">
+  <cellXfs count="58">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -258,19 +259,19 @@
     <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1" indent="4"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="3" fontId="6" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="3" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="4" fontId="6" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="4" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -291,22 +292,37 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="6"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="4" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="11" fillId="9" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -672,7 +688,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:L40"/>
+  <dimension ref="A1:L56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -843,22 +859,22 @@
       <c r="C8" s="7" t="n"/>
       <c r="D8" s="7" t="n"/>
       <c r="E8" s="8" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F8" s="9" t="n">
-        <v>13170000</v>
+        <v>41417000</v>
       </c>
       <c r="G8" s="9" t="n">
-        <v>4560750</v>
+        <v>10328815</v>
       </c>
       <c r="H8" s="9" t="n">
-        <v>3180000</v>
+        <v>7454500</v>
       </c>
       <c r="I8" s="9" t="n">
-        <v>1085000</v>
+        <v>2350865</v>
       </c>
       <c r="J8" s="9" t="n">
-        <v>295750</v>
+        <v>523450</v>
       </c>
       <c r="K8" s="10" t="n"/>
       <c r="L8" s="6" t="n"/>
@@ -873,22 +889,22 @@
       <c r="C9" s="12" t="n"/>
       <c r="D9" s="12" t="n"/>
       <c r="E9" s="13" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F9" s="14" t="n">
-        <v>2550000</v>
+        <v>22922000</v>
       </c>
       <c r="G9" s="14" t="n">
-        <v>330250</v>
+        <v>4326440</v>
       </c>
       <c r="H9" s="14" t="n">
-        <v>240000</v>
+        <v>3202000</v>
       </c>
       <c r="I9" s="14" t="n">
-        <v>69500</v>
+        <v>980990</v>
       </c>
       <c r="J9" s="14" t="n">
-        <v>20750</v>
+        <v>143450</v>
       </c>
       <c r="K9" s="15" t="n"/>
       <c r="L9" s="11" t="n"/>
@@ -903,22 +919,22 @@
       <c r="C10" s="17" t="n"/>
       <c r="D10" s="17" t="n"/>
       <c r="E10" s="18" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F10" s="19" t="n">
-        <v>2550000</v>
+        <v>22922000</v>
       </c>
       <c r="G10" s="19" t="n">
-        <v>330250</v>
+        <v>4326440</v>
       </c>
       <c r="H10" s="19" t="n">
-        <v>240000</v>
+        <v>3202000</v>
       </c>
       <c r="I10" s="19" t="n">
-        <v>69500</v>
+        <v>980990</v>
       </c>
       <c r="J10" s="19" t="n">
-        <v>20750</v>
+        <v>143450</v>
       </c>
       <c r="K10" s="20" t="n"/>
       <c r="L10" s="21" t="n"/>
@@ -933,22 +949,22 @@
       <c r="C11" s="23" t="n"/>
       <c r="D11" s="23" t="n"/>
       <c r="E11" s="24" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F11" s="25" t="n">
-        <v>650000</v>
+        <v>16150000</v>
       </c>
       <c r="G11" s="25" t="n">
-        <v>149400</v>
+        <v>3083900</v>
       </c>
       <c r="H11" s="25" t="n">
-        <v>90000</v>
+        <v>2240000</v>
       </c>
       <c r="I11" s="25" t="n">
-        <v>41000</v>
+        <v>733250</v>
       </c>
       <c r="J11" s="25" t="n">
-        <v>18400</v>
+        <v>110650</v>
       </c>
       <c r="K11" s="26" t="n"/>
       <c r="L11" s="27" t="n"/>
@@ -1070,215 +1086,245 @@
       </c>
     </row>
     <row r="15" ht="13" customHeight="1">
-      <c r="A15" s="22" t="inlineStr">
-        <is>
-          <t>г. Бишкек</t>
-        </is>
-      </c>
-      <c r="B15" s="23" t="n"/>
-      <c r="C15" s="23" t="n"/>
-      <c r="D15" s="23" t="n"/>
-      <c r="E15" s="24" t="n">
-        <v>1</v>
-      </c>
-      <c r="F15" s="25" t="n">
-        <v>1900000</v>
-      </c>
-      <c r="G15" s="25" t="n">
-        <v>180850</v>
-      </c>
-      <c r="H15" s="25" t="n">
-        <v>150000</v>
-      </c>
-      <c r="I15" s="25" t="n">
-        <v>28500</v>
-      </c>
-      <c r="J15" s="25" t="n">
-        <v>2350</v>
-      </c>
-      <c r="K15" s="26" t="n"/>
-      <c r="L15" s="27" t="n"/>
+      <c r="A15" s="28" t="inlineStr">
+        <is>
+          <t>Кеминский р-н</t>
+        </is>
+      </c>
+      <c r="B15" s="29" t="n"/>
+      <c r="C15" s="29" t="n"/>
+      <c r="D15" s="29" t="n"/>
+      <c r="E15" s="30" t="n">
+        <v>3</v>
+      </c>
+      <c r="F15" s="31" t="n">
+        <v>15500000</v>
+      </c>
+      <c r="G15" s="31" t="n">
+        <v>2934500</v>
+      </c>
+      <c r="H15" s="31" t="n">
+        <v>2150000</v>
+      </c>
+      <c r="I15" s="31" t="n">
+        <v>692250</v>
+      </c>
+      <c r="J15" s="31" t="n">
+        <v>92250</v>
+      </c>
+      <c r="K15" s="32" t="n"/>
+      <c r="L15" s="33" t="n"/>
     </row>
     <row r="16" ht="13" customHeight="1">
-      <c r="A16" s="28" t="inlineStr">
-        <is>
-          <t>г. Бишкек</t>
-        </is>
-      </c>
-      <c r="B16" s="29" t="n"/>
-      <c r="C16" s="29" t="n"/>
-      <c r="D16" s="29" t="n"/>
-      <c r="E16" s="30" t="n">
-        <v>1</v>
-      </c>
-      <c r="F16" s="31" t="n">
-        <v>1900000</v>
-      </c>
-      <c r="G16" s="31" t="n">
-        <v>180850</v>
-      </c>
-      <c r="H16" s="31" t="n">
-        <v>150000</v>
-      </c>
-      <c r="I16" s="31" t="n">
-        <v>28500</v>
-      </c>
-      <c r="J16" s="31" t="n">
-        <v>2350</v>
-      </c>
-      <c r="K16" s="32" t="n"/>
-      <c r="L16" s="33" t="n"/>
-    </row>
-    <row r="17" ht="13" customHeight="1">
-      <c r="A17" s="34" t="inlineStr">
-        <is>
-          <t>ОсОО «Тянь-Шань Строй»</t>
-        </is>
-      </c>
-      <c r="B17" s="35" t="inlineStr">
+      <c r="A16" s="34" t="inlineStr">
+        <is>
+          <t>ОсОО «Кемин-Курулуш»</t>
+        </is>
+      </c>
+      <c r="B16" s="35" t="inlineStr">
+        <is>
+          <t>высокий</t>
+        </is>
+      </c>
+      <c r="C16" s="35" t="inlineStr">
+        <is>
+          <t>2.1</t>
+        </is>
+      </c>
+      <c r="D16" s="35" t="n"/>
+      <c r="E16" s="36" t="n">
+        <v>3</v>
+      </c>
+      <c r="F16" s="37" t="n">
+        <v>15500000</v>
+      </c>
+      <c r="G16" s="37" t="n">
+        <v>2934500</v>
+      </c>
+      <c r="H16" s="37" t="n">
+        <v>2150000</v>
+      </c>
+      <c r="I16" s="37" t="n">
+        <v>692250</v>
+      </c>
+      <c r="J16" s="37" t="n">
+        <v>92250</v>
+      </c>
+      <c r="K16" s="36" t="n">
+        <v>190</v>
+      </c>
+      <c r="L16" s="38" t="n"/>
+    </row>
+    <row r="17" ht="24" customHeight="1">
+      <c r="A17" s="39" t="inlineStr">
+        <is>
+          <t>№ 19-3/061 от 11.04.2019</t>
+        </is>
+      </c>
+      <c r="B17" s="40" t="inlineStr">
+        <is>
+          <t>высокий</t>
+        </is>
+      </c>
+      <c r="C17" s="40" t="inlineStr">
+        <is>
+          <t>2.1</t>
+        </is>
+      </c>
+      <c r="D17" s="40" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="E17" s="41" t="n"/>
+      <c r="F17" s="42" t="n">
+        <v>10500000</v>
+      </c>
+      <c r="G17" s="42" t="n">
+        <v>2380000</v>
+      </c>
+      <c r="H17" s="42" t="n">
+        <v>1750000</v>
+      </c>
+      <c r="I17" s="42" t="n">
+        <v>551250</v>
+      </c>
+      <c r="J17" s="42" t="n">
+        <v>78750</v>
+      </c>
+      <c r="K17" s="43" t="n">
+        <v>190</v>
+      </c>
+      <c r="L17" s="44" t="inlineStr">
+        <is>
+          <t>Извещение о внесудебном обращении взыскания на залог, 21.09.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="13" customHeight="1">
+      <c r="A18" s="45" t="inlineStr">
+        <is>
+          <t>в USD (курс 87,50000)</t>
+        </is>
+      </c>
+      <c r="B18" s="46" t="n"/>
+      <c r="C18" s="46" t="n"/>
+      <c r="D18" s="46" t="n"/>
+      <c r="E18" s="47" t="n"/>
+      <c r="F18" s="48" t="n">
+        <v>120000</v>
+      </c>
+      <c r="G18" s="48" t="n">
+        <v>27200</v>
+      </c>
+      <c r="H18" s="48" t="n">
+        <v>20000</v>
+      </c>
+      <c r="I18" s="48" t="n">
+        <v>6300</v>
+      </c>
+      <c r="J18" s="48" t="n">
+        <v>900</v>
+      </c>
+      <c r="K18" s="47" t="n"/>
+      <c r="L18" s="49" t="n"/>
+    </row>
+    <row r="19" ht="13" customHeight="1">
+      <c r="A19" s="39" t="inlineStr">
+        <is>
+          <t>№ 22-3/014 от 18.03.2022</t>
+        </is>
+      </c>
+      <c r="B19" s="40" t="inlineStr">
         <is>
           <t>средний</t>
         </is>
       </c>
-      <c r="C17" s="35" t="inlineStr">
-        <is>
-          <t>1.2</t>
-        </is>
-      </c>
-      <c r="D17" s="35" t="n"/>
-      <c r="E17" s="36" t="n">
-        <v>1</v>
-      </c>
-      <c r="F17" s="37" t="n">
-        <v>1900000</v>
-      </c>
-      <c r="G17" s="37" t="n">
-        <v>180850</v>
-      </c>
-      <c r="H17" s="37" t="n">
-        <v>150000</v>
-      </c>
-      <c r="I17" s="37" t="n">
-        <v>28500</v>
-      </c>
-      <c r="J17" s="37" t="n">
-        <v>2350</v>
-      </c>
-      <c r="K17" s="36" t="n">
-        <v>20</v>
-      </c>
-      <c r="L17" s="38" t="n"/>
-    </row>
-    <row r="18" ht="13" customHeight="1">
-      <c r="A18" s="39" t="inlineStr">
-        <is>
-          <t>№ 22-1/045 от 03.02.2022</t>
-        </is>
-      </c>
-      <c r="B18" s="40" t="inlineStr">
+      <c r="C19" s="40" t="inlineStr">
+        <is>
+          <t>2.1</t>
+        </is>
+      </c>
+      <c r="D19" s="40" t="inlineStr">
+        <is>
+          <t>KGS</t>
+        </is>
+      </c>
+      <c r="E19" s="41" t="n"/>
+      <c r="F19" s="42" t="n">
+        <v>3200000</v>
+      </c>
+      <c r="G19" s="42" t="n">
+        <v>508400</v>
+      </c>
+      <c r="H19" s="42" t="n">
+        <v>400000</v>
+      </c>
+      <c r="I19" s="42" t="n">
+        <v>96000</v>
+      </c>
+      <c r="J19" s="42" t="n">
+        <v>12400</v>
+      </c>
+      <c r="K19" s="43" t="n">
+        <v>120</v>
+      </c>
+      <c r="L19" s="44" t="inlineStr">
+        <is>
+          <t>Повторная претензия, 14.09.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="13" customHeight="1">
+      <c r="A20" s="39" t="inlineStr">
+        <is>
+          <t>№ 24-3/105 от 02.12.2024</t>
+        </is>
+      </c>
+      <c r="B20" s="40" t="inlineStr">
         <is>
           <t>средний</t>
         </is>
       </c>
-      <c r="C18" s="40" t="inlineStr">
-        <is>
-          <t>1.2</t>
-        </is>
-      </c>
-      <c r="D18" s="40" t="inlineStr">
+      <c r="C20" s="40" t="inlineStr">
+        <is>
+          <t>2.1</t>
+        </is>
+      </c>
+      <c r="D20" s="40" t="inlineStr">
         <is>
           <t>KGS</t>
         </is>
       </c>
-      <c r="E18" s="41" t="n"/>
-      <c r="F18" s="42" t="n">
-        <v>1900000</v>
-      </c>
-      <c r="G18" s="42" t="n">
-        <v>180850</v>
-      </c>
-      <c r="H18" s="42" t="n">
-        <v>150000</v>
-      </c>
-      <c r="I18" s="42" t="n">
-        <v>28500</v>
-      </c>
-      <c r="J18" s="42" t="n">
-        <v>2350</v>
-      </c>
-      <c r="K18" s="43" t="n">
-        <v>20</v>
-      </c>
-      <c r="L18" s="44" t="inlineStr">
-        <is>
-          <t>Первичная претензия, 25.09.2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="13" customHeight="1">
-      <c r="A19" s="11" t="inlineStr">
-        <is>
-          <t>Департамент регионального развития</t>
-        </is>
-      </c>
-      <c r="B19" s="12" t="n"/>
-      <c r="C19" s="12" t="n"/>
-      <c r="D19" s="12" t="n"/>
-      <c r="E19" s="13" t="n">
-        <v>5</v>
-      </c>
-      <c r="F19" s="14" t="n">
-        <v>10620000</v>
-      </c>
-      <c r="G19" s="14" t="n">
-        <v>4230500</v>
-      </c>
-      <c r="H19" s="14" t="n">
-        <v>2940000</v>
-      </c>
-      <c r="I19" s="14" t="n">
-        <v>1015500</v>
-      </c>
-      <c r="J19" s="14" t="n">
-        <v>275000</v>
-      </c>
-      <c r="K19" s="15" t="n"/>
-      <c r="L19" s="11" t="n"/>
-    </row>
-    <row r="20" ht="13" customHeight="1">
-      <c r="A20" s="16" t="inlineStr">
-        <is>
-          <t>Отдел развития регионов</t>
-        </is>
-      </c>
-      <c r="B20" s="17" t="n"/>
-      <c r="C20" s="17" t="n"/>
-      <c r="D20" s="17" t="n"/>
-      <c r="E20" s="18" t="n">
-        <v>2</v>
-      </c>
-      <c r="F20" s="19" t="n">
-        <v>5800000</v>
-      </c>
-      <c r="G20" s="19" t="n">
-        <v>2281500</v>
-      </c>
-      <c r="H20" s="19" t="n">
-        <v>1600000</v>
-      </c>
-      <c r="I20" s="19" t="n">
-        <v>530000</v>
-      </c>
-      <c r="J20" s="19" t="n">
-        <v>151500</v>
-      </c>
-      <c r="K20" s="20" t="n"/>
-      <c r="L20" s="21" t="n"/>
+      <c r="E20" s="41" t="n"/>
+      <c r="F20" s="42" t="n">
+        <v>1800000</v>
+      </c>
+      <c r="G20" s="42" t="n">
+        <v>46100</v>
+      </c>
+      <c r="H20" s="42" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" s="42" t="n">
+        <v>45000</v>
+      </c>
+      <c r="J20" s="42" t="n">
+        <v>1100</v>
+      </c>
+      <c r="K20" s="43" t="n">
+        <v>35</v>
+      </c>
+      <c r="L20" s="44" t="inlineStr">
+        <is>
+          <t>Первичная претензия, 14.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="13" customHeight="1">
       <c r="A21" s="22" t="inlineStr">
         <is>
-          <t>Нарынская обл.</t>
+          <t>г. Бишкек</t>
         </is>
       </c>
       <c r="B21" s="23" t="n"/>
@@ -1288,19 +1334,19 @@
         <v>1</v>
       </c>
       <c r="F21" s="25" t="n">
-        <v>2200000</v>
+        <v>1900000</v>
       </c>
       <c r="G21" s="25" t="n">
-        <v>551000</v>
+        <v>180850</v>
       </c>
       <c r="H21" s="25" t="n">
-        <v>400000</v>
+        <v>150000</v>
       </c>
       <c r="I21" s="25" t="n">
-        <v>120000</v>
+        <v>28500</v>
       </c>
       <c r="J21" s="25" t="n">
-        <v>31000</v>
+        <v>2350</v>
       </c>
       <c r="K21" s="26" t="n"/>
       <c r="L21" s="27" t="n"/>
@@ -1308,7 +1354,7 @@
     <row r="22" ht="13" customHeight="1">
       <c r="A22" s="28" t="inlineStr">
         <is>
-          <t>г. Нарын</t>
+          <t>г. Бишкек</t>
         </is>
       </c>
       <c r="B22" s="29" t="n"/>
@@ -1318,19 +1364,19 @@
         <v>1</v>
       </c>
       <c r="F22" s="31" t="n">
-        <v>2200000</v>
+        <v>1900000</v>
       </c>
       <c r="G22" s="31" t="n">
-        <v>551000</v>
+        <v>180850</v>
       </c>
       <c r="H22" s="31" t="n">
-        <v>400000</v>
+        <v>150000</v>
       </c>
       <c r="I22" s="31" t="n">
-        <v>120000</v>
+        <v>28500</v>
       </c>
       <c r="J22" s="31" t="n">
-        <v>31000</v>
+        <v>2350</v>
       </c>
       <c r="K22" s="32" t="n"/>
       <c r="L22" s="33" t="n"/>
@@ -1338,17 +1384,17 @@
     <row r="23" ht="13" customHeight="1">
       <c r="A23" s="34" t="inlineStr">
         <is>
-          <t>ОсОО «Нарын-Сүт»</t>
+          <t>ОсОО «Тянь-Шань Строй»</t>
         </is>
       </c>
       <c r="B23" s="35" t="inlineStr">
         <is>
-          <t>высокий</t>
+          <t>средний</t>
         </is>
       </c>
       <c r="C23" s="35" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="D23" s="35" t="n"/>
@@ -1356,39 +1402,39 @@
         <v>1</v>
       </c>
       <c r="F23" s="37" t="n">
-        <v>2200000</v>
+        <v>1900000</v>
       </c>
       <c r="G23" s="37" t="n">
-        <v>551000</v>
+        <v>180850</v>
       </c>
       <c r="H23" s="37" t="n">
-        <v>400000</v>
+        <v>150000</v>
       </c>
       <c r="I23" s="37" t="n">
-        <v>120000</v>
+        <v>28500</v>
       </c>
       <c r="J23" s="37" t="n">
-        <v>31000</v>
+        <v>2350</v>
       </c>
       <c r="K23" s="36" t="n">
-        <v>190</v>
+        <v>20</v>
       </c>
       <c r="L23" s="38" t="n"/>
     </row>
     <row r="24" ht="13" customHeight="1">
       <c r="A24" s="39" t="inlineStr">
         <is>
-          <t>№ 23-5/071 от 09.08.2023</t>
+          <t>№ 22-1/045 от 03.02.2022</t>
         </is>
       </c>
       <c r="B24" s="40" t="inlineStr">
         <is>
-          <t>высокий</t>
+          <t>средний</t>
         </is>
       </c>
       <c r="C24" s="40" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="D24" s="40" t="inlineStr">
@@ -1398,33 +1444,33 @@
       </c>
       <c r="E24" s="41" t="n"/>
       <c r="F24" s="42" t="n">
-        <v>2200000</v>
+        <v>1900000</v>
       </c>
       <c r="G24" s="42" t="n">
-        <v>551000</v>
+        <v>180850</v>
       </c>
       <c r="H24" s="42" t="n">
-        <v>400000</v>
+        <v>150000</v>
       </c>
       <c r="I24" s="42" t="n">
-        <v>120000</v>
+        <v>28500</v>
       </c>
       <c r="J24" s="42" t="n">
-        <v>31000</v>
+        <v>2350</v>
       </c>
       <c r="K24" s="43" t="n">
-        <v>190</v>
+        <v>20</v>
       </c>
       <c r="L24" s="44" t="inlineStr">
         <is>
-          <t>мер нет</t>
+          <t>Первичная претензия, 25.09.2026</t>
         </is>
       </c>
     </row>
     <row r="25" ht="13" customHeight="1">
       <c r="A25" s="22" t="inlineStr">
         <is>
-          <t>Ошская обл.</t>
+          <t>г. Ош</t>
         </is>
       </c>
       <c r="B25" s="23" t="n"/>
@@ -1434,19 +1480,19 @@
         <v>1</v>
       </c>
       <c r="F25" s="25" t="n">
-        <v>3600000</v>
+        <v>4872000</v>
       </c>
       <c r="G25" s="25" t="n">
-        <v>1730500</v>
+        <v>1061690</v>
       </c>
       <c r="H25" s="25" t="n">
-        <v>1200000</v>
+        <v>812000</v>
       </c>
       <c r="I25" s="25" t="n">
-        <v>410000</v>
+        <v>219240</v>
       </c>
       <c r="J25" s="25" t="n">
-        <v>120500</v>
+        <v>30450</v>
       </c>
       <c r="K25" s="26" t="n"/>
       <c r="L25" s="27" t="n"/>
@@ -1454,7 +1500,7 @@
     <row r="26" ht="13" customHeight="1">
       <c r="A26" s="28" t="inlineStr">
         <is>
-          <t>Кара-Суйский р-н</t>
+          <t>г. Ош</t>
         </is>
       </c>
       <c r="B26" s="29" t="n"/>
@@ -1464,19 +1510,19 @@
         <v>1</v>
       </c>
       <c r="F26" s="31" t="n">
-        <v>3600000</v>
+        <v>4872000</v>
       </c>
       <c r="G26" s="31" t="n">
-        <v>1730500</v>
+        <v>1061690</v>
       </c>
       <c r="H26" s="31" t="n">
-        <v>1200000</v>
+        <v>812000</v>
       </c>
       <c r="I26" s="31" t="n">
-        <v>410000</v>
+        <v>219240</v>
       </c>
       <c r="J26" s="31" t="n">
-        <v>120500</v>
+        <v>30450</v>
       </c>
       <c r="K26" s="32" t="n"/>
       <c r="L26" s="33" t="n"/>
@@ -1484,12 +1530,12 @@
     <row r="27" ht="13" customHeight="1">
       <c r="A27" s="34" t="inlineStr">
         <is>
-          <t>ОсОО «Ош-Текстиль»</t>
+          <t>ОсОО «Сулайман-Тоо Трейд»</t>
         </is>
       </c>
       <c r="B27" s="35" t="inlineStr">
         <is>
-          <t>высокий</t>
+          <t>средний</t>
         </is>
       </c>
       <c r="C27" s="35" t="inlineStr">
@@ -1502,34 +1548,34 @@
         <v>1</v>
       </c>
       <c r="F27" s="37" t="n">
-        <v>3600000</v>
+        <v>4872000</v>
       </c>
       <c r="G27" s="37" t="n">
-        <v>1730500</v>
+        <v>1061690</v>
       </c>
       <c r="H27" s="37" t="n">
-        <v>1200000</v>
+        <v>812000</v>
       </c>
       <c r="I27" s="37" t="n">
-        <v>410000</v>
+        <v>219240</v>
       </c>
       <c r="J27" s="37" t="n">
-        <v>120500</v>
+        <v>30450</v>
       </c>
       <c r="K27" s="36" t="n">
-        <v>212</v>
+        <v>62</v>
       </c>
       <c r="L27" s="38" t="n"/>
     </row>
-    <row r="28" ht="24" customHeight="1">
+    <row r="28" ht="13" customHeight="1">
       <c r="A28" s="39" t="inlineStr">
         <is>
-          <t>№ 21-5/203 от 09.09.2021</t>
+          <t>№ 21-1/207 от 15.11.2021</t>
         </is>
       </c>
       <c r="B28" s="40" t="inlineStr">
         <is>
-          <t>высокий</t>
+          <t>средний</t>
         </is>
       </c>
       <c r="C28" s="40" t="inlineStr">
@@ -1539,360 +1585,330 @@
       </c>
       <c r="D28" s="40" t="inlineStr">
         <is>
-          <t>KGS</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="E28" s="41" t="n"/>
       <c r="F28" s="42" t="n">
-        <v>3600000</v>
+        <v>4872000</v>
       </c>
       <c r="G28" s="42" t="n">
-        <v>1730500</v>
+        <v>1061690</v>
       </c>
       <c r="H28" s="42" t="n">
-        <v>1200000</v>
+        <v>812000</v>
       </c>
       <c r="I28" s="42" t="n">
-        <v>410000</v>
+        <v>219240</v>
       </c>
       <c r="J28" s="42" t="n">
-        <v>120500</v>
+        <v>30450</v>
       </c>
       <c r="K28" s="43" t="n">
-        <v>212</v>
+        <v>62</v>
       </c>
       <c r="L28" s="44" t="inlineStr">
         <is>
-          <t>Извещение о внесудебном обращении взыскания на залог, 14.07.2026</t>
+          <t>Первичная претензия, 08.09.2026</t>
         </is>
       </c>
     </row>
     <row r="29" ht="13" customHeight="1">
-      <c r="A29" s="16" t="inlineStr">
-        <is>
-          <t>Отдел развития АПК</t>
-        </is>
-      </c>
-      <c r="B29" s="17" t="n"/>
-      <c r="C29" s="17" t="n"/>
-      <c r="D29" s="17" t="n"/>
-      <c r="E29" s="18" t="n">
+      <c r="A29" s="45" t="inlineStr">
+        <is>
+          <t>в EUR (курс 101,50000)</t>
+        </is>
+      </c>
+      <c r="B29" s="46" t="n"/>
+      <c r="C29" s="46" t="n"/>
+      <c r="D29" s="46" t="n"/>
+      <c r="E29" s="47" t="n"/>
+      <c r="F29" s="48" t="n">
+        <v>48000</v>
+      </c>
+      <c r="G29" s="48" t="n">
+        <v>10460</v>
+      </c>
+      <c r="H29" s="48" t="n">
+        <v>8000</v>
+      </c>
+      <c r="I29" s="48" t="n">
+        <v>2160</v>
+      </c>
+      <c r="J29" s="48" t="n">
+        <v>300</v>
+      </c>
+      <c r="K29" s="47" t="n"/>
+      <c r="L29" s="49" t="n"/>
+    </row>
+    <row r="30" ht="13" customHeight="1">
+      <c r="A30" s="11" t="inlineStr">
+        <is>
+          <t>Департамент регионального развития</t>
+        </is>
+      </c>
+      <c r="B30" s="12" t="n"/>
+      <c r="C30" s="12" t="n"/>
+      <c r="D30" s="12" t="n"/>
+      <c r="E30" s="13" t="n">
+        <v>6</v>
+      </c>
+      <c r="F30" s="14" t="n">
+        <v>18495000</v>
+      </c>
+      <c r="G30" s="14" t="n">
+        <v>6002375</v>
+      </c>
+      <c r="H30" s="14" t="n">
+        <v>4252500</v>
+      </c>
+      <c r="I30" s="14" t="n">
+        <v>1369875</v>
+      </c>
+      <c r="J30" s="14" t="n">
+        <v>380000</v>
+      </c>
+      <c r="K30" s="15" t="n"/>
+      <c r="L30" s="11" t="n"/>
+    </row>
+    <row r="31" ht="13" customHeight="1">
+      <c r="A31" s="16" t="inlineStr">
+        <is>
+          <t>Отдел развития регионов</t>
+        </is>
+      </c>
+      <c r="B31" s="17" t="n"/>
+      <c r="C31" s="17" t="n"/>
+      <c r="D31" s="17" t="n"/>
+      <c r="E31" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="F29" s="19" t="n">
-        <v>4820000</v>
-      </c>
-      <c r="G29" s="19" t="n">
-        <v>1949000</v>
-      </c>
-      <c r="H29" s="19" t="n">
-        <v>1340000</v>
-      </c>
-      <c r="I29" s="19" t="n">
-        <v>485500</v>
-      </c>
-      <c r="J29" s="19" t="n">
-        <v>123500</v>
-      </c>
-      <c r="K29" s="20" t="n"/>
-      <c r="L29" s="21" t="n"/>
-    </row>
-    <row r="30" ht="13" customHeight="1">
-      <c r="A30" s="22" t="inlineStr">
+      <c r="F31" s="19" t="n">
+        <v>13675000</v>
+      </c>
+      <c r="G31" s="19" t="n">
+        <v>4053375</v>
+      </c>
+      <c r="H31" s="19" t="n">
+        <v>2912500</v>
+      </c>
+      <c r="I31" s="19" t="n">
+        <v>884375</v>
+      </c>
+      <c r="J31" s="19" t="n">
+        <v>256500</v>
+      </c>
+      <c r="K31" s="20" t="n"/>
+      <c r="L31" s="21" t="n"/>
+    </row>
+    <row r="32" ht="13" customHeight="1">
+      <c r="A32" s="22" t="inlineStr">
+        <is>
+          <t>Джалал-Абадская обл.</t>
+        </is>
+      </c>
+      <c r="B32" s="23" t="n"/>
+      <c r="C32" s="23" t="n"/>
+      <c r="D32" s="23" t="n"/>
+      <c r="E32" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="F32" s="25" t="n">
+        <v>7875000</v>
+      </c>
+      <c r="G32" s="25" t="n">
+        <v>1771875</v>
+      </c>
+      <c r="H32" s="25" t="n">
+        <v>1312500</v>
+      </c>
+      <c r="I32" s="25" t="n">
+        <v>354375</v>
+      </c>
+      <c r="J32" s="25" t="n">
+        <v>105000</v>
+      </c>
+      <c r="K32" s="26" t="n"/>
+      <c r="L32" s="27" t="n"/>
+    </row>
+    <row r="33" ht="13" customHeight="1">
+      <c r="A33" s="28" t="inlineStr">
+        <is>
+          <t>Ноокенский р-н</t>
+        </is>
+      </c>
+      <c r="B33" s="29" t="n"/>
+      <c r="C33" s="29" t="n"/>
+      <c r="D33" s="29" t="n"/>
+      <c r="E33" s="30" t="n">
+        <v>1</v>
+      </c>
+      <c r="F33" s="31" t="n">
+        <v>7875000</v>
+      </c>
+      <c r="G33" s="31" t="n">
+        <v>1771875</v>
+      </c>
+      <c r="H33" s="31" t="n">
+        <v>1312500</v>
+      </c>
+      <c r="I33" s="31" t="n">
+        <v>354375</v>
+      </c>
+      <c r="J33" s="31" t="n">
+        <v>105000</v>
+      </c>
+      <c r="K33" s="32" t="n"/>
+      <c r="L33" s="33" t="n"/>
+    </row>
+    <row r="34" ht="13" customHeight="1">
+      <c r="A34" s="34" t="inlineStr">
+        <is>
+          <t>ОсОО «Кербен-Жибек»</t>
+        </is>
+      </c>
+      <c r="B34" s="35" t="inlineStr">
+        <is>
+          <t>высокий</t>
+        </is>
+      </c>
+      <c r="C34" s="35" t="inlineStr">
+        <is>
+          <t>2.2</t>
+        </is>
+      </c>
+      <c r="D34" s="35" t="n"/>
+      <c r="E34" s="36" t="n">
+        <v>1</v>
+      </c>
+      <c r="F34" s="37" t="n">
+        <v>7875000</v>
+      </c>
+      <c r="G34" s="37" t="n">
+        <v>1771875</v>
+      </c>
+      <c r="H34" s="37" t="n">
+        <v>1312500</v>
+      </c>
+      <c r="I34" s="37" t="n">
+        <v>354375</v>
+      </c>
+      <c r="J34" s="37" t="n">
+        <v>105000</v>
+      </c>
+      <c r="K34" s="36" t="n">
+        <v>245</v>
+      </c>
+      <c r="L34" s="38" t="n"/>
+    </row>
+    <row r="35" ht="24" customHeight="1">
+      <c r="A35" s="39" t="inlineStr">
+        <is>
+          <t>№ 20-5/118 от 23.06.2020</t>
+        </is>
+      </c>
+      <c r="B35" s="40" t="inlineStr">
+        <is>
+          <t>высокий</t>
+        </is>
+      </c>
+      <c r="C35" s="40" t="inlineStr">
+        <is>
+          <t>2.2</t>
+        </is>
+      </c>
+      <c r="D35" s="40" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="E35" s="41" t="n"/>
+      <c r="F35" s="42" t="n">
+        <v>7875000</v>
+      </c>
+      <c r="G35" s="42" t="n">
+        <v>1771875</v>
+      </c>
+      <c r="H35" s="42" t="n">
+        <v>1312500</v>
+      </c>
+      <c r="I35" s="42" t="n">
+        <v>354375</v>
+      </c>
+      <c r="J35" s="42" t="n">
+        <v>105000</v>
+      </c>
+      <c r="K35" s="43" t="n">
+        <v>245</v>
+      </c>
+      <c r="L35" s="44" t="inlineStr">
+        <is>
+          <t>Исковое заявление в суд, 03.09.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="13" customHeight="1">
+      <c r="A36" s="45" t="inlineStr">
+        <is>
+          <t>в USD (курс 87,50000)</t>
+        </is>
+      </c>
+      <c r="B36" s="46" t="n"/>
+      <c r="C36" s="46" t="n"/>
+      <c r="D36" s="46" t="n"/>
+      <c r="E36" s="47" t="n"/>
+      <c r="F36" s="48" t="n">
+        <v>90000</v>
+      </c>
+      <c r="G36" s="48" t="n">
+        <v>20250</v>
+      </c>
+      <c r="H36" s="48" t="n">
+        <v>15000</v>
+      </c>
+      <c r="I36" s="48" t="n">
+        <v>4050</v>
+      </c>
+      <c r="J36" s="48" t="n">
+        <v>1200</v>
+      </c>
+      <c r="K36" s="47" t="n"/>
+      <c r="L36" s="49" t="n"/>
+    </row>
+    <row r="37" ht="13" customHeight="1">
+      <c r="A37" s="22" t="inlineStr">
         <is>
           <t>Нарынская обл.</t>
         </is>
       </c>
-      <c r="B30" s="23" t="n"/>
-      <c r="C30" s="23" t="n"/>
-      <c r="D30" s="23" t="n"/>
-      <c r="E30" s="24" t="n">
+      <c r="B37" s="23" t="n"/>
+      <c r="C37" s="23" t="n"/>
+      <c r="D37" s="23" t="n"/>
+      <c r="E37" s="24" t="n">
         <v>1</v>
       </c>
-      <c r="F30" s="25" t="n">
-        <v>2100000</v>
-      </c>
-      <c r="G30" s="25" t="n">
-        <v>1024300</v>
-      </c>
-      <c r="H30" s="25" t="n">
-        <v>700000</v>
-      </c>
-      <c r="I30" s="25" t="n">
-        <v>260000</v>
-      </c>
-      <c r="J30" s="25" t="n">
-        <v>64300</v>
-      </c>
-      <c r="K30" s="26" t="n"/>
-      <c r="L30" s="27" t="n"/>
-    </row>
-    <row r="31" ht="13" customHeight="1">
-      <c r="A31" s="28" t="inlineStr">
-        <is>
-          <t>Кочкорский р-н</t>
-        </is>
-      </c>
-      <c r="B31" s="29" t="n"/>
-      <c r="C31" s="29" t="n"/>
-      <c r="D31" s="29" t="n"/>
-      <c r="E31" s="30" t="n">
-        <v>1</v>
-      </c>
-      <c r="F31" s="31" t="n">
-        <v>2100000</v>
-      </c>
-      <c r="G31" s="31" t="n">
-        <v>1024300</v>
-      </c>
-      <c r="H31" s="31" t="n">
-        <v>700000</v>
-      </c>
-      <c r="I31" s="31" t="n">
-        <v>260000</v>
-      </c>
-      <c r="J31" s="31" t="n">
-        <v>64300</v>
-      </c>
-      <c r="K31" s="32" t="n"/>
-      <c r="L31" s="33" t="n"/>
-    </row>
-    <row r="32" ht="13" customHeight="1">
-      <c r="A32" s="34" t="inlineStr">
-        <is>
-          <t>ОсОО «Нарын-Агро»</t>
-        </is>
-      </c>
-      <c r="B32" s="35" t="inlineStr">
-        <is>
-          <t>высокий</t>
-        </is>
-      </c>
-      <c r="C32" s="35" t="inlineStr">
-        <is>
-          <t>2.1</t>
-        </is>
-      </c>
-      <c r="D32" s="35" t="n"/>
-      <c r="E32" s="36" t="n">
-        <v>1</v>
-      </c>
-      <c r="F32" s="37" t="n">
-        <v>2100000</v>
-      </c>
-      <c r="G32" s="37" t="n">
-        <v>1024300</v>
-      </c>
-      <c r="H32" s="37" t="n">
-        <v>700000</v>
-      </c>
-      <c r="I32" s="37" t="n">
-        <v>260000</v>
-      </c>
-      <c r="J32" s="37" t="n">
-        <v>64300</v>
-      </c>
-      <c r="K32" s="36" t="n">
-        <v>409</v>
-      </c>
-      <c r="L32" s="38" t="n"/>
-    </row>
-    <row r="33" ht="24" customHeight="1">
-      <c r="A33" s="39" t="inlineStr">
-        <is>
-          <t>№ 21-2/077 от 18.05.2021</t>
-        </is>
-      </c>
-      <c r="B33" s="40" t="inlineStr">
-        <is>
-          <t>высокий</t>
-        </is>
-      </c>
-      <c r="C33" s="40" t="inlineStr">
-        <is>
-          <t>2.1</t>
-        </is>
-      </c>
-      <c r="D33" s="40" t="inlineStr">
-        <is>
-          <t>KGS</t>
-        </is>
-      </c>
-      <c r="E33" s="41" t="n"/>
-      <c r="F33" s="42" t="n">
-        <v>2100000</v>
-      </c>
-      <c r="G33" s="42" t="n">
-        <v>1024300</v>
-      </c>
-      <c r="H33" s="42" t="n">
-        <v>700000</v>
-      </c>
-      <c r="I33" s="42" t="n">
-        <v>260000</v>
-      </c>
-      <c r="J33" s="42" t="n">
-        <v>64300</v>
-      </c>
-      <c r="K33" s="43" t="n">
-        <v>409</v>
-      </c>
-      <c r="L33" s="44" t="inlineStr">
-        <is>
-          <t>Соглашение о добровольном исполнении № 3, 10.09.2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="13" customHeight="1">
-      <c r="A34" s="22" t="inlineStr">
-        <is>
-          <t>Таласская обл.</t>
-        </is>
-      </c>
-      <c r="B34" s="23" t="n"/>
-      <c r="C34" s="23" t="n"/>
-      <c r="D34" s="23" t="n"/>
-      <c r="E34" s="24" t="n">
-        <v>2</v>
-      </c>
-      <c r="F34" s="25" t="n">
-        <v>2720000</v>
-      </c>
-      <c r="G34" s="25" t="n">
-        <v>924700</v>
-      </c>
-      <c r="H34" s="25" t="n">
-        <v>640000</v>
-      </c>
-      <c r="I34" s="25" t="n">
-        <v>225500</v>
-      </c>
-      <c r="J34" s="25" t="n">
-        <v>59200</v>
-      </c>
-      <c r="K34" s="26" t="n"/>
-      <c r="L34" s="27" t="n"/>
-    </row>
-    <row r="35" ht="13" customHeight="1">
-      <c r="A35" s="28" t="inlineStr">
-        <is>
-          <t>Бакай-Атинский р-н</t>
-        </is>
-      </c>
-      <c r="B35" s="29" t="n"/>
-      <c r="C35" s="29" t="n"/>
-      <c r="D35" s="29" t="n"/>
-      <c r="E35" s="30" t="n">
-        <v>1</v>
-      </c>
-      <c r="F35" s="31" t="n">
-        <v>420000</v>
-      </c>
-      <c r="G35" s="31" t="n">
-        <v>51700</v>
-      </c>
-      <c r="H35" s="31" t="n">
-        <v>40000</v>
-      </c>
-      <c r="I35" s="31" t="n">
-        <v>10500</v>
-      </c>
-      <c r="J35" s="31" t="n">
-        <v>1200</v>
-      </c>
-      <c r="K35" s="32" t="n"/>
-      <c r="L35" s="33" t="n"/>
-    </row>
-    <row r="36" ht="13" customHeight="1">
-      <c r="A36" s="34" t="inlineStr">
-        <is>
-          <t>Иманалиев Бакыт Тологонович</t>
-        </is>
-      </c>
-      <c r="B36" s="35" t="inlineStr">
-        <is>
-          <t>средний</t>
-        </is>
-      </c>
-      <c r="C36" s="35" t="inlineStr">
-        <is>
-          <t>1.2</t>
-        </is>
-      </c>
-      <c r="D36" s="35" t="n"/>
-      <c r="E36" s="36" t="n">
-        <v>1</v>
-      </c>
-      <c r="F36" s="37" t="n">
-        <v>420000</v>
-      </c>
-      <c r="G36" s="37" t="n">
-        <v>51700</v>
-      </c>
-      <c r="H36" s="37" t="n">
-        <v>40000</v>
-      </c>
-      <c r="I36" s="37" t="n">
-        <v>10500</v>
-      </c>
-      <c r="J36" s="37" t="n">
-        <v>1200</v>
-      </c>
-      <c r="K36" s="36" t="n">
-        <v>95</v>
-      </c>
-      <c r="L36" s="38" t="n"/>
-    </row>
-    <row r="37" ht="24" customHeight="1">
-      <c r="A37" s="39" t="inlineStr">
-        <is>
-          <t>№ 24-2/077 от 14.05.2024</t>
-        </is>
-      </c>
-      <c r="B37" s="40" t="inlineStr">
-        <is>
-          <t>средний</t>
-        </is>
-      </c>
-      <c r="C37" s="40" t="inlineStr">
-        <is>
-          <t>1.2</t>
-        </is>
-      </c>
-      <c r="D37" s="40" t="inlineStr">
-        <is>
-          <t>KGS</t>
-        </is>
-      </c>
-      <c r="E37" s="41" t="n"/>
-      <c r="F37" s="42" t="n">
-        <v>420000</v>
-      </c>
-      <c r="G37" s="42" t="n">
-        <v>51700</v>
-      </c>
-      <c r="H37" s="42" t="n">
-        <v>40000</v>
-      </c>
-      <c r="I37" s="42" t="n">
-        <v>10500</v>
-      </c>
-      <c r="J37" s="42" t="n">
-        <v>1200</v>
-      </c>
-      <c r="K37" s="43" t="n">
-        <v>95</v>
-      </c>
-      <c r="L37" s="44" t="inlineStr">
-        <is>
-          <t>Запросы нотариату, ЦОН и органу регистрации, 24.08.2026</t>
-        </is>
-      </c>
+      <c r="F37" s="25" t="n">
+        <v>2200000</v>
+      </c>
+      <c r="G37" s="25" t="n">
+        <v>551000</v>
+      </c>
+      <c r="H37" s="25" t="n">
+        <v>400000</v>
+      </c>
+      <c r="I37" s="25" t="n">
+        <v>120000</v>
+      </c>
+      <c r="J37" s="25" t="n">
+        <v>31000</v>
+      </c>
+      <c r="K37" s="26" t="n"/>
+      <c r="L37" s="27" t="n"/>
     </row>
     <row r="38" ht="13" customHeight="1">
       <c r="A38" s="28" t="inlineStr">
         <is>
-          <t>Таласский р-н</t>
+          <t>г. Нарын</t>
         </is>
       </c>
       <c r="B38" s="29" t="n"/>
@@ -1902,19 +1918,19 @@
         <v>1</v>
       </c>
       <c r="F38" s="31" t="n">
-        <v>2300000</v>
+        <v>2200000</v>
       </c>
       <c r="G38" s="31" t="n">
-        <v>873000</v>
+        <v>551000</v>
       </c>
       <c r="H38" s="31" t="n">
-        <v>600000</v>
+        <v>400000</v>
       </c>
       <c r="I38" s="31" t="n">
-        <v>215000</v>
+        <v>120000</v>
       </c>
       <c r="J38" s="31" t="n">
-        <v>58000</v>
+        <v>31000</v>
       </c>
       <c r="K38" s="32" t="n"/>
       <c r="L38" s="33" t="n"/>
@@ -1922,7 +1938,7 @@
     <row r="39" ht="13" customHeight="1">
       <c r="A39" s="34" t="inlineStr">
         <is>
-          <t>ОсОО «Талас-Бал»</t>
+          <t>ОсОО «Нарын-Сүт»</t>
         </is>
       </c>
       <c r="B39" s="35" t="inlineStr">
@@ -1932,7 +1948,7 @@
       </c>
       <c r="C39" s="35" t="inlineStr">
         <is>
-          <t>2.3</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="D39" s="35" t="n"/>
@@ -1940,29 +1956,29 @@
         <v>1</v>
       </c>
       <c r="F39" s="37" t="n">
-        <v>2300000</v>
+        <v>2200000</v>
       </c>
       <c r="G39" s="37" t="n">
-        <v>873000</v>
+        <v>551000</v>
       </c>
       <c r="H39" s="37" t="n">
-        <v>600000</v>
+        <v>400000</v>
       </c>
       <c r="I39" s="37" t="n">
-        <v>215000</v>
+        <v>120000</v>
       </c>
       <c r="J39" s="37" t="n">
-        <v>58000</v>
+        <v>31000</v>
       </c>
       <c r="K39" s="36" t="n">
-        <v>260</v>
+        <v>190</v>
       </c>
       <c r="L39" s="38" t="n"/>
     </row>
-    <row r="40" ht="35" customHeight="1">
+    <row r="40" ht="13" customHeight="1">
       <c r="A40" s="39" t="inlineStr">
         <is>
-          <t>№ 23-4/021 от 21.08.2023</t>
+          <t>№ 23-5/071 от 09.08.2023</t>
         </is>
       </c>
       <c r="B40" s="40" t="inlineStr">
@@ -1972,7 +1988,7 @@
       </c>
       <c r="C40" s="40" t="inlineStr">
         <is>
-          <t>2.3</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="D40" s="40" t="inlineStr">
@@ -1982,24 +1998,608 @@
       </c>
       <c r="E40" s="41" t="n"/>
       <c r="F40" s="42" t="n">
+        <v>2200000</v>
+      </c>
+      <c r="G40" s="42" t="n">
+        <v>551000</v>
+      </c>
+      <c r="H40" s="42" t="n">
+        <v>400000</v>
+      </c>
+      <c r="I40" s="42" t="n">
+        <v>120000</v>
+      </c>
+      <c r="J40" s="42" t="n">
+        <v>31000</v>
+      </c>
+      <c r="K40" s="43" t="n">
+        <v>190</v>
+      </c>
+      <c r="L40" s="44" t="inlineStr">
+        <is>
+          <t>мер нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="13" customHeight="1">
+      <c r="A41" s="22" t="inlineStr">
+        <is>
+          <t>Ошская обл.</t>
+        </is>
+      </c>
+      <c r="B41" s="23" t="n"/>
+      <c r="C41" s="23" t="n"/>
+      <c r="D41" s="23" t="n"/>
+      <c r="E41" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="F41" s="25" t="n">
+        <v>3600000</v>
+      </c>
+      <c r="G41" s="25" t="n">
+        <v>1730500</v>
+      </c>
+      <c r="H41" s="25" t="n">
+        <v>1200000</v>
+      </c>
+      <c r="I41" s="25" t="n">
+        <v>410000</v>
+      </c>
+      <c r="J41" s="25" t="n">
+        <v>120500</v>
+      </c>
+      <c r="K41" s="26" t="n"/>
+      <c r="L41" s="27" t="n"/>
+    </row>
+    <row r="42" ht="13" customHeight="1">
+      <c r="A42" s="28" t="inlineStr">
+        <is>
+          <t>Кара-Суйский р-н</t>
+        </is>
+      </c>
+      <c r="B42" s="29" t="n"/>
+      <c r="C42" s="29" t="n"/>
+      <c r="D42" s="29" t="n"/>
+      <c r="E42" s="30" t="n">
+        <v>1</v>
+      </c>
+      <c r="F42" s="31" t="n">
+        <v>3600000</v>
+      </c>
+      <c r="G42" s="31" t="n">
+        <v>1730500</v>
+      </c>
+      <c r="H42" s="31" t="n">
+        <v>1200000</v>
+      </c>
+      <c r="I42" s="31" t="n">
+        <v>410000</v>
+      </c>
+      <c r="J42" s="31" t="n">
+        <v>120500</v>
+      </c>
+      <c r="K42" s="32" t="n"/>
+      <c r="L42" s="33" t="n"/>
+    </row>
+    <row r="43" ht="13" customHeight="1">
+      <c r="A43" s="34" t="inlineStr">
+        <is>
+          <t>ОсОО «Ош-Текстиль»</t>
+        </is>
+      </c>
+      <c r="B43" s="35" t="inlineStr">
+        <is>
+          <t>высокий</t>
+        </is>
+      </c>
+      <c r="C43" s="35" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
+      <c r="D43" s="35" t="n"/>
+      <c r="E43" s="36" t="n">
+        <v>1</v>
+      </c>
+      <c r="F43" s="37" t="n">
+        <v>3600000</v>
+      </c>
+      <c r="G43" s="37" t="n">
+        <v>1730500</v>
+      </c>
+      <c r="H43" s="37" t="n">
+        <v>1200000</v>
+      </c>
+      <c r="I43" s="37" t="n">
+        <v>410000</v>
+      </c>
+      <c r="J43" s="37" t="n">
+        <v>120500</v>
+      </c>
+      <c r="K43" s="36" t="n">
+        <v>212</v>
+      </c>
+      <c r="L43" s="38" t="n"/>
+    </row>
+    <row r="44" ht="24" customHeight="1">
+      <c r="A44" s="39" t="inlineStr">
+        <is>
+          <t>№ 21-5/203 от 09.09.2021</t>
+        </is>
+      </c>
+      <c r="B44" s="40" t="inlineStr">
+        <is>
+          <t>высокий</t>
+        </is>
+      </c>
+      <c r="C44" s="40" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
+      <c r="D44" s="40" t="inlineStr">
+        <is>
+          <t>KGS</t>
+        </is>
+      </c>
+      <c r="E44" s="41" t="n"/>
+      <c r="F44" s="42" t="n">
+        <v>3600000</v>
+      </c>
+      <c r="G44" s="42" t="n">
+        <v>1730500</v>
+      </c>
+      <c r="H44" s="42" t="n">
+        <v>1200000</v>
+      </c>
+      <c r="I44" s="42" t="n">
+        <v>410000</v>
+      </c>
+      <c r="J44" s="42" t="n">
+        <v>120500</v>
+      </c>
+      <c r="K44" s="43" t="n">
+        <v>212</v>
+      </c>
+      <c r="L44" s="44" t="inlineStr">
+        <is>
+          <t>Извещение о внесудебном обращении взыскания на залог, 14.07.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="13" customHeight="1">
+      <c r="A45" s="16" t="inlineStr">
+        <is>
+          <t>Отдел развития АПК</t>
+        </is>
+      </c>
+      <c r="B45" s="17" t="n"/>
+      <c r="C45" s="17" t="n"/>
+      <c r="D45" s="17" t="n"/>
+      <c r="E45" s="18" t="n">
+        <v>3</v>
+      </c>
+      <c r="F45" s="19" t="n">
+        <v>4820000</v>
+      </c>
+      <c r="G45" s="19" t="n">
+        <v>1949000</v>
+      </c>
+      <c r="H45" s="19" t="n">
+        <v>1340000</v>
+      </c>
+      <c r="I45" s="19" t="n">
+        <v>485500</v>
+      </c>
+      <c r="J45" s="19" t="n">
+        <v>123500</v>
+      </c>
+      <c r="K45" s="20" t="n"/>
+      <c r="L45" s="21" t="n"/>
+    </row>
+    <row r="46" ht="13" customHeight="1">
+      <c r="A46" s="22" t="inlineStr">
+        <is>
+          <t>Нарынская обл.</t>
+        </is>
+      </c>
+      <c r="B46" s="23" t="n"/>
+      <c r="C46" s="23" t="n"/>
+      <c r="D46" s="23" t="n"/>
+      <c r="E46" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="F46" s="25" t="n">
+        <v>2100000</v>
+      </c>
+      <c r="G46" s="25" t="n">
+        <v>1024300</v>
+      </c>
+      <c r="H46" s="25" t="n">
+        <v>700000</v>
+      </c>
+      <c r="I46" s="25" t="n">
+        <v>260000</v>
+      </c>
+      <c r="J46" s="25" t="n">
+        <v>64300</v>
+      </c>
+      <c r="K46" s="26" t="n"/>
+      <c r="L46" s="27" t="n"/>
+    </row>
+    <row r="47" ht="13" customHeight="1">
+      <c r="A47" s="28" t="inlineStr">
+        <is>
+          <t>Кочкорский р-н</t>
+        </is>
+      </c>
+      <c r="B47" s="29" t="n"/>
+      <c r="C47" s="29" t="n"/>
+      <c r="D47" s="29" t="n"/>
+      <c r="E47" s="30" t="n">
+        <v>1</v>
+      </c>
+      <c r="F47" s="31" t="n">
+        <v>2100000</v>
+      </c>
+      <c r="G47" s="31" t="n">
+        <v>1024300</v>
+      </c>
+      <c r="H47" s="31" t="n">
+        <v>700000</v>
+      </c>
+      <c r="I47" s="31" t="n">
+        <v>260000</v>
+      </c>
+      <c r="J47" s="31" t="n">
+        <v>64300</v>
+      </c>
+      <c r="K47" s="32" t="n"/>
+      <c r="L47" s="33" t="n"/>
+    </row>
+    <row r="48" ht="13" customHeight="1">
+      <c r="A48" s="34" t="inlineStr">
+        <is>
+          <t>ОсОО «Нарын-Агро»</t>
+        </is>
+      </c>
+      <c r="B48" s="35" t="inlineStr">
+        <is>
+          <t>высокий</t>
+        </is>
+      </c>
+      <c r="C48" s="35" t="inlineStr">
+        <is>
+          <t>2.1</t>
+        </is>
+      </c>
+      <c r="D48" s="35" t="n"/>
+      <c r="E48" s="36" t="n">
+        <v>1</v>
+      </c>
+      <c r="F48" s="37" t="n">
+        <v>2100000</v>
+      </c>
+      <c r="G48" s="37" t="n">
+        <v>1024300</v>
+      </c>
+      <c r="H48" s="37" t="n">
+        <v>700000</v>
+      </c>
+      <c r="I48" s="37" t="n">
+        <v>260000</v>
+      </c>
+      <c r="J48" s="37" t="n">
+        <v>64300</v>
+      </c>
+      <c r="K48" s="36" t="n">
+        <v>409</v>
+      </c>
+      <c r="L48" s="38" t="n"/>
+    </row>
+    <row r="49" ht="24" customHeight="1">
+      <c r="A49" s="39" t="inlineStr">
+        <is>
+          <t>№ 21-2/077 от 18.05.2021</t>
+        </is>
+      </c>
+      <c r="B49" s="40" t="inlineStr">
+        <is>
+          <t>высокий</t>
+        </is>
+      </c>
+      <c r="C49" s="40" t="inlineStr">
+        <is>
+          <t>2.1</t>
+        </is>
+      </c>
+      <c r="D49" s="40" t="inlineStr">
+        <is>
+          <t>KGS</t>
+        </is>
+      </c>
+      <c r="E49" s="41" t="n"/>
+      <c r="F49" s="42" t="n">
+        <v>2100000</v>
+      </c>
+      <c r="G49" s="42" t="n">
+        <v>1024300</v>
+      </c>
+      <c r="H49" s="42" t="n">
+        <v>700000</v>
+      </c>
+      <c r="I49" s="42" t="n">
+        <v>260000</v>
+      </c>
+      <c r="J49" s="42" t="n">
+        <v>64300</v>
+      </c>
+      <c r="K49" s="43" t="n">
+        <v>409</v>
+      </c>
+      <c r="L49" s="44" t="inlineStr">
+        <is>
+          <t>Соглашение о добровольном исполнении № 3, 10.09.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="13" customHeight="1">
+      <c r="A50" s="22" t="inlineStr">
+        <is>
+          <t>Таласская обл.</t>
+        </is>
+      </c>
+      <c r="B50" s="23" t="n"/>
+      <c r="C50" s="23" t="n"/>
+      <c r="D50" s="23" t="n"/>
+      <c r="E50" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="F50" s="25" t="n">
+        <v>2720000</v>
+      </c>
+      <c r="G50" s="25" t="n">
+        <v>924700</v>
+      </c>
+      <c r="H50" s="25" t="n">
+        <v>640000</v>
+      </c>
+      <c r="I50" s="25" t="n">
+        <v>225500</v>
+      </c>
+      <c r="J50" s="25" t="n">
+        <v>59200</v>
+      </c>
+      <c r="K50" s="26" t="n"/>
+      <c r="L50" s="27" t="n"/>
+    </row>
+    <row r="51" ht="13" customHeight="1">
+      <c r="A51" s="28" t="inlineStr">
+        <is>
+          <t>Бакай-Атинский р-н</t>
+        </is>
+      </c>
+      <c r="B51" s="29" t="n"/>
+      <c r="C51" s="29" t="n"/>
+      <c r="D51" s="29" t="n"/>
+      <c r="E51" s="30" t="n">
+        <v>1</v>
+      </c>
+      <c r="F51" s="31" t="n">
+        <v>420000</v>
+      </c>
+      <c r="G51" s="31" t="n">
+        <v>51700</v>
+      </c>
+      <c r="H51" s="31" t="n">
+        <v>40000</v>
+      </c>
+      <c r="I51" s="31" t="n">
+        <v>10500</v>
+      </c>
+      <c r="J51" s="31" t="n">
+        <v>1200</v>
+      </c>
+      <c r="K51" s="32" t="n"/>
+      <c r="L51" s="33" t="n"/>
+    </row>
+    <row r="52" ht="13" customHeight="1">
+      <c r="A52" s="34" t="inlineStr">
+        <is>
+          <t>Иманалиев Бакыт Тологонович</t>
+        </is>
+      </c>
+      <c r="B52" s="35" t="inlineStr">
+        <is>
+          <t>средний</t>
+        </is>
+      </c>
+      <c r="C52" s="35" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
+      <c r="D52" s="35" t="n"/>
+      <c r="E52" s="36" t="n">
+        <v>1</v>
+      </c>
+      <c r="F52" s="37" t="n">
+        <v>420000</v>
+      </c>
+      <c r="G52" s="37" t="n">
+        <v>51700</v>
+      </c>
+      <c r="H52" s="37" t="n">
+        <v>40000</v>
+      </c>
+      <c r="I52" s="37" t="n">
+        <v>10500</v>
+      </c>
+      <c r="J52" s="37" t="n">
+        <v>1200</v>
+      </c>
+      <c r="K52" s="36" t="n">
+        <v>95</v>
+      </c>
+      <c r="L52" s="38" t="n"/>
+    </row>
+    <row r="53" ht="24" customHeight="1">
+      <c r="A53" s="39" t="inlineStr">
+        <is>
+          <t>№ 24-2/077 от 14.05.2024</t>
+        </is>
+      </c>
+      <c r="B53" s="40" t="inlineStr">
+        <is>
+          <t>средний</t>
+        </is>
+      </c>
+      <c r="C53" s="40" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
+      <c r="D53" s="40" t="inlineStr">
+        <is>
+          <t>KGS</t>
+        </is>
+      </c>
+      <c r="E53" s="41" t="n"/>
+      <c r="F53" s="42" t="n">
+        <v>420000</v>
+      </c>
+      <c r="G53" s="42" t="n">
+        <v>51700</v>
+      </c>
+      <c r="H53" s="42" t="n">
+        <v>40000</v>
+      </c>
+      <c r="I53" s="42" t="n">
+        <v>10500</v>
+      </c>
+      <c r="J53" s="42" t="n">
+        <v>1200</v>
+      </c>
+      <c r="K53" s="43" t="n">
+        <v>95</v>
+      </c>
+      <c r="L53" s="44" t="inlineStr">
+        <is>
+          <t>Запросы нотариату, ЦОН и органу регистрации, 24.08.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="13" customHeight="1">
+      <c r="A54" s="28" t="inlineStr">
+        <is>
+          <t>Таласский р-н</t>
+        </is>
+      </c>
+      <c r="B54" s="29" t="n"/>
+      <c r="C54" s="29" t="n"/>
+      <c r="D54" s="29" t="n"/>
+      <c r="E54" s="30" t="n">
+        <v>1</v>
+      </c>
+      <c r="F54" s="31" t="n">
         <v>2300000</v>
       </c>
-      <c r="G40" s="42" t="n">
+      <c r="G54" s="31" t="n">
         <v>873000</v>
       </c>
-      <c r="H40" s="42" t="n">
+      <c r="H54" s="31" t="n">
         <v>600000</v>
       </c>
-      <c r="I40" s="42" t="n">
+      <c r="I54" s="31" t="n">
         <v>215000</v>
       </c>
-      <c r="J40" s="42" t="n">
+      <c r="J54" s="31" t="n">
         <v>58000</v>
       </c>
-      <c r="K40" s="43" t="n">
+      <c r="K54" s="32" t="n"/>
+      <c r="L54" s="33" t="n"/>
+    </row>
+    <row r="55" ht="13" customHeight="1">
+      <c r="A55" s="34" t="inlineStr">
+        <is>
+          <t>ОсОО «Талас-Бал»</t>
+        </is>
+      </c>
+      <c r="B55" s="35" t="inlineStr">
+        <is>
+          <t>высокий</t>
+        </is>
+      </c>
+      <c r="C55" s="35" t="inlineStr">
+        <is>
+          <t>2.3</t>
+        </is>
+      </c>
+      <c r="D55" s="35" t="n"/>
+      <c r="E55" s="36" t="n">
+        <v>1</v>
+      </c>
+      <c r="F55" s="37" t="n">
+        <v>2300000</v>
+      </c>
+      <c r="G55" s="37" t="n">
+        <v>873000</v>
+      </c>
+      <c r="H55" s="37" t="n">
+        <v>600000</v>
+      </c>
+      <c r="I55" s="37" t="n">
+        <v>215000</v>
+      </c>
+      <c r="J55" s="37" t="n">
+        <v>58000</v>
+      </c>
+      <c r="K55" s="36" t="n">
         <v>260</v>
       </c>
-      <c r="L40" s="44" t="inlineStr">
+      <c r="L55" s="38" t="n"/>
+    </row>
+    <row r="56" ht="35" customHeight="1">
+      <c r="A56" s="39" t="inlineStr">
+        <is>
+          <t>№ 23-4/021 от 21.08.2023</t>
+        </is>
+      </c>
+      <c r="B56" s="40" t="inlineStr">
+        <is>
+          <t>высокий</t>
+        </is>
+      </c>
+      <c r="C56" s="40" t="inlineStr">
+        <is>
+          <t>2.3</t>
+        </is>
+      </c>
+      <c r="D56" s="40" t="inlineStr">
+        <is>
+          <t>KGS</t>
+        </is>
+      </c>
+      <c r="E56" s="41" t="n"/>
+      <c r="F56" s="42" t="n">
+        <v>2300000</v>
+      </c>
+      <c r="G56" s="42" t="n">
+        <v>873000</v>
+      </c>
+      <c r="H56" s="42" t="n">
+        <v>600000</v>
+      </c>
+      <c r="I56" s="42" t="n">
+        <v>215000</v>
+      </c>
+      <c r="J56" s="42" t="n">
+        <v>58000</v>
+      </c>
+      <c r="K56" s="43" t="n">
+        <v>260</v>
+      </c>
+      <c r="L56" s="44" t="inlineStr">
         <is>
           <t>Уведомление о намерении инициировать банкротство, 15.06.2026</t>
         </is>
@@ -2047,175 +2647,175 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="45" t="inlineStr">
+      <c r="A1" s="50" t="inlineStr">
         <is>
           <t>Параметры отчёта</t>
         </is>
       </c>
     </row>
     <row r="3" ht="15" customHeight="1">
-      <c r="A3" s="46" t="inlineStr">
+      <c r="A3" s="51" t="inlineStr">
         <is>
           <t>Отчёт</t>
         </is>
       </c>
-      <c r="B3" s="47" t="inlineStr">
+      <c r="B3" s="52" t="inlineStr">
         <is>
           <t>ФО-01 «Просроченная задолженность по состоянию на дату»</t>
         </is>
       </c>
     </row>
     <row r="4" ht="15" customHeight="1">
-      <c r="A4" s="46" t="inlineStr">
+      <c r="A4" s="51" t="inlineStr">
         <is>
           <t>Дата состояния</t>
         </is>
       </c>
-      <c r="B4" s="47" t="inlineStr">
+      <c r="B4" s="52" t="inlineStr">
         <is>
           <t>01.10.2026 (данные на конец 30.09.2026)</t>
         </is>
       </c>
     </row>
     <row r="5" ht="15" customHeight="1">
-      <c r="A5" s="46" t="inlineStr">
+      <c r="A5" s="51" t="inlineStr">
         <is>
           <t>Департамент</t>
         </is>
       </c>
-      <c r="B5" s="47" t="inlineStr">
+      <c r="B5" s="52" t="inlineStr">
         <is>
           <t>все</t>
         </is>
       </c>
     </row>
     <row r="6" ht="15" customHeight="1">
-      <c r="A6" s="46" t="inlineStr">
+      <c r="A6" s="51" t="inlineStr">
         <is>
           <t>Отдел</t>
         </is>
       </c>
-      <c r="B6" s="47" t="inlineStr">
+      <c r="B6" s="52" t="inlineStr">
         <is>
           <t>все</t>
         </is>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
-      <c r="A7" s="46" t="inlineStr">
+      <c r="A7" s="51" t="inlineStr">
         <is>
           <t>Область</t>
         </is>
       </c>
-      <c r="B7" s="47" t="inlineStr">
+      <c r="B7" s="52" t="inlineStr">
         <is>
           <t>все</t>
         </is>
       </c>
     </row>
     <row r="8" ht="15" customHeight="1">
-      <c r="A8" s="46" t="inlineStr">
+      <c r="A8" s="51" t="inlineStr">
         <is>
           <t>Категория риска</t>
         </is>
       </c>
-      <c r="B8" s="47" t="inlineStr">
+      <c r="B8" s="52" t="inlineStr">
         <is>
           <t>все</t>
         </is>
       </c>
     </row>
     <row r="9" ht="15" customHeight="1">
-      <c r="A9" s="46" t="inlineStr">
+      <c r="A9" s="51" t="inlineStr">
         <is>
           <t>Просрочка от, дней</t>
         </is>
       </c>
-      <c r="B9" s="47" t="inlineStr">
+      <c r="B9" s="52" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1">
-      <c r="A10" s="46" t="inlineStr">
+      <c r="A10" s="51" t="inlineStr">
         <is>
           <t>Единица</t>
         </is>
       </c>
-      <c r="B10" s="47" t="inlineStr">
+      <c r="B10" s="52" t="inlineStr">
         <is>
           <t>сом</t>
         </is>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1">
-      <c r="A11" s="46" t="inlineStr">
+      <c r="A11" s="51" t="inlineStr">
         <is>
           <t>Разрезы</t>
         </is>
       </c>
-      <c r="B11" s="47" t="inlineStr">
+      <c r="B11" s="52" t="inlineStr">
         <is>
           <t>Департамент → Отдел → Область → Район → Заёмщик → кредит</t>
         </is>
       </c>
     </row>
     <row r="12" ht="15" customHeight="1">
-      <c r="A12" s="46" t="inlineStr">
+      <c r="A12" s="51" t="inlineStr">
         <is>
           <t>Курсы валют</t>
         </is>
       </c>
-      <c r="B12" s="47" t="inlineStr">
-        <is>
-          <t>USD — 87,50000 на 30.09.2026</t>
+      <c r="B12" s="52" t="inlineStr">
+        <is>
+          <t>USD — 87,50000, EUR — 101,50000 на 30.09.2026</t>
         </is>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1">
-      <c r="A13" s="46" t="inlineStr">
+      <c r="A13" s="51" t="inlineStr">
         <is>
           <t>Период</t>
         </is>
       </c>
-      <c r="B13" s="47" t="inlineStr">
+      <c r="B13" s="52" t="inlineStr">
         <is>
           <t>сентябрь 2026 — закрыт 05.10.2026; исправлений после закрытия нет</t>
         </is>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
-      <c r="A14" s="46" t="inlineStr">
+      <c r="A14" s="51" t="inlineStr">
         <is>
           <t>Рассчитан</t>
         </is>
       </c>
-      <c r="B14" s="47" t="inlineStr">
+      <c r="B14" s="52" t="inlineStr">
         <is>
           <t>06.10.2026 09:12</t>
         </is>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
-      <c r="A15" s="46" t="inlineStr">
+      <c r="A15" s="51" t="inlineStr">
         <is>
           <t>Сформировал</t>
         </is>
       </c>
-      <c r="B15" s="47" t="inlineStr">
+      <c r="B15" s="52" t="inlineStr">
         <is>
           <t>Асанов А. К.</t>
         </is>
       </c>
     </row>
     <row r="16" ht="27" customHeight="1">
-      <c r="A16" s="46" t="inlineStr">
+      <c r="A16" s="51" t="inlineStr">
         <is>
           <t>Округление</t>
         </is>
       </c>
-      <c r="B16" s="47" t="inlineStr">
+      <c r="B16" s="52" t="inlineStr">
         <is>
           <t>В ячейках — точные суммы, на экране и в печати — до копеек. Итоги считаются по точным суммам, поэтому сумма округлённых строк может отличаться от итога на копейки.</t>
         </is>
@@ -2233,7 +2833,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:C45"/>
+  <dimension ref="A1:C47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -2242,139 +2842,139 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="48" t="inlineStr">
+      <c r="A1" s="53" t="inlineStr">
         <is>
           <t>ФО-01 «Просроченная задолженность по состоянию на дату» — карточка</t>
         </is>
       </c>
     </row>
     <row r="3" ht="15" customHeight="1">
-      <c r="A3" s="49" t="inlineStr">
+      <c r="A3" s="54" t="inlineStr">
         <is>
           <t>Номер</t>
         </is>
       </c>
-      <c r="B3" s="50" t="inlineStr">
+      <c r="B3" s="55" t="inlineStr">
         <is>
           <t>ФО-01</t>
         </is>
       </c>
     </row>
     <row r="4" ht="15" customHeight="1">
-      <c r="A4" s="49" t="inlineStr">
+      <c r="A4" s="54" t="inlineStr">
         <is>
           <t>Название</t>
         </is>
       </c>
-      <c r="B4" s="50" t="inlineStr">
+      <c r="B4" s="55" t="inlineStr">
         <is>
           <t>Просроченная задолженность по состоянию на дату</t>
         </is>
       </c>
     </row>
     <row r="5" ht="15" customHeight="1">
-      <c r="A5" s="49" t="inlineStr">
+      <c r="A5" s="54" t="inlineStr">
         <is>
           <t>Часть</t>
         </is>
       </c>
-      <c r="B5" s="50" t="inlineStr">
+      <c r="B5" s="55" t="inlineStr">
         <is>
           <t>Отчёт</t>
         </is>
       </c>
     </row>
     <row r="6" ht="15" customHeight="1">
-      <c r="A6" s="49" t="inlineStr">
+      <c r="A6" s="54" t="inlineStr">
         <is>
           <t>Модуль</t>
         </is>
       </c>
-      <c r="B6" s="50" t="inlineStr">
+      <c r="B6" s="55" t="inlineStr">
         <is>
           <t>Кредит</t>
         </is>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
-      <c r="A7" s="49" t="inlineStr">
+      <c r="A7" s="54" t="inlineStr">
         <is>
           <t>Получатель</t>
         </is>
       </c>
-      <c r="B7" s="50" t="inlineStr">
+      <c r="B7" s="55" t="inlineStr">
         <is>
           <t>Комитет</t>
         </is>
       </c>
     </row>
     <row r="8" ht="15" customHeight="1">
-      <c r="A8" s="49" t="inlineStr">
+      <c r="A8" s="54" t="inlineStr">
         <is>
           <t>Язык</t>
         </is>
       </c>
-      <c r="B8" s="50" t="inlineStr">
+      <c r="B8" s="55" t="inlineStr">
         <is>
           <t>язык интерфейса</t>
         </is>
       </c>
     </row>
     <row r="9" ht="15" customHeight="1">
-      <c r="A9" s="49" t="inlineStr">
+      <c r="A9" s="54" t="inlineStr">
         <is>
           <t>Основание</t>
         </is>
       </c>
-      <c r="B9" s="50" t="inlineStr">
+      <c r="B9" s="55" t="inlineStr">
         <is>
           <t>Порядок №41 п. 12, п. 6 пп. 1; оф. ТЗ ¶76, ¶477, ¶644–670; ТЗ 17</t>
         </is>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1">
-      <c r="A10" s="49" t="inlineStr">
+      <c r="A10" s="54" t="inlineStr">
         <is>
           <t>Образец-основа</t>
         </is>
       </c>
-      <c r="B10" s="50" t="inlineStr">
+      <c r="B10" s="55" t="inlineStr">
         <is>
           <t>старая система «Отчет по задолженности»</t>
         </is>
       </c>
     </row>
     <row r="11" ht="45" customHeight="1">
-      <c r="A11" s="49" t="inlineStr">
+      <c r="A11" s="54" t="inlineStr">
         <is>
           <t>Кому и зачем</t>
         </is>
       </c>
-      <c r="B11" s="50" t="inlineStr">
+      <c r="B11" s="55" t="inlineStr">
         <is>
           <t>Соответствующему комитету (по администрированию бюджетных кредитов или по региональному развитию — в зависимости от департамента) — актуальная просроченная задолженность заёмщиков: сколько кредитов с просрочкой, на какую сумму, как давно и что по ним делается.</t>
         </is>
       </c>
     </row>
     <row r="12" ht="30" customHeight="1">
-      <c r="A12" s="49" t="inlineStr">
+      <c r="A12" s="54" t="inlineStr">
         <is>
           <t>Когда</t>
         </is>
       </c>
-      <c r="B12" s="50" t="inlineStr">
+      <c r="B12" s="55" t="inlineStr">
         <is>
           <t>На любую дату. Для комитета — на 1-е число месяца, следующего за отчётным, ежемесячно; отраслевой департамент выносит на соответствующий комитет не позднее 15-го числа (Порядок №41 п. 12).</t>
         </is>
       </c>
     </row>
     <row r="13" ht="180" customHeight="1">
-      <c r="A13" s="49" t="inlineStr">
+      <c r="A13" s="54" t="inlineStr">
         <is>
           <t>Параметры</t>
         </is>
       </c>
-      <c r="B13" s="50" t="inlineStr">
+      <c r="B13" s="55" t="inlineStr">
         <is>
           <t>• Дата состояния — 1-е число текущего месяца; можно выбрать любую дату
 • Департамент — все
@@ -2388,389 +2988,415 @@
       </c>
     </row>
     <row r="14" ht="180" customHeight="1">
-      <c r="A14" s="49" t="inlineStr">
+      <c r="A14" s="54" t="inlineStr">
         <is>
           <t>Строки</t>
         </is>
       </c>
-      <c r="B14" s="50" t="inlineStr">
+      <c r="B14" s="55" t="inlineStr">
         <is>
           <t>Строка детали — кредит: договор, признаки, суммы, дни просрочки, стадия взыскания. Над кредитами разрезы, по умолчанию департамент → отдел → область → район → заёмщик; область и район — кредита на дату состояния; у городов республиканского значения показываются обе строки — области и района; подразделение — то, за которым кредит закреплён на дату состояния. Первая строка — ИТОГО; строка разреза несёт его итог (число кредитов и суммы) и стоит над его строками; строка заёмщика есть всегда, даже при одном кредите. Признак, выбранный разрезом, колонкой не повторяется. Порядок: департаменты и отделы — по оргструктуре; области — по справочнику (области по алфавиту, затем г. Бишкек, г. Ош); районы — по алфавиту; заёмщики — по убыванию наибольших дней просрочки, при равных — по алфавиту; кредиты заёмщика — по убыванию дней. В отчёт попадают кредиты с просрочкой не меньше заданного числа дней на дату состояния. Кредит в иностранной валюте: суммы в сомах по курсу на дату, под ним курсивом строка «в &lt;валюта&gt; (курс …)» с теми же суммами в валюте договора; в итоги она не входит.</t>
         </is>
       </c>
     </row>
     <row r="15" ht="45" customHeight="1">
-      <c r="A15" s="49" t="inlineStr">
+      <c r="A15" s="54" t="inlineStr">
         <is>
           <t>Разрезы</t>
         </is>
       </c>
-      <c r="B15" s="50" t="inlineStr">
+      <c r="B15" s="55" t="inlineStr">
         <is>
           <t>по умолчанию: Департамент → Отдел → Область → Район → Заёмщик → кредит; можно выбрать: Департамент, Отдел, Куратор, Область, Район, Категория риска, Группа платёжеспособности, Тип проекта, Заёмщик</t>
         </is>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
-      <c r="A16" s="49" t="inlineStr">
+      <c r="A16" s="54" t="inlineStr">
         <is>
           <t>Если строк нет</t>
         </is>
       </c>
-      <c r="B16" s="50" t="inlineStr">
+      <c r="B16" s="55" t="inlineStr">
         <is>
           <t>Кредитов с просрочкой от {N} дней на {дата} нет.</t>
         </is>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
-      <c r="A17" s="49" t="inlineStr">
+      <c r="A17" s="54" t="inlineStr">
         <is>
           <t>Выгрузка</t>
         </is>
       </c>
-      <c r="B17" s="50" t="inlineStr">
+      <c r="B17" s="55" t="inlineStr">
         <is>
           <t>xlsx, pdf</t>
         </is>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
-      <c r="A18" s="49" t="inlineStr">
+      <c r="A18" s="54" t="inlineStr">
         <is>
           <t>Примечание</t>
         </is>
       </c>
-      <c r="B18" s="50" t="inlineStr">
+      <c r="B18" s="55" t="inlineStr">
         <is>
           <t>Для комитета — на 1-е число, ежемесячно до 15-го</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="51" t="inlineStr">
+      <c r="A20" s="56" t="inlineStr">
         <is>
           <t>Колонки</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="52" t="inlineStr">
+      <c r="A21" s="57" t="inlineStr">
         <is>
           <t>Колонка</t>
         </is>
       </c>
-      <c r="B21" s="52" t="inlineStr">
+      <c r="B21" s="57" t="inlineStr">
         <is>
           <t>Общая шапка</t>
         </is>
       </c>
-      <c r="C21" s="52" t="inlineStr">
+      <c r="C21" s="57" t="inlineStr">
         <is>
           <t>Что в ней</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="50" t="inlineStr">
+      <c r="A22" s="55" t="inlineStr">
         <is>
           <t>Наименование</t>
         </is>
       </c>
-      <c r="B22" s="50" t="inlineStr"/>
-      <c r="C22" s="50" t="inlineStr">
+      <c r="B22" s="55" t="inlineStr"/>
+      <c r="C22" s="55" t="inlineStr">
         <is>
           <t>департамент, отдел, область, район, заёмщик или договор — по уровню строки</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="50" t="inlineStr">
+      <c r="A23" s="55" t="inlineStr">
         <is>
           <t>Категория риска</t>
         </is>
       </c>
-      <c r="B23" s="50" t="inlineStr"/>
-      <c r="C23" s="50" t="inlineStr">
+      <c r="B23" s="55" t="inlineStr"/>
+      <c r="C23" s="55" t="inlineStr">
         <is>
           <t>категория кредитного риска на дату состояния: у кредита — его категория, у заёмщика — худшая по его кредитам; выше заёмщика пусто</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="50" t="inlineStr">
+      <c r="A24" s="55" t="inlineStr">
         <is>
           <t>Группа</t>
         </is>
       </c>
-      <c r="B24" s="50" t="inlineStr"/>
-      <c r="C24" s="50" t="inlineStr">
+      <c r="B24" s="55" t="inlineStr"/>
+      <c r="C24" s="55" t="inlineStr">
         <is>
           <t>группа платёжеспособности заёмщика на дату состояния по Инструкции №14; у заёмщика и у каждого его кредита одна и та же; выше заёмщика пусто</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="50" t="inlineStr">
+      <c r="A25" s="55" t="inlineStr">
         <is>
           <t>Валюта</t>
         </is>
       </c>
-      <c r="B25" s="50" t="inlineStr"/>
-      <c r="C25" s="50" t="inlineStr">
+      <c r="B25" s="55" t="inlineStr"/>
+      <c r="C25" s="55" t="inlineStr">
         <is>
           <t>валюта кредита; заполняется у кредита</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="50" t="inlineStr">
+      <c r="A26" s="55" t="inlineStr">
         <is>
           <t>Кредитов с просрочкой</t>
         </is>
       </c>
-      <c r="B26" s="50" t="inlineStr"/>
-      <c r="C26" s="50" t="inlineStr">
+      <c r="B26" s="55" t="inlineStr"/>
+      <c r="C26" s="55" t="inlineStr">
         <is>
           <t>число кредитов разреза с просрочкой не меньше заданной; у кредита пусто</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="50" t="inlineStr">
+      <c r="A27" s="55" t="inlineStr">
         <is>
           <t>Остаток основного долга</t>
         </is>
       </c>
-      <c r="B27" s="50" t="inlineStr"/>
-      <c r="C27" s="50" t="inlineStr">
+      <c r="B27" s="55" t="inlineStr"/>
+      <c r="C27" s="55" t="inlineStr">
         <is>
           <t>остаток основной суммы на дату состояния; валютный кредит — в сомах по курсу на эту дату</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="50" t="inlineStr">
+      <c r="A28" s="55" t="inlineStr">
         <is>
           <t>Просроченная задолженность</t>
         </is>
       </c>
-      <c r="B28" s="50" t="inlineStr"/>
-      <c r="C28" s="50" t="inlineStr">
+      <c r="B28" s="55" t="inlineStr"/>
+      <c r="C28" s="55" t="inlineStr">
         <is>
           <t>основная сумма + проценты + штрафы, срок уплаты которых наступил и которые не оплачены</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="50" t="inlineStr">
+      <c r="A29" s="55" t="inlineStr">
         <is>
           <t>основная сумма</t>
         </is>
       </c>
-      <c r="B29" s="50" t="inlineStr">
+      <c r="B29" s="55" t="inlineStr">
         <is>
           <t>в том числе</t>
         </is>
       </c>
-      <c r="C29" s="50" t="inlineStr">
+      <c r="C29" s="55" t="inlineStr">
         <is>
           <t>просроченная основная сумма</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="50" t="inlineStr">
+      <c r="A30" s="55" t="inlineStr">
         <is>
           <t>проценты</t>
         </is>
       </c>
-      <c r="B30" s="50" t="inlineStr">
+      <c r="B30" s="55" t="inlineStr">
         <is>
           <t>в том числе</t>
         </is>
       </c>
-      <c r="C30" s="50" t="inlineStr">
+      <c r="C30" s="55" t="inlineStr">
         <is>
           <t>просроченные проценты — начисленные и ранее накопленные (накопленные бывают только после реструктуризации)</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="50" t="inlineStr">
+      <c r="A31" s="55" t="inlineStr">
         <is>
           <t>штрафы</t>
         </is>
       </c>
-      <c r="B31" s="50" t="inlineStr">
+      <c r="B31" s="55" t="inlineStr">
         <is>
           <t>в том числе</t>
         </is>
       </c>
-      <c r="C31" s="50" t="inlineStr">
+      <c r="C31" s="55" t="inlineStr">
         <is>
           <t>неоплаченные штрафы — начисленные и ранее накопленные</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="50" t="inlineStr">
+      <c r="A32" s="55" t="inlineStr">
         <is>
           <t>Дни просрочки</t>
         </is>
       </c>
-      <c r="B32" s="50" t="inlineStr"/>
-      <c r="C32" s="50" t="inlineStr">
+      <c r="B32" s="55" t="inlineStr"/>
+      <c r="C32" s="55" t="inlineStr">
         <is>
           <t>дни от самой ранней неоплаченной даты платежа до даты состояния; у заёмщика — наибольшие по его кредитам; выше заёмщика пусто</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="50" t="inlineStr">
+      <c r="A33" s="55" t="inlineStr">
         <is>
           <t>Стадия взыскания</t>
         </is>
       </c>
-      <c r="B33" s="50" t="inlineStr"/>
-      <c r="C33" s="50" t="inlineStr">
+      <c r="B33" s="55" t="inlineStr"/>
+      <c r="C33" s="55" t="inlineStr">
         <is>
           <t>последняя зарегистрированная мера взыскания по кредиту и её дата; если мер нет — «мер нет»; заполняется у кредита</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="51" t="inlineStr">
+      <c r="A35" s="56" t="inlineStr">
         <is>
           <t>Правила проверки</t>
         </is>
       </c>
     </row>
     <row r="36" ht="30" customHeight="1">
-      <c r="A36" s="49" t="inlineStr">
+      <c r="A36" s="54" t="inlineStr">
         <is>
           <t>1.</t>
         </is>
       </c>
-      <c r="B36" s="50" t="inlineStr">
-        <is>
-          <t>ИТОГО: «Просроченная задолженность» = 4 560 750,00 сом по 7 кредитам (КЗ-02, 03, 04, 05, 09, 10, 19); «Остаток основного долга» = 13 170 000,00 сом.</t>
+      <c r="B36" s="55" t="inlineStr">
+        <is>
+          <t>ИТОГО: «Просроченная задолженность» = 10 328 815,00 сом по 12 кредитам (КЗ-02, 03, 04, 05, 09, 10, 19, 22, 23 и три кредита КЗ-21); «Остаток основного долга» = 41 417 000,00 сом.</t>
         </is>
       </c>
     </row>
     <row r="37" ht="45" customHeight="1">
-      <c r="A37" s="49" t="inlineStr">
+      <c r="A37" s="54" t="inlineStr">
         <is>
           <t>2.</t>
         </is>
       </c>
-      <c r="B37" s="50" t="inlineStr">
-        <is>
-          <t>Строка разреза = сумма строк на уровень ниже по каждой суммовой колонке (заёмщик — его кредитов, район — его заёмщиков и т. д.), ИТОГО — сумма департаментов; «Кредитов с просрочкой» = число кредитов разреза, в ИТОГО — 7.</t>
+      <c r="B37" s="55" t="inlineStr">
+        <is>
+          <t>Строка разреза = сумма строк на уровень ниже по каждой суммовой колонке (заёмщик — его кредитов, район — его заёмщиков и т. д.), ИТОГО — сумма департаментов; «Кредитов с просрочкой» = число кредитов разреза, в ИТОГО — 12.</t>
         </is>
       </c>
     </row>
     <row r="38" ht="15" customHeight="1">
-      <c r="A38" s="49" t="inlineStr">
+      <c r="A38" s="54" t="inlineStr">
         <is>
           <t>3.</t>
         </is>
       </c>
-      <c r="B38" s="50" t="inlineStr">
-        <is>
-          <t>У КЗ-02 (г. Бишкек) две строки: область и район.</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="30" customHeight="1">
-      <c r="A39" s="49" t="inlineStr">
+      <c r="B38" s="55" t="inlineStr">
+        <is>
+          <t>У КЗ-02 (г. Бишкек) и КЗ-22 (г. Ош) по две строки: область и район.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="75" customHeight="1">
+      <c r="A39" s="54" t="inlineStr">
         <is>
           <t>4.</t>
         </is>
       </c>
-      <c r="B39" s="50" t="inlineStr">
-        <is>
-          <t>Дни просрочки на 01.10.2026: КЗ-02 — 20, КЗ-03 — 75, КЗ-09 — 95, КЗ-19 — 190, КЗ-04 — 212, КЗ-10 — 260, КЗ-05 — 409 (считается от 18.08.2025).</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="30" customHeight="1">
-      <c r="A40" s="49" t="inlineStr">
+      <c r="B39" s="55" t="inlineStr">
+        <is>
+          <t>Валютный кредит — в сомах по курсу на 30.09.2026 (USD 87,50000, EUR 101,50000); под ним курсивом строка «в USD (курс 87,50000)» или «в EUR (курс 101,50000)» с суммами в валюте договора, в итоги она не входит. КЗ-23: остаток 90 000,00 USD = 7 875 000,00 сом, просрочка 20 250,00 USD = 1 771 875,00 сом; КЗ-22: остаток 48 000,00 EUR = 4 872 000,00 сом, просрочка 10 460,00 EUR = 1 061 690,00 сом.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="60" customHeight="1">
+      <c r="A40" s="54" t="inlineStr">
         <is>
           <t>5.</t>
         </is>
       </c>
-      <c r="B40" s="50" t="inlineStr">
-        <is>
-          <t>Категория риска: средний — КЗ-02, 03, 09; высокий — КЗ-04, 05, 10, 19 (Порядок №41 п. 11: 1–180 дней — средний, более 180 — высокий).</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="15" customHeight="1">
-      <c r="A41" s="49" t="inlineStr">
+      <c r="B40" s="55" t="inlineStr">
+        <is>
+          <t>Заёмщик с несколькими кредитами — КЗ-21 (USD и два в сомах): строка заёмщика — 3 кредита, остаток 15 500 000,00, просрочка 2 934 500,00 сом (валютный кредит — в сомах), категория — худшая (высокий), дни — наибольшие (190); кредиты под ним по убыванию дней — 190, 120, 35. У № 24-3/105 просрочены только проценты и штрафы, просроченная основная сумма — 0,00.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="30" customHeight="1">
+      <c r="A41" s="54" t="inlineStr">
         <is>
           <t>6.</t>
         </is>
       </c>
-      <c r="B41" s="50" t="inlineStr">
+      <c r="B41" s="55" t="inlineStr">
+        <is>
+          <t>Дни просрочки на 01.10.2026: КЗ-02 — 20, КЗ-03 — 75, КЗ-09 — 95, КЗ-19 — 190, КЗ-04 — 212, КЗ-10 — 260, КЗ-05 — 409 (считается от 18.08.2025); КЗ-21 — 190, 120, 35; КЗ-22 — 62; КЗ-23 — 245.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="45" customHeight="1">
+      <c r="A42" s="54" t="inlineStr">
+        <is>
+          <t>7.</t>
+        </is>
+      </c>
+      <c r="B42" s="55" t="inlineStr">
+        <is>
+          <t>Категория риска: средний — КЗ-02, 03, 09, 22, КЗ-21 № 22-3/014 и № 24-3/105; высокий — КЗ-04, 05, 10, 19, 23, КЗ-21 № 19-3/061 (Порядок №41 п. 11: 1–180 дней — средний, более 180 — высокий).</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="15" customHeight="1">
+      <c r="A43" s="54" t="inlineStr">
+        <is>
+          <t>8.</t>
+        </is>
+      </c>
+      <c r="B43" s="55" t="inlineStr">
         <is>
           <t>Группа = группе заёмщика в контрольном наборе.</t>
         </is>
       </c>
     </row>
-    <row r="42" ht="30" customHeight="1">
-      <c r="A42" s="49" t="inlineStr">
-        <is>
-          <t>7.</t>
-        </is>
-      </c>
-      <c r="B42" s="50" t="inlineStr">
+    <row r="44" ht="30" customHeight="1">
+      <c r="A44" s="54" t="inlineStr">
+        <is>
+          <t>9.</t>
+        </is>
+      </c>
+      <c r="B44" s="55" t="inlineStr">
         <is>
           <t>Стадия взыскания: КЗ-05 — «Соглашение о добровольном исполнении № 3, 10.09.2026»; КЗ-19 — «мер нет».</t>
         </is>
       </c>
     </row>
-    <row r="43" ht="15" customHeight="1">
-      <c r="A43" s="49" t="inlineStr">
-        <is>
-          <t>8.</t>
-        </is>
-      </c>
-      <c r="B43" s="50" t="inlineStr">
+    <row r="45" ht="15" customHeight="1">
+      <c r="A45" s="54" t="inlineStr">
+        <is>
+          <t>10.</t>
+        </is>
+      </c>
+      <c r="B45" s="55" t="inlineStr">
         <is>
           <t>КЗ-01 (платит по графику) и КЗ-15 (кредит погашен) в отчёте на 01.10.2026 не показаны.</t>
         </is>
       </c>
     </row>
-    <row r="44" ht="15" customHeight="1">
-      <c r="A44" s="49" t="inlineStr">
-        <is>
-          <t>9.</t>
-        </is>
-      </c>
-      <c r="B44" s="50" t="inlineStr">
+    <row r="46" ht="15" customHeight="1">
+      <c r="A46" s="54" t="inlineStr">
+        <is>
+          <t>11.</t>
+        </is>
+      </c>
+      <c r="B46" s="55" t="inlineStr">
         <is>
           <t>Строка заёмщика есть и при одном кредите; в районе заёмщики — по убыванию дней.</t>
         </is>
       </c>
     </row>
-    <row r="45" ht="30" customHeight="1">
-      <c r="A45" s="49" t="inlineStr">
-        <is>
-          <t>10.</t>
-        </is>
-      </c>
-      <c r="B45" s="50" t="inlineStr">
+    <row r="47" ht="30" customHeight="1">
+      <c r="A47" s="54" t="inlineStr">
+        <is>
+          <t>12.</t>
+        </is>
+      </c>
+      <c r="B47" s="55" t="inlineStr">
         <is>
           <t>Отбор «Отдел развития регионов», категория «средний» на 01.10.2026: только ИТОГО с нулями и под таблицей «Кредитов с просрочкой от 1 дня на 01.10.2026 нет.»</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="26">
+  <mergeCells count="28">
+    <mergeCell ref="B47:C47"/>
     <mergeCell ref="B16:C16"/>
     <mergeCell ref="B7:C7"/>
     <mergeCell ref="B3:C3"/>
+    <mergeCell ref="B46:C46"/>
     <mergeCell ref="B18:C18"/>
     <mergeCell ref="B43:C43"/>
     <mergeCell ref="B12:C12"/>

--- a/docs/perechen-otchetov/obrazcy/ФО-01.xlsx
+++ b/docs/perechen-otchetov/obrazcy/ФО-01.xlsx
@@ -688,19 +688,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:L56"/>
+  <dimension ref="A1:L60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
-    <col width="7" customWidth="1" min="2" max="2"/>
+    <col width="7.8" customWidth="1" min="2" max="2"/>
     <col width="7" customWidth="1" min="3" max="3"/>
     <col width="7" customWidth="1" min="4" max="4"/>
-    <col width="8" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="8.6" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
     <col width="8" customWidth="1" min="11" max="11"/>
     <col width="28" customWidth="1" min="12" max="12"/>
   </cols>
@@ -727,7 +727,7 @@
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>по состоянию на 01.10.2026, сом</t>
+          <t>по состоянию на 01.10.2026, тыс. сом</t>
         </is>
       </c>
     </row>
@@ -785,7 +785,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="27" customHeight="1">
+    <row r="6" ht="19" customHeight="1">
       <c r="A6" s="5" t="n"/>
       <c r="B6" s="5" t="n"/>
       <c r="C6" s="5" t="n"/>
@@ -859,22 +859,22 @@
       <c r="C8" s="7" t="n"/>
       <c r="D8" s="7" t="n"/>
       <c r="E8" s="8" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F8" s="9" t="n">
-        <v>41417000</v>
+        <v>41417</v>
       </c>
       <c r="G8" s="9" t="n">
-        <v>10328815</v>
+        <v>10347.215</v>
       </c>
       <c r="H8" s="9" t="n">
-        <v>7454500</v>
+        <v>7454.5</v>
       </c>
       <c r="I8" s="9" t="n">
-        <v>2350865</v>
+        <v>2350.865</v>
       </c>
       <c r="J8" s="9" t="n">
-        <v>523450</v>
+        <v>541.85</v>
       </c>
       <c r="K8" s="10" t="n"/>
       <c r="L8" s="6" t="n"/>
@@ -892,19 +892,19 @@
         <v>6</v>
       </c>
       <c r="F9" s="14" t="n">
-        <v>22922000</v>
+        <v>22922</v>
       </c>
       <c r="G9" s="14" t="n">
-        <v>4326440</v>
+        <v>4326.44</v>
       </c>
       <c r="H9" s="14" t="n">
-        <v>3202000</v>
+        <v>3202</v>
       </c>
       <c r="I9" s="14" t="n">
-        <v>980990</v>
+        <v>980.99</v>
       </c>
       <c r="J9" s="14" t="n">
-        <v>143450</v>
+        <v>143.45</v>
       </c>
       <c r="K9" s="15" t="n"/>
       <c r="L9" s="11" t="n"/>
@@ -922,19 +922,19 @@
         <v>6</v>
       </c>
       <c r="F10" s="19" t="n">
-        <v>22922000</v>
+        <v>22922</v>
       </c>
       <c r="G10" s="19" t="n">
-        <v>4326440</v>
+        <v>4326.44</v>
       </c>
       <c r="H10" s="19" t="n">
-        <v>3202000</v>
+        <v>3202</v>
       </c>
       <c r="I10" s="19" t="n">
-        <v>980990</v>
+        <v>980.99</v>
       </c>
       <c r="J10" s="19" t="n">
-        <v>143450</v>
+        <v>143.45</v>
       </c>
       <c r="K10" s="20" t="n"/>
       <c r="L10" s="21" t="n"/>
@@ -952,19 +952,19 @@
         <v>4</v>
       </c>
       <c r="F11" s="25" t="n">
-        <v>16150000</v>
+        <v>16150</v>
       </c>
       <c r="G11" s="25" t="n">
-        <v>3083900</v>
+        <v>3083.9</v>
       </c>
       <c r="H11" s="25" t="n">
-        <v>2240000</v>
+        <v>2240</v>
       </c>
       <c r="I11" s="25" t="n">
-        <v>733250</v>
+        <v>733.25</v>
       </c>
       <c r="J11" s="25" t="n">
-        <v>110650</v>
+        <v>110.65</v>
       </c>
       <c r="K11" s="26" t="n"/>
       <c r="L11" s="27" t="n"/>
@@ -982,19 +982,19 @@
         <v>1</v>
       </c>
       <c r="F12" s="31" t="n">
-        <v>650000</v>
+        <v>650</v>
       </c>
       <c r="G12" s="31" t="n">
-        <v>149400</v>
+        <v>149.4</v>
       </c>
       <c r="H12" s="31" t="n">
-        <v>90000</v>
+        <v>90</v>
       </c>
       <c r="I12" s="31" t="n">
-        <v>41000</v>
+        <v>41</v>
       </c>
       <c r="J12" s="31" t="n">
-        <v>18400</v>
+        <v>18.4</v>
       </c>
       <c r="K12" s="32" t="n"/>
       <c r="L12" s="33" t="n"/>
@@ -1020,19 +1020,19 @@
         <v>1</v>
       </c>
       <c r="F13" s="37" t="n">
-        <v>650000</v>
+        <v>650</v>
       </c>
       <c r="G13" s="37" t="n">
-        <v>149400</v>
+        <v>149.4</v>
       </c>
       <c r="H13" s="37" t="n">
-        <v>90000</v>
+        <v>90</v>
       </c>
       <c r="I13" s="37" t="n">
-        <v>41000</v>
+        <v>41</v>
       </c>
       <c r="J13" s="37" t="n">
-        <v>18400</v>
+        <v>18.4</v>
       </c>
       <c r="K13" s="36" t="n">
         <v>75</v>
@@ -1062,19 +1062,19 @@
       </c>
       <c r="E14" s="41" t="n"/>
       <c r="F14" s="42" t="n">
-        <v>650000</v>
+        <v>650</v>
       </c>
       <c r="G14" s="42" t="n">
-        <v>149400</v>
+        <v>149.4</v>
       </c>
       <c r="H14" s="42" t="n">
-        <v>90000</v>
+        <v>90</v>
       </c>
       <c r="I14" s="42" t="n">
-        <v>41000</v>
+        <v>41</v>
       </c>
       <c r="J14" s="42" t="n">
-        <v>18400</v>
+        <v>18.4</v>
       </c>
       <c r="K14" s="43" t="n">
         <v>75</v>
@@ -1098,19 +1098,19 @@
         <v>3</v>
       </c>
       <c r="F15" s="31" t="n">
-        <v>15500000</v>
+        <v>15500</v>
       </c>
       <c r="G15" s="31" t="n">
-        <v>2934500</v>
+        <v>2934.5</v>
       </c>
       <c r="H15" s="31" t="n">
-        <v>2150000</v>
+        <v>2150</v>
       </c>
       <c r="I15" s="31" t="n">
-        <v>692250</v>
+        <v>692.25</v>
       </c>
       <c r="J15" s="31" t="n">
-        <v>92250</v>
+        <v>92.25</v>
       </c>
       <c r="K15" s="32" t="n"/>
       <c r="L15" s="33" t="n"/>
@@ -1136,19 +1136,19 @@
         <v>3</v>
       </c>
       <c r="F16" s="37" t="n">
-        <v>15500000</v>
+        <v>15500</v>
       </c>
       <c r="G16" s="37" t="n">
-        <v>2934500</v>
+        <v>2934.5</v>
       </c>
       <c r="H16" s="37" t="n">
-        <v>2150000</v>
+        <v>2150</v>
       </c>
       <c r="I16" s="37" t="n">
-        <v>692250</v>
+        <v>692.25</v>
       </c>
       <c r="J16" s="37" t="n">
-        <v>92250</v>
+        <v>92.25</v>
       </c>
       <c r="K16" s="36" t="n">
         <v>190</v>
@@ -1178,19 +1178,19 @@
       </c>
       <c r="E17" s="41" t="n"/>
       <c r="F17" s="42" t="n">
-        <v>10500000</v>
+        <v>10500</v>
       </c>
       <c r="G17" s="42" t="n">
-        <v>2380000</v>
+        <v>2380</v>
       </c>
       <c r="H17" s="42" t="n">
-        <v>1750000</v>
+        <v>1750</v>
       </c>
       <c r="I17" s="42" t="n">
-        <v>551250</v>
+        <v>551.25</v>
       </c>
       <c r="J17" s="42" t="n">
-        <v>78750</v>
+        <v>78.75</v>
       </c>
       <c r="K17" s="43" t="n">
         <v>190</v>
@@ -1204,7 +1204,7 @@
     <row r="18" ht="13" customHeight="1">
       <c r="A18" s="45" t="inlineStr">
         <is>
-          <t>в USD (курс 87,50000)</t>
+          <t>в тыс. USD (курс 87,50000)</t>
         </is>
       </c>
       <c r="B18" s="46" t="n"/>
@@ -1212,19 +1212,19 @@
       <c r="D18" s="46" t="n"/>
       <c r="E18" s="47" t="n"/>
       <c r="F18" s="48" t="n">
-        <v>120000</v>
+        <v>120</v>
       </c>
       <c r="G18" s="48" t="n">
-        <v>27200</v>
+        <v>27.2</v>
       </c>
       <c r="H18" s="48" t="n">
-        <v>20000</v>
+        <v>20</v>
       </c>
       <c r="I18" s="48" t="n">
-        <v>6300</v>
+        <v>6.3</v>
       </c>
       <c r="J18" s="48" t="n">
-        <v>900</v>
+        <v>0.9</v>
       </c>
       <c r="K18" s="47" t="n"/>
       <c r="L18" s="49" t="n"/>
@@ -1252,19 +1252,19 @@
       </c>
       <c r="E19" s="41" t="n"/>
       <c r="F19" s="42" t="n">
-        <v>3200000</v>
+        <v>3200</v>
       </c>
       <c r="G19" s="42" t="n">
-        <v>508400</v>
+        <v>508.4</v>
       </c>
       <c r="H19" s="42" t="n">
-        <v>400000</v>
+        <v>400</v>
       </c>
       <c r="I19" s="42" t="n">
-        <v>96000</v>
+        <v>96</v>
       </c>
       <c r="J19" s="42" t="n">
-        <v>12400</v>
+        <v>12.4</v>
       </c>
       <c r="K19" s="43" t="n">
         <v>120</v>
@@ -1298,19 +1298,19 @@
       </c>
       <c r="E20" s="41" t="n"/>
       <c r="F20" s="42" t="n">
-        <v>1800000</v>
+        <v>1800</v>
       </c>
       <c r="G20" s="42" t="n">
-        <v>46100</v>
+        <v>46.1</v>
       </c>
       <c r="H20" s="42" t="n">
         <v>0</v>
       </c>
       <c r="I20" s="42" t="n">
-        <v>45000</v>
+        <v>45</v>
       </c>
       <c r="J20" s="42" t="n">
-        <v>1100</v>
+        <v>1.1</v>
       </c>
       <c r="K20" s="43" t="n">
         <v>35</v>
@@ -1334,19 +1334,19 @@
         <v>1</v>
       </c>
       <c r="F21" s="25" t="n">
-        <v>1900000</v>
+        <v>1900</v>
       </c>
       <c r="G21" s="25" t="n">
-        <v>180850</v>
+        <v>180.85</v>
       </c>
       <c r="H21" s="25" t="n">
-        <v>150000</v>
+        <v>150</v>
       </c>
       <c r="I21" s="25" t="n">
-        <v>28500</v>
+        <v>28.5</v>
       </c>
       <c r="J21" s="25" t="n">
-        <v>2350</v>
+        <v>2.35</v>
       </c>
       <c r="K21" s="26" t="n"/>
       <c r="L21" s="27" t="n"/>
@@ -1364,19 +1364,19 @@
         <v>1</v>
       </c>
       <c r="F22" s="31" t="n">
-        <v>1900000</v>
+        <v>1900</v>
       </c>
       <c r="G22" s="31" t="n">
-        <v>180850</v>
+        <v>180.85</v>
       </c>
       <c r="H22" s="31" t="n">
-        <v>150000</v>
+        <v>150</v>
       </c>
       <c r="I22" s="31" t="n">
-        <v>28500</v>
+        <v>28.5</v>
       </c>
       <c r="J22" s="31" t="n">
-        <v>2350</v>
+        <v>2.35</v>
       </c>
       <c r="K22" s="32" t="n"/>
       <c r="L22" s="33" t="n"/>
@@ -1402,19 +1402,19 @@
         <v>1</v>
       </c>
       <c r="F23" s="37" t="n">
-        <v>1900000</v>
+        <v>1900</v>
       </c>
       <c r="G23" s="37" t="n">
-        <v>180850</v>
+        <v>180.85</v>
       </c>
       <c r="H23" s="37" t="n">
-        <v>150000</v>
+        <v>150</v>
       </c>
       <c r="I23" s="37" t="n">
-        <v>28500</v>
+        <v>28.5</v>
       </c>
       <c r="J23" s="37" t="n">
-        <v>2350</v>
+        <v>2.35</v>
       </c>
       <c r="K23" s="36" t="n">
         <v>20</v>
@@ -1444,19 +1444,19 @@
       </c>
       <c r="E24" s="41" t="n"/>
       <c r="F24" s="42" t="n">
-        <v>1900000</v>
+        <v>1900</v>
       </c>
       <c r="G24" s="42" t="n">
-        <v>180850</v>
+        <v>180.85</v>
       </c>
       <c r="H24" s="42" t="n">
-        <v>150000</v>
+        <v>150</v>
       </c>
       <c r="I24" s="42" t="n">
-        <v>28500</v>
+        <v>28.5</v>
       </c>
       <c r="J24" s="42" t="n">
-        <v>2350</v>
+        <v>2.35</v>
       </c>
       <c r="K24" s="43" t="n">
         <v>20</v>
@@ -1480,19 +1480,19 @@
         <v>1</v>
       </c>
       <c r="F25" s="25" t="n">
-        <v>4872000</v>
+        <v>4872</v>
       </c>
       <c r="G25" s="25" t="n">
-        <v>1061690</v>
+        <v>1061.69</v>
       </c>
       <c r="H25" s="25" t="n">
-        <v>812000</v>
+        <v>812</v>
       </c>
       <c r="I25" s="25" t="n">
-        <v>219240</v>
+        <v>219.24</v>
       </c>
       <c r="J25" s="25" t="n">
-        <v>30450</v>
+        <v>30.45</v>
       </c>
       <c r="K25" s="26" t="n"/>
       <c r="L25" s="27" t="n"/>
@@ -1510,19 +1510,19 @@
         <v>1</v>
       </c>
       <c r="F26" s="31" t="n">
-        <v>4872000</v>
+        <v>4872</v>
       </c>
       <c r="G26" s="31" t="n">
-        <v>1061690</v>
+        <v>1061.69</v>
       </c>
       <c r="H26" s="31" t="n">
-        <v>812000</v>
+        <v>812</v>
       </c>
       <c r="I26" s="31" t="n">
-        <v>219240</v>
+        <v>219.24</v>
       </c>
       <c r="J26" s="31" t="n">
-        <v>30450</v>
+        <v>30.45</v>
       </c>
       <c r="K26" s="32" t="n"/>
       <c r="L26" s="33" t="n"/>
@@ -1548,19 +1548,19 @@
         <v>1</v>
       </c>
       <c r="F27" s="37" t="n">
-        <v>4872000</v>
+        <v>4872</v>
       </c>
       <c r="G27" s="37" t="n">
-        <v>1061690</v>
+        <v>1061.69</v>
       </c>
       <c r="H27" s="37" t="n">
-        <v>812000</v>
+        <v>812</v>
       </c>
       <c r="I27" s="37" t="n">
-        <v>219240</v>
+        <v>219.24</v>
       </c>
       <c r="J27" s="37" t="n">
-        <v>30450</v>
+        <v>30.45</v>
       </c>
       <c r="K27" s="36" t="n">
         <v>62</v>
@@ -1590,19 +1590,19 @@
       </c>
       <c r="E28" s="41" t="n"/>
       <c r="F28" s="42" t="n">
-        <v>4872000</v>
+        <v>4872</v>
       </c>
       <c r="G28" s="42" t="n">
-        <v>1061690</v>
+        <v>1061.69</v>
       </c>
       <c r="H28" s="42" t="n">
-        <v>812000</v>
+        <v>812</v>
       </c>
       <c r="I28" s="42" t="n">
-        <v>219240</v>
+        <v>219.24</v>
       </c>
       <c r="J28" s="42" t="n">
-        <v>30450</v>
+        <v>30.45</v>
       </c>
       <c r="K28" s="43" t="n">
         <v>62</v>
@@ -1616,7 +1616,7 @@
     <row r="29" ht="13" customHeight="1">
       <c r="A29" s="45" t="inlineStr">
         <is>
-          <t>в EUR (курс 101,50000)</t>
+          <t>в тыс. EUR (курс 101,50000)</t>
         </is>
       </c>
       <c r="B29" s="46" t="n"/>
@@ -1624,19 +1624,19 @@
       <c r="D29" s="46" t="n"/>
       <c r="E29" s="47" t="n"/>
       <c r="F29" s="48" t="n">
-        <v>48000</v>
+        <v>48</v>
       </c>
       <c r="G29" s="48" t="n">
-        <v>10460</v>
+        <v>10.46</v>
       </c>
       <c r="H29" s="48" t="n">
-        <v>8000</v>
+        <v>8</v>
       </c>
       <c r="I29" s="48" t="n">
-        <v>2160</v>
+        <v>2.16</v>
       </c>
       <c r="J29" s="48" t="n">
-        <v>300</v>
+        <v>0.3</v>
       </c>
       <c r="K29" s="47" t="n"/>
       <c r="L29" s="49" t="n"/>
@@ -1651,22 +1651,22 @@
       <c r="C30" s="12" t="n"/>
       <c r="D30" s="12" t="n"/>
       <c r="E30" s="13" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F30" s="14" t="n">
-        <v>18495000</v>
+        <v>18495</v>
       </c>
       <c r="G30" s="14" t="n">
-        <v>6002375</v>
+        <v>6020.775</v>
       </c>
       <c r="H30" s="14" t="n">
-        <v>4252500</v>
+        <v>4252.5</v>
       </c>
       <c r="I30" s="14" t="n">
-        <v>1369875</v>
+        <v>1369.875</v>
       </c>
       <c r="J30" s="14" t="n">
-        <v>380000</v>
+        <v>398.4</v>
       </c>
       <c r="K30" s="15" t="n"/>
       <c r="L30" s="11" t="n"/>
@@ -1684,19 +1684,19 @@
         <v>3</v>
       </c>
       <c r="F31" s="19" t="n">
-        <v>13675000</v>
+        <v>13675</v>
       </c>
       <c r="G31" s="19" t="n">
-        <v>4053375</v>
+        <v>4053.375</v>
       </c>
       <c r="H31" s="19" t="n">
-        <v>2912500</v>
+        <v>2912.5</v>
       </c>
       <c r="I31" s="19" t="n">
-        <v>884375</v>
+        <v>884.375</v>
       </c>
       <c r="J31" s="19" t="n">
-        <v>256500</v>
+        <v>256.5</v>
       </c>
       <c r="K31" s="20" t="n"/>
       <c r="L31" s="21" t="n"/>
@@ -1714,19 +1714,19 @@
         <v>1</v>
       </c>
       <c r="F32" s="25" t="n">
-        <v>7875000</v>
+        <v>7875</v>
       </c>
       <c r="G32" s="25" t="n">
-        <v>1771875</v>
+        <v>1771.875</v>
       </c>
       <c r="H32" s="25" t="n">
-        <v>1312500</v>
+        <v>1312.5</v>
       </c>
       <c r="I32" s="25" t="n">
-        <v>354375</v>
+        <v>354.375</v>
       </c>
       <c r="J32" s="25" t="n">
-        <v>105000</v>
+        <v>105</v>
       </c>
       <c r="K32" s="26" t="n"/>
       <c r="L32" s="27" t="n"/>
@@ -1744,19 +1744,19 @@
         <v>1</v>
       </c>
       <c r="F33" s="31" t="n">
-        <v>7875000</v>
+        <v>7875</v>
       </c>
       <c r="G33" s="31" t="n">
-        <v>1771875</v>
+        <v>1771.875</v>
       </c>
       <c r="H33" s="31" t="n">
-        <v>1312500</v>
+        <v>1312.5</v>
       </c>
       <c r="I33" s="31" t="n">
-        <v>354375</v>
+        <v>354.375</v>
       </c>
       <c r="J33" s="31" t="n">
-        <v>105000</v>
+        <v>105</v>
       </c>
       <c r="K33" s="32" t="n"/>
       <c r="L33" s="33" t="n"/>
@@ -1782,19 +1782,19 @@
         <v>1</v>
       </c>
       <c r="F34" s="37" t="n">
-        <v>7875000</v>
+        <v>7875</v>
       </c>
       <c r="G34" s="37" t="n">
-        <v>1771875</v>
+        <v>1771.875</v>
       </c>
       <c r="H34" s="37" t="n">
-        <v>1312500</v>
+        <v>1312.5</v>
       </c>
       <c r="I34" s="37" t="n">
-        <v>354375</v>
+        <v>354.375</v>
       </c>
       <c r="J34" s="37" t="n">
-        <v>105000</v>
+        <v>105</v>
       </c>
       <c r="K34" s="36" t="n">
         <v>245</v>
@@ -1824,19 +1824,19 @@
       </c>
       <c r="E35" s="41" t="n"/>
       <c r="F35" s="42" t="n">
-        <v>7875000</v>
+        <v>7875</v>
       </c>
       <c r="G35" s="42" t="n">
-        <v>1771875</v>
+        <v>1771.875</v>
       </c>
       <c r="H35" s="42" t="n">
-        <v>1312500</v>
+        <v>1312.5</v>
       </c>
       <c r="I35" s="42" t="n">
-        <v>354375</v>
+        <v>354.375</v>
       </c>
       <c r="J35" s="42" t="n">
-        <v>105000</v>
+        <v>105</v>
       </c>
       <c r="K35" s="43" t="n">
         <v>245</v>
@@ -1850,7 +1850,7 @@
     <row r="36" ht="13" customHeight="1">
       <c r="A36" s="45" t="inlineStr">
         <is>
-          <t>в USD (курс 87,50000)</t>
+          <t>в тыс. USD (курс 87,50000)</t>
         </is>
       </c>
       <c r="B36" s="46" t="n"/>
@@ -1858,19 +1858,19 @@
       <c r="D36" s="46" t="n"/>
       <c r="E36" s="47" t="n"/>
       <c r="F36" s="48" t="n">
-        <v>90000</v>
+        <v>90</v>
       </c>
       <c r="G36" s="48" t="n">
-        <v>20250</v>
+        <v>20.25</v>
       </c>
       <c r="H36" s="48" t="n">
-        <v>15000</v>
+        <v>15</v>
       </c>
       <c r="I36" s="48" t="n">
-        <v>4050</v>
+        <v>4.05</v>
       </c>
       <c r="J36" s="48" t="n">
-        <v>1200</v>
+        <v>1.2</v>
       </c>
       <c r="K36" s="47" t="n"/>
       <c r="L36" s="49" t="n"/>
@@ -1888,19 +1888,19 @@
         <v>1</v>
       </c>
       <c r="F37" s="25" t="n">
-        <v>2200000</v>
+        <v>2200</v>
       </c>
       <c r="G37" s="25" t="n">
-        <v>551000</v>
+        <v>551</v>
       </c>
       <c r="H37" s="25" t="n">
-        <v>400000</v>
+        <v>400</v>
       </c>
       <c r="I37" s="25" t="n">
-        <v>120000</v>
+        <v>120</v>
       </c>
       <c r="J37" s="25" t="n">
-        <v>31000</v>
+        <v>31</v>
       </c>
       <c r="K37" s="26" t="n"/>
       <c r="L37" s="27" t="n"/>
@@ -1918,19 +1918,19 @@
         <v>1</v>
       </c>
       <c r="F38" s="31" t="n">
-        <v>2200000</v>
+        <v>2200</v>
       </c>
       <c r="G38" s="31" t="n">
-        <v>551000</v>
+        <v>551</v>
       </c>
       <c r="H38" s="31" t="n">
-        <v>400000</v>
+        <v>400</v>
       </c>
       <c r="I38" s="31" t="n">
-        <v>120000</v>
+        <v>120</v>
       </c>
       <c r="J38" s="31" t="n">
-        <v>31000</v>
+        <v>31</v>
       </c>
       <c r="K38" s="32" t="n"/>
       <c r="L38" s="33" t="n"/>
@@ -1956,19 +1956,19 @@
         <v>1</v>
       </c>
       <c r="F39" s="37" t="n">
-        <v>2200000</v>
+        <v>2200</v>
       </c>
       <c r="G39" s="37" t="n">
-        <v>551000</v>
+        <v>551</v>
       </c>
       <c r="H39" s="37" t="n">
-        <v>400000</v>
+        <v>400</v>
       </c>
       <c r="I39" s="37" t="n">
-        <v>120000</v>
+        <v>120</v>
       </c>
       <c r="J39" s="37" t="n">
-        <v>31000</v>
+        <v>31</v>
       </c>
       <c r="K39" s="36" t="n">
         <v>190</v>
@@ -1998,19 +1998,19 @@
       </c>
       <c r="E40" s="41" t="n"/>
       <c r="F40" s="42" t="n">
-        <v>2200000</v>
+        <v>2200</v>
       </c>
       <c r="G40" s="42" t="n">
-        <v>551000</v>
+        <v>551</v>
       </c>
       <c r="H40" s="42" t="n">
-        <v>400000</v>
+        <v>400</v>
       </c>
       <c r="I40" s="42" t="n">
-        <v>120000</v>
+        <v>120</v>
       </c>
       <c r="J40" s="42" t="n">
-        <v>31000</v>
+        <v>31</v>
       </c>
       <c r="K40" s="43" t="n">
         <v>190</v>
@@ -2034,19 +2034,19 @@
         <v>1</v>
       </c>
       <c r="F41" s="25" t="n">
-        <v>3600000</v>
+        <v>3600</v>
       </c>
       <c r="G41" s="25" t="n">
-        <v>1730500</v>
+        <v>1730.5</v>
       </c>
       <c r="H41" s="25" t="n">
-        <v>1200000</v>
+        <v>1200</v>
       </c>
       <c r="I41" s="25" t="n">
-        <v>410000</v>
+        <v>410</v>
       </c>
       <c r="J41" s="25" t="n">
-        <v>120500</v>
+        <v>120.5</v>
       </c>
       <c r="K41" s="26" t="n"/>
       <c r="L41" s="27" t="n"/>
@@ -2064,19 +2064,19 @@
         <v>1</v>
       </c>
       <c r="F42" s="31" t="n">
-        <v>3600000</v>
+        <v>3600</v>
       </c>
       <c r="G42" s="31" t="n">
-        <v>1730500</v>
+        <v>1730.5</v>
       </c>
       <c r="H42" s="31" t="n">
-        <v>1200000</v>
+        <v>1200</v>
       </c>
       <c r="I42" s="31" t="n">
-        <v>410000</v>
+        <v>410</v>
       </c>
       <c r="J42" s="31" t="n">
-        <v>120500</v>
+        <v>120.5</v>
       </c>
       <c r="K42" s="32" t="n"/>
       <c r="L42" s="33" t="n"/>
@@ -2102,19 +2102,19 @@
         <v>1</v>
       </c>
       <c r="F43" s="37" t="n">
-        <v>3600000</v>
+        <v>3600</v>
       </c>
       <c r="G43" s="37" t="n">
-        <v>1730500</v>
+        <v>1730.5</v>
       </c>
       <c r="H43" s="37" t="n">
-        <v>1200000</v>
+        <v>1200</v>
       </c>
       <c r="I43" s="37" t="n">
-        <v>410000</v>
+        <v>410</v>
       </c>
       <c r="J43" s="37" t="n">
-        <v>120500</v>
+        <v>120.5</v>
       </c>
       <c r="K43" s="36" t="n">
         <v>212</v>
@@ -2144,19 +2144,19 @@
       </c>
       <c r="E44" s="41" t="n"/>
       <c r="F44" s="42" t="n">
-        <v>3600000</v>
+        <v>3600</v>
       </c>
       <c r="G44" s="42" t="n">
-        <v>1730500</v>
+        <v>1730.5</v>
       </c>
       <c r="H44" s="42" t="n">
-        <v>1200000</v>
+        <v>1200</v>
       </c>
       <c r="I44" s="42" t="n">
-        <v>410000</v>
+        <v>410</v>
       </c>
       <c r="J44" s="42" t="n">
-        <v>120500</v>
+        <v>120.5</v>
       </c>
       <c r="K44" s="43" t="n">
         <v>212</v>
@@ -2177,22 +2177,22 @@
       <c r="C45" s="17" t="n"/>
       <c r="D45" s="17" t="n"/>
       <c r="E45" s="18" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F45" s="19" t="n">
-        <v>4820000</v>
+        <v>4820</v>
       </c>
       <c r="G45" s="19" t="n">
-        <v>1949000</v>
+        <v>1967.4</v>
       </c>
       <c r="H45" s="19" t="n">
-        <v>1340000</v>
+        <v>1340</v>
       </c>
       <c r="I45" s="19" t="n">
-        <v>485500</v>
+        <v>485.5</v>
       </c>
       <c r="J45" s="19" t="n">
-        <v>123500</v>
+        <v>141.9</v>
       </c>
       <c r="K45" s="20" t="n"/>
       <c r="L45" s="21" t="n"/>
@@ -2200,7 +2200,7 @@
     <row r="46" ht="13" customHeight="1">
       <c r="A46" s="22" t="inlineStr">
         <is>
-          <t>Нарынская обл.</t>
+          <t>Иссык-Кульская обл.</t>
         </is>
       </c>
       <c r="B46" s="23" t="n"/>
@@ -2210,19 +2210,19 @@
         <v>1</v>
       </c>
       <c r="F46" s="25" t="n">
-        <v>2100000</v>
+        <v>0</v>
       </c>
       <c r="G46" s="25" t="n">
-        <v>1024300</v>
+        <v>18.4</v>
       </c>
       <c r="H46" s="25" t="n">
-        <v>700000</v>
+        <v>0</v>
       </c>
       <c r="I46" s="25" t="n">
-        <v>260000</v>
+        <v>0</v>
       </c>
       <c r="J46" s="25" t="n">
-        <v>64300</v>
+        <v>18.4</v>
       </c>
       <c r="K46" s="26" t="n"/>
       <c r="L46" s="27" t="n"/>
@@ -2230,7 +2230,7 @@
     <row r="47" ht="13" customHeight="1">
       <c r="A47" s="28" t="inlineStr">
         <is>
-          <t>Кочкорский р-н</t>
+          <t>Ак-Суйский р-н</t>
         </is>
       </c>
       <c r="B47" s="29" t="n"/>
@@ -2240,19 +2240,19 @@
         <v>1</v>
       </c>
       <c r="F47" s="31" t="n">
-        <v>2100000</v>
+        <v>0</v>
       </c>
       <c r="G47" s="31" t="n">
-        <v>1024300</v>
+        <v>18.4</v>
       </c>
       <c r="H47" s="31" t="n">
-        <v>700000</v>
+        <v>0</v>
       </c>
       <c r="I47" s="31" t="n">
-        <v>260000</v>
+        <v>0</v>
       </c>
       <c r="J47" s="31" t="n">
-        <v>64300</v>
+        <v>18.4</v>
       </c>
       <c r="K47" s="32" t="n"/>
       <c r="L47" s="33" t="n"/>
@@ -2260,17 +2260,17 @@
     <row r="48" ht="13" customHeight="1">
       <c r="A48" s="34" t="inlineStr">
         <is>
-          <t>ОсОО «Нарын-Агро»</t>
+          <t>КФХ «Ак-Суу»</t>
         </is>
       </c>
       <c r="B48" s="35" t="inlineStr">
         <is>
-          <t>высокий</t>
+          <t>средний</t>
         </is>
       </c>
       <c r="C48" s="35" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="D48" s="35" t="n"/>
@@ -2278,39 +2278,39 @@
         <v>1</v>
       </c>
       <c r="F48" s="37" t="n">
-        <v>2100000</v>
+        <v>0</v>
       </c>
       <c r="G48" s="37" t="n">
-        <v>1024300</v>
+        <v>18.4</v>
       </c>
       <c r="H48" s="37" t="n">
-        <v>700000</v>
+        <v>0</v>
       </c>
       <c r="I48" s="37" t="n">
-        <v>260000</v>
+        <v>0</v>
       </c>
       <c r="J48" s="37" t="n">
-        <v>64300</v>
+        <v>18.4</v>
       </c>
       <c r="K48" s="36" t="n">
-        <v>409</v>
+        <v>31</v>
       </c>
       <c r="L48" s="38" t="n"/>
     </row>
-    <row r="49" ht="24" customHeight="1">
+    <row r="49" ht="13" customHeight="1">
       <c r="A49" s="39" t="inlineStr">
         <is>
-          <t>№ 21-2/077 от 18.05.2021</t>
+          <t>№ 20-6/027 от 12.05.2020</t>
         </is>
       </c>
       <c r="B49" s="40" t="inlineStr">
         <is>
-          <t>высокий</t>
+          <t>средний</t>
         </is>
       </c>
       <c r="C49" s="40" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="D49" s="40" t="inlineStr">
@@ -2320,55 +2320,55 @@
       </c>
       <c r="E49" s="41" t="n"/>
       <c r="F49" s="42" t="n">
-        <v>2100000</v>
+        <v>0</v>
       </c>
       <c r="G49" s="42" t="n">
-        <v>1024300</v>
+        <v>18.4</v>
       </c>
       <c r="H49" s="42" t="n">
-        <v>700000</v>
+        <v>0</v>
       </c>
       <c r="I49" s="42" t="n">
-        <v>260000</v>
+        <v>0</v>
       </c>
       <c r="J49" s="42" t="n">
-        <v>64300</v>
+        <v>18.4</v>
       </c>
       <c r="K49" s="43" t="n">
-        <v>409</v>
+        <v>31</v>
       </c>
       <c r="L49" s="44" t="inlineStr">
         <is>
-          <t>Соглашение о добровольном исполнении № 3, 10.09.2026</t>
+          <t>Первичная претензия, 21.08.2026</t>
         </is>
       </c>
     </row>
     <row r="50" ht="13" customHeight="1">
       <c r="A50" s="22" t="inlineStr">
         <is>
-          <t>Таласская обл.</t>
+          <t>Нарынская обл.</t>
         </is>
       </c>
       <c r="B50" s="23" t="n"/>
       <c r="C50" s="23" t="n"/>
       <c r="D50" s="23" t="n"/>
       <c r="E50" s="24" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F50" s="25" t="n">
-        <v>2720000</v>
+        <v>2100</v>
       </c>
       <c r="G50" s="25" t="n">
-        <v>924700</v>
+        <v>1024.3</v>
       </c>
       <c r="H50" s="25" t="n">
-        <v>640000</v>
+        <v>700</v>
       </c>
       <c r="I50" s="25" t="n">
-        <v>225500</v>
+        <v>260</v>
       </c>
       <c r="J50" s="25" t="n">
-        <v>59200</v>
+        <v>64.3</v>
       </c>
       <c r="K50" s="26" t="n"/>
       <c r="L50" s="27" t="n"/>
@@ -2376,7 +2376,7 @@
     <row r="51" ht="13" customHeight="1">
       <c r="A51" s="28" t="inlineStr">
         <is>
-          <t>Бакай-Атинский р-н</t>
+          <t>Кочкорский р-н</t>
         </is>
       </c>
       <c r="B51" s="29" t="n"/>
@@ -2386,19 +2386,19 @@
         <v>1</v>
       </c>
       <c r="F51" s="31" t="n">
-        <v>420000</v>
+        <v>2100</v>
       </c>
       <c r="G51" s="31" t="n">
-        <v>51700</v>
+        <v>1024.3</v>
       </c>
       <c r="H51" s="31" t="n">
-        <v>40000</v>
+        <v>700</v>
       </c>
       <c r="I51" s="31" t="n">
-        <v>10500</v>
+        <v>260</v>
       </c>
       <c r="J51" s="31" t="n">
-        <v>1200</v>
+        <v>64.3</v>
       </c>
       <c r="K51" s="32" t="n"/>
       <c r="L51" s="33" t="n"/>
@@ -2406,17 +2406,17 @@
     <row r="52" ht="13" customHeight="1">
       <c r="A52" s="34" t="inlineStr">
         <is>
-          <t>Иманалиев Бакыт Тологонович</t>
+          <t>ОсОО «Нарын-Агро»</t>
         </is>
       </c>
       <c r="B52" s="35" t="inlineStr">
         <is>
-          <t>средний</t>
+          <t>высокий</t>
         </is>
       </c>
       <c r="C52" s="35" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="D52" s="35" t="n"/>
@@ -2424,39 +2424,39 @@
         <v>1</v>
       </c>
       <c r="F52" s="37" t="n">
-        <v>420000</v>
+        <v>2100</v>
       </c>
       <c r="G52" s="37" t="n">
-        <v>51700</v>
+        <v>1024.3</v>
       </c>
       <c r="H52" s="37" t="n">
-        <v>40000</v>
+        <v>700</v>
       </c>
       <c r="I52" s="37" t="n">
-        <v>10500</v>
+        <v>260</v>
       </c>
       <c r="J52" s="37" t="n">
-        <v>1200</v>
+        <v>64.3</v>
       </c>
       <c r="K52" s="36" t="n">
-        <v>95</v>
+        <v>409</v>
       </c>
       <c r="L52" s="38" t="n"/>
     </row>
     <row r="53" ht="24" customHeight="1">
       <c r="A53" s="39" t="inlineStr">
         <is>
-          <t>№ 24-2/077 от 14.05.2024</t>
+          <t>№ 21-2/077 от 18.05.2021</t>
         </is>
       </c>
       <c r="B53" s="40" t="inlineStr">
         <is>
-          <t>средний</t>
+          <t>высокий</t>
         </is>
       </c>
       <c r="C53" s="40" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="D53" s="40" t="inlineStr">
@@ -2466,140 +2466,286 @@
       </c>
       <c r="E53" s="41" t="n"/>
       <c r="F53" s="42" t="n">
-        <v>420000</v>
+        <v>2100</v>
       </c>
       <c r="G53" s="42" t="n">
-        <v>51700</v>
+        <v>1024.3</v>
       </c>
       <c r="H53" s="42" t="n">
-        <v>40000</v>
+        <v>700</v>
       </c>
       <c r="I53" s="42" t="n">
-        <v>10500</v>
+        <v>260</v>
       </c>
       <c r="J53" s="42" t="n">
-        <v>1200</v>
+        <v>64.3</v>
       </c>
       <c r="K53" s="43" t="n">
+        <v>409</v>
+      </c>
+      <c r="L53" s="44" t="inlineStr">
+        <is>
+          <t>Соглашение о добровольном исполнении № 3, 10.09.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="13" customHeight="1">
+      <c r="A54" s="22" t="inlineStr">
+        <is>
+          <t>Таласская обл.</t>
+        </is>
+      </c>
+      <c r="B54" s="23" t="n"/>
+      <c r="C54" s="23" t="n"/>
+      <c r="D54" s="23" t="n"/>
+      <c r="E54" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="F54" s="25" t="n">
+        <v>2720</v>
+      </c>
+      <c r="G54" s="25" t="n">
+        <v>924.7</v>
+      </c>
+      <c r="H54" s="25" t="n">
+        <v>640</v>
+      </c>
+      <c r="I54" s="25" t="n">
+        <v>225.5</v>
+      </c>
+      <c r="J54" s="25" t="n">
+        <v>59.2</v>
+      </c>
+      <c r="K54" s="26" t="n"/>
+      <c r="L54" s="27" t="n"/>
+    </row>
+    <row r="55" ht="13" customHeight="1">
+      <c r="A55" s="28" t="inlineStr">
+        <is>
+          <t>Бакай-Атинский р-н</t>
+        </is>
+      </c>
+      <c r="B55" s="29" t="n"/>
+      <c r="C55" s="29" t="n"/>
+      <c r="D55" s="29" t="n"/>
+      <c r="E55" s="30" t="n">
+        <v>1</v>
+      </c>
+      <c r="F55" s="31" t="n">
+        <v>420</v>
+      </c>
+      <c r="G55" s="31" t="n">
+        <v>51.7</v>
+      </c>
+      <c r="H55" s="31" t="n">
+        <v>40</v>
+      </c>
+      <c r="I55" s="31" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="J55" s="31" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="K55" s="32" t="n"/>
+      <c r="L55" s="33" t="n"/>
+    </row>
+    <row r="56" ht="13" customHeight="1">
+      <c r="A56" s="34" t="inlineStr">
+        <is>
+          <t>Иманалиев Бакыт Тологонович</t>
+        </is>
+      </c>
+      <c r="B56" s="35" t="inlineStr">
+        <is>
+          <t>средний</t>
+        </is>
+      </c>
+      <c r="C56" s="35" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
+      <c r="D56" s="35" t="n"/>
+      <c r="E56" s="36" t="n">
+        <v>1</v>
+      </c>
+      <c r="F56" s="37" t="n">
+        <v>420</v>
+      </c>
+      <c r="G56" s="37" t="n">
+        <v>51.7</v>
+      </c>
+      <c r="H56" s="37" t="n">
+        <v>40</v>
+      </c>
+      <c r="I56" s="37" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="J56" s="37" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="K56" s="36" t="n">
         <v>95</v>
       </c>
-      <c r="L53" s="44" t="inlineStr">
+      <c r="L56" s="38" t="n"/>
+    </row>
+    <row r="57" ht="24" customHeight="1">
+      <c r="A57" s="39" t="inlineStr">
+        <is>
+          <t>№ 24-2/077 от 14.05.2024</t>
+        </is>
+      </c>
+      <c r="B57" s="40" t="inlineStr">
+        <is>
+          <t>средний</t>
+        </is>
+      </c>
+      <c r="C57" s="40" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
+      <c r="D57" s="40" t="inlineStr">
+        <is>
+          <t>KGS</t>
+        </is>
+      </c>
+      <c r="E57" s="41" t="n"/>
+      <c r="F57" s="42" t="n">
+        <v>420</v>
+      </c>
+      <c r="G57" s="42" t="n">
+        <v>51.7</v>
+      </c>
+      <c r="H57" s="42" t="n">
+        <v>40</v>
+      </c>
+      <c r="I57" s="42" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="J57" s="42" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="K57" s="43" t="n">
+        <v>95</v>
+      </c>
+      <c r="L57" s="44" t="inlineStr">
         <is>
           <t>Запросы нотариату, ЦОН и органу регистрации, 24.08.2026</t>
         </is>
       </c>
     </row>
-    <row r="54" ht="13" customHeight="1">
-      <c r="A54" s="28" t="inlineStr">
+    <row r="58" ht="13" customHeight="1">
+      <c r="A58" s="28" t="inlineStr">
         <is>
           <t>Таласский р-н</t>
         </is>
       </c>
-      <c r="B54" s="29" t="n"/>
-      <c r="C54" s="29" t="n"/>
-      <c r="D54" s="29" t="n"/>
-      <c r="E54" s="30" t="n">
+      <c r="B58" s="29" t="n"/>
+      <c r="C58" s="29" t="n"/>
+      <c r="D58" s="29" t="n"/>
+      <c r="E58" s="30" t="n">
         <v>1</v>
       </c>
-      <c r="F54" s="31" t="n">
-        <v>2300000</v>
-      </c>
-      <c r="G54" s="31" t="n">
-        <v>873000</v>
-      </c>
-      <c r="H54" s="31" t="n">
-        <v>600000</v>
-      </c>
-      <c r="I54" s="31" t="n">
-        <v>215000</v>
-      </c>
-      <c r="J54" s="31" t="n">
-        <v>58000</v>
-      </c>
-      <c r="K54" s="32" t="n"/>
-      <c r="L54" s="33" t="n"/>
-    </row>
-    <row r="55" ht="13" customHeight="1">
-      <c r="A55" s="34" t="inlineStr">
+      <c r="F58" s="31" t="n">
+        <v>2300</v>
+      </c>
+      <c r="G58" s="31" t="n">
+        <v>873</v>
+      </c>
+      <c r="H58" s="31" t="n">
+        <v>600</v>
+      </c>
+      <c r="I58" s="31" t="n">
+        <v>215</v>
+      </c>
+      <c r="J58" s="31" t="n">
+        <v>58</v>
+      </c>
+      <c r="K58" s="32" t="n"/>
+      <c r="L58" s="33" t="n"/>
+    </row>
+    <row r="59" ht="13" customHeight="1">
+      <c r="A59" s="34" t="inlineStr">
         <is>
           <t>ОсОО «Талас-Бал»</t>
         </is>
       </c>
-      <c r="B55" s="35" t="inlineStr">
+      <c r="B59" s="35" t="inlineStr">
         <is>
           <t>высокий</t>
         </is>
       </c>
-      <c r="C55" s="35" t="inlineStr">
+      <c r="C59" s="35" t="inlineStr">
         <is>
           <t>2.3</t>
         </is>
       </c>
-      <c r="D55" s="35" t="n"/>
-      <c r="E55" s="36" t="n">
+      <c r="D59" s="35" t="n"/>
+      <c r="E59" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="F55" s="37" t="n">
-        <v>2300000</v>
-      </c>
-      <c r="G55" s="37" t="n">
-        <v>873000</v>
-      </c>
-      <c r="H55" s="37" t="n">
-        <v>600000</v>
-      </c>
-      <c r="I55" s="37" t="n">
-        <v>215000</v>
-      </c>
-      <c r="J55" s="37" t="n">
-        <v>58000</v>
-      </c>
-      <c r="K55" s="36" t="n">
+      <c r="F59" s="37" t="n">
+        <v>2300</v>
+      </c>
+      <c r="G59" s="37" t="n">
+        <v>873</v>
+      </c>
+      <c r="H59" s="37" t="n">
+        <v>600</v>
+      </c>
+      <c r="I59" s="37" t="n">
+        <v>215</v>
+      </c>
+      <c r="J59" s="37" t="n">
+        <v>58</v>
+      </c>
+      <c r="K59" s="36" t="n">
         <v>260</v>
       </c>
-      <c r="L55" s="38" t="n"/>
-    </row>
-    <row r="56" ht="35" customHeight="1">
-      <c r="A56" s="39" t="inlineStr">
+      <c r="L59" s="38" t="n"/>
+    </row>
+    <row r="60" ht="35" customHeight="1">
+      <c r="A60" s="39" t="inlineStr">
         <is>
           <t>№ 23-4/021 от 21.08.2023</t>
         </is>
       </c>
-      <c r="B56" s="40" t="inlineStr">
+      <c r="B60" s="40" t="inlineStr">
         <is>
           <t>высокий</t>
         </is>
       </c>
-      <c r="C56" s="40" t="inlineStr">
+      <c r="C60" s="40" t="inlineStr">
         <is>
           <t>2.3</t>
         </is>
       </c>
-      <c r="D56" s="40" t="inlineStr">
+      <c r="D60" s="40" t="inlineStr">
         <is>
           <t>KGS</t>
         </is>
       </c>
-      <c r="E56" s="41" t="n"/>
-      <c r="F56" s="42" t="n">
-        <v>2300000</v>
-      </c>
-      <c r="G56" s="42" t="n">
-        <v>873000</v>
-      </c>
-      <c r="H56" s="42" t="n">
-        <v>600000</v>
-      </c>
-      <c r="I56" s="42" t="n">
-        <v>215000</v>
-      </c>
-      <c r="J56" s="42" t="n">
-        <v>58000</v>
-      </c>
-      <c r="K56" s="43" t="n">
+      <c r="E60" s="41" t="n"/>
+      <c r="F60" s="42" t="n">
+        <v>2300</v>
+      </c>
+      <c r="G60" s="42" t="n">
+        <v>873</v>
+      </c>
+      <c r="H60" s="42" t="n">
+        <v>600</v>
+      </c>
+      <c r="I60" s="42" t="n">
+        <v>215</v>
+      </c>
+      <c r="J60" s="42" t="n">
+        <v>58</v>
+      </c>
+      <c r="K60" s="43" t="n">
         <v>260</v>
       </c>
-      <c r="L56" s="44" t="inlineStr">
+      <c r="L60" s="44" t="inlineStr">
         <is>
           <t>Уведомление о намерении инициировать банкротство, 15.06.2026</t>
         </is>
@@ -2745,7 +2891,7 @@
       </c>
       <c r="B10" s="52" t="inlineStr">
         <is>
-          <t>сом</t>
+          <t>тыс. сом</t>
         </is>
       </c>
     </row>
@@ -2817,7 +2963,7 @@
       </c>
       <c r="B16" s="52" t="inlineStr">
         <is>
-          <t>В ячейках — точные суммы, на экране и в печати — до копеек. Итоги считаются по точным суммам, поэтому сумма округлённых строк может отличаться от итога на копейки.</t>
+          <t>В ячейках — точные суммы, на экране и в печати — тыс. сом с двумя знаками. Итоги считаются по точным суммам, поэтому сумма округлённых строк может отличаться от итога на 0,01.</t>
         </is>
       </c>
     </row>
@@ -2833,7 +2979,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:C47"/>
+  <dimension ref="A1:C48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -2982,7 +3128,7 @@
 • Область — все
 • Категория риска — все (низкий, средний, высокий)
 • Просрочка от, дней — 1; 0 — все кредиты с остатком
-• Единица — сом (можно выбрать «тыс. сом»)
+• Единица — тыс. сом (можно выбрать «сом»)
 • Разрезы — департамент → отдел → область → район → заёмщик; можно выбрать другие и их порядок</t>
         </is>
       </c>
@@ -2995,7 +3141,7 @@
       </c>
       <c r="B14" s="55" t="inlineStr">
         <is>
-          <t>Строка детали — кредит: договор, признаки, суммы, дни просрочки, стадия взыскания. Над кредитами разрезы, по умолчанию департамент → отдел → область → район → заёмщик; область и район — кредита на дату состояния; у городов республиканского значения показываются обе строки — области и района; подразделение — то, за которым кредит закреплён на дату состояния. Первая строка — ИТОГО; строка разреза несёт его итог (число кредитов и суммы) и стоит над его строками; строка заёмщика есть всегда, даже при одном кредите. Признак, выбранный разрезом, колонкой не повторяется. Порядок: департаменты и отделы — по оргструктуре; области — по справочнику (области по алфавиту, затем г. Бишкек, г. Ош); районы — по алфавиту; заёмщики — по убыванию наибольших дней просрочки, при равных — по алфавиту; кредиты заёмщика — по убыванию дней. В отчёт попадают кредиты с просрочкой не меньше заданного числа дней на дату состояния. Кредит в иностранной валюте: суммы в сомах по курсу на дату, под ним курсивом строка «в &lt;валюта&gt; (курс …)» с теми же суммами в валюте договора; в итоги она не входит.</t>
+          <t>Строка детали — кредит: договор, признаки, суммы, дни просрочки, стадия взыскания. Над кредитами разрезы, по умолчанию департамент → отдел → область → район → заёмщик; область и район — кредита на дату состояния; у городов республиканского значения показываются обе строки — области и района; подразделение — то, за которым кредит закреплён на дату состояния. Первая строка — ИТОГО; строка разреза несёт его итог (число кредитов и суммы) и стоит над его строками; строка заёмщика есть всегда, даже при одном кредите. Признак, выбранный разрезом, колонкой не повторяется. Порядок: департаменты и отделы — по оргструктуре; области — по справочнику (области по алфавиту, затем г. Бишкек, г. Ош); районы — по алфавиту; заёмщики — по убыванию наибольших дней просрочки, при равных — по алфавиту; кредиты заёмщика — по убыванию дней. В отчёт попадают кредиты с просрочкой не меньше заданного числа дней на дату состояния. Суммы — в тыс. сом. Кредит в иностранной валюте: суммы в сомах по курсу на дату, под ним курсивом строка «в тыс. &lt;валюта&gt; (курс …)» с теми же суммами в тысячах единиц валюты договора; в итоги она не входит.</t>
         </is>
       </c>
     </row>
@@ -3254,7 +3400,7 @@
       </c>
       <c r="B36" s="55" t="inlineStr">
         <is>
-          <t>ИТОГО: «Просроченная задолженность» = 10 328 815,00 сом по 12 кредитам (КЗ-02, 03, 04, 05, 09, 10, 19, 22, 23 и три кредита КЗ-21); «Остаток основного долга» = 41 417 000,00 сом.</t>
+          <t>ИТОГО: «Просроченная задолженность» = 10 347,215 тыс. сом по 13 кредитам (КЗ-02, 03, 04, 05, 09, 10, 19, 22, 23, 24 и три кредита КЗ-21); «Остаток основного долга» = 41 417,000 тыс. сом.</t>
         </is>
       </c>
     </row>
@@ -3266,7 +3412,7 @@
       </c>
       <c r="B37" s="55" t="inlineStr">
         <is>
-          <t>Строка разреза = сумма строк на уровень ниже по каждой суммовой колонке (заёмщик — его кредитов, район — его заёмщиков и т. д.), ИТОГО — сумма департаментов; «Кредитов с просрочкой» = число кредитов разреза, в ИТОГО — 12.</t>
+          <t>Строка разреза = сумма строк на уровень ниже по каждой суммовой колонке (заёмщик — его кредитов, район — его заёмщиков и т. д.), ИТОГО — сумма департаментов; «Кредитов с просрочкой» = число кредитов разреза, в ИТОГО — 13.</t>
         </is>
       </c>
     </row>
@@ -3290,7 +3436,7 @@
       </c>
       <c r="B39" s="55" t="inlineStr">
         <is>
-          <t>Валютный кредит — в сомах по курсу на 30.09.2026 (USD 87,50000, EUR 101,50000); под ним курсивом строка «в USD (курс 87,50000)» или «в EUR (курс 101,50000)» с суммами в валюте договора, в итоги она не входит. КЗ-23: остаток 90 000,00 USD = 7 875 000,00 сом, просрочка 20 250,00 USD = 1 771 875,00 сом; КЗ-22: остаток 48 000,00 EUR = 4 872 000,00 сом, просрочка 10 460,00 EUR = 1 061 690,00 сом.</t>
+          <t>Валютный кредит — в сомах по курсу на 30.09.2026 (USD 87,50000, EUR 101,50000); под ним курсивом строка «в тыс. USD (курс 87,50000)» или «в тыс. EUR (курс 101,50000)» с суммами в валюте договора, в итоги она не входит. КЗ-23: остаток 90,000 тыс. USD = 7 875,000 тыс. сом, просрочка 20,250 тыс. USD = 1 771,875 тыс. сом; КЗ-22: остаток 48,000 тыс. EUR = 4 872,000 тыс. сом, просрочка 10,460 тыс. EUR = 1 061,690 тыс. сом.</t>
         </is>
       </c>
     </row>
@@ -3302,11 +3448,11 @@
       </c>
       <c r="B40" s="55" t="inlineStr">
         <is>
-          <t>Заёмщик с несколькими кредитами — КЗ-21 (USD и два в сомах): строка заёмщика — 3 кредита, остаток 15 500 000,00, просрочка 2 934 500,00 сом (валютный кредит — в сомах), категория — худшая (высокий), дни — наибольшие (190); кредиты под ним по убыванию дней — 190, 120, 35. У № 24-3/105 просрочены только проценты и штрафы, просроченная основная сумма — 0,00.</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="30" customHeight="1">
+          <t>Заёмщик с несколькими кредитами — КЗ-21 (USD и два в сомах): строка заёмщика — 3 кредита, остаток 15 500,000, просрочка 2 934,500 тыс. сом (валютный кредит — в сомах), категория — худшая (высокий), дни — наибольшие (190); кредиты под ним по убыванию дней — 190, 120, 35. У № 24-3/105 просрочены только проценты и штрафы, просроченная основная сумма — 0,00.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="45" customHeight="1">
       <c r="A41" s="54" t="inlineStr">
         <is>
           <t>6.</t>
@@ -3314,7 +3460,7 @@
       </c>
       <c r="B41" s="55" t="inlineStr">
         <is>
-          <t>Дни просрочки на 01.10.2026: КЗ-02 — 20, КЗ-03 — 75, КЗ-09 — 95, КЗ-19 — 190, КЗ-04 — 212, КЗ-10 — 260, КЗ-05 — 409 (считается от 18.08.2025); КЗ-21 — 190, 120, 35; КЗ-22 — 62; КЗ-23 — 245.</t>
+          <t>Дни просрочки на 01.10.2026: КЗ-02 — 20, КЗ-03 — 75, КЗ-09 — 95, КЗ-19 — 190, КЗ-04 — 212, КЗ-10 — 260, КЗ-05 — 409 (считается от 18.08.2025); КЗ-21 — 190, 120, 35; КЗ-22 — 62; КЗ-23 — 245; КЗ-24 — 31.</t>
         </is>
       </c>
     </row>
@@ -3326,7 +3472,7 @@
       </c>
       <c r="B42" s="55" t="inlineStr">
         <is>
-          <t>Категория риска: средний — КЗ-02, 03, 09, 22, КЗ-21 № 22-3/014 и № 24-3/105; высокий — КЗ-04, 05, 10, 19, 23, КЗ-21 № 19-3/061 (Порядок №41 п. 11: 1–180 дней — средний, более 180 — высокий).</t>
+          <t>Категория риска: средний — КЗ-02, 03, 09, 22, 24, КЗ-21 № 22-3/014 и № 24-3/105; высокий — КЗ-04, 05, 10, 19, 23, КЗ-21 № 19-3/061 (Порядок №41 п. 11: 1–180 дней — средний, более 180 — высокий).</t>
         </is>
       </c>
     </row>
@@ -3386,12 +3532,24 @@
       </c>
       <c r="B47" s="55" t="inlineStr">
         <is>
+          <t>КЗ-24: основная сумма и проценты погашены, просрочены только штрафы 18,400 тыс. сом — кредит в отчёте есть, остаток основного долга 0,00, дни просрочки 31.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="30" customHeight="1">
+      <c r="A48" s="54" t="inlineStr">
+        <is>
+          <t>13.</t>
+        </is>
+      </c>
+      <c r="B48" s="55" t="inlineStr">
+        <is>
           <t>Отбор «Отдел развития регионов», категория «средний» на 01.10.2026: только ИТОГО с нулями и под таблицей «Кредитов с просрочкой от 1 дня на 01.10.2026 нет.»</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="28">
+  <mergeCells count="29">
     <mergeCell ref="B47:C47"/>
     <mergeCell ref="B16:C16"/>
     <mergeCell ref="B7:C7"/>
@@ -3401,6 +3559,7 @@
     <mergeCell ref="B43:C43"/>
     <mergeCell ref="B12:C12"/>
     <mergeCell ref="B39:C39"/>
+    <mergeCell ref="B48:C48"/>
     <mergeCell ref="B11:C11"/>
     <mergeCell ref="B42:C42"/>
     <mergeCell ref="B14:C14"/>

--- a/docs/perechen-otchetov/obrazcy/ФО-01.xlsx
+++ b/docs/perechen-otchetov/obrazcy/ФО-01.xlsx
@@ -1081,7 +1081,7 @@
       </c>
       <c r="L14" s="44" t="inlineStr">
         <is>
-          <t>Повторная претензия, 15.09.2026</t>
+          <t>Повторная претензия, 24.08.2026</t>
         </is>
       </c>
     </row>
@@ -1463,7 +1463,7 @@
       </c>
       <c r="L24" s="44" t="inlineStr">
         <is>
-          <t>Первичная претензия, 25.09.2026</t>
+          <t>Первичная претензия, 24.09.2026</t>
         </is>
       </c>
     </row>
@@ -1774,7 +1774,7 @@
       </c>
       <c r="C34" s="35" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="D34" s="35" t="n"/>
@@ -1801,7 +1801,7 @@
       </c>
       <c r="L34" s="38" t="n"/>
     </row>
-    <row r="35" ht="24" customHeight="1">
+    <row r="35" ht="35" customHeight="1">
       <c r="A35" s="39" t="inlineStr">
         <is>
           <t>№ 20-5/118 от 23.06.2020</t>
@@ -1814,7 +1814,7 @@
       </c>
       <c r="C35" s="40" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="D35" s="40" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="L35" s="44" t="inlineStr">
         <is>
-          <t>Исковое заявление в суд, 03.09.2026</t>
+          <t>Определение о принятии искового заявления к производству, 10.09.2026</t>
         </is>
       </c>
     </row>
@@ -2416,7 +2416,7 @@
       </c>
       <c r="C52" s="35" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>2.2</t>
         </is>
       </c>
       <c r="D52" s="35" t="n"/>
@@ -2456,7 +2456,7 @@
       </c>
       <c r="C53" s="40" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>2.2</t>
         </is>
       </c>
       <c r="D53" s="40" t="inlineStr">
@@ -2979,7 +2979,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:C48"/>
+  <dimension ref="A1:C49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -3476,7 +3476,7 @@
         </is>
       </c>
     </row>
-    <row r="43" ht="15" customHeight="1">
+    <row r="43" ht="45" customHeight="1">
       <c r="A43" s="54" t="inlineStr">
         <is>
           <t>8.</t>
@@ -3484,11 +3484,11 @@
       </c>
       <c r="B43" s="55" t="inlineStr">
         <is>
-          <t>Группа = группе заёмщика в контрольном наборе.</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="30" customHeight="1">
+          <t>Группа = группе заёмщика в контрольном наборе на 30.09.2026 (= ФО-28, ФО-57): КЗ-05 — 2.2 (исполнительный лист на исполнении с 17.07.2026), КЗ-23 — 2.1 (иск 03.09.2026), КЗ-21 — 2.1 (с 21.09.2026), КЗ-02 — 1.2 (с 12.09.2026).</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="105" customHeight="1">
       <c r="A44" s="54" t="inlineStr">
         <is>
           <t>9.</t>
@@ -3496,11 +3496,11 @@
       </c>
       <c r="B44" s="55" t="inlineStr">
         <is>
-          <t>Стадия взыскания: КЗ-05 — «Соглашение о добровольном исполнении № 3, 10.09.2026»; КЗ-19 — «мер нет».</t>
-        </is>
-      </c>
-    </row>
-    <row r="45" ht="15" customHeight="1">
+          <t>Стадия взыскания = последняя мера журнала взыскания по кредиту на 30.09.2026, дата — как в ФО-17 (наш документ — по дате документа, входящий акт — по дате факта): КЗ-02 — «Первичная претензия, 24.09.2026» (дата претензии, не вручения 25.09.2026); КЗ-03 — «Повторная претензия, 24.08.2026» (решение комитета о безакцептном списании, протокол № 11 от 17.09.2026, — не мера; платёжное требование в банк от 01.10.2026 — после даты данных); КЗ-05 — «Соглашение о добровольном исполнении № 3, 10.09.2026»; КЗ-23 — «Определение о принятии искового заявления к производству, 10.09.2026» (заседания 17.09 и 29.09.2026 — не меры); КЗ-19 — «мер нет».</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="75" customHeight="1">
       <c r="A45" s="54" t="inlineStr">
         <is>
           <t>10.</t>
@@ -3508,7 +3508,7 @@
       </c>
       <c r="B45" s="55" t="inlineStr">
         <is>
-          <t>КЗ-01 (платит по графику) и КЗ-15 (кредит погашен) в отчёте на 01.10.2026 не показаны.</t>
+          <t>В отчёте на 01.10.2026 не показаны: КЗ-01, КЗ-25 (платят по графику; начисленные проценты КЗ-25 121,60 EUR срока уплаты не достигли), КЗ-15 (погашен 18.09.2026), КЗ-08 (списан 17.09.2026; на 31.08.2026 просрочено 599,269 тыс. сом — в отчёте на 01.09.2026), КЗ-16 (погашен имуществом; просрочка покупателя по договору купли-продажи — не кредит, ФО-47), КЗ-17 и КЗ-26 (новые кредиты без просрочки; у КЗ-26 освоения нет, задолженности нет), КЗ-18 (расторгнут без выдачи).</t>
         </is>
       </c>
     </row>
@@ -3548,8 +3548,20 @@
         </is>
       </c>
     </row>
+    <row r="49" ht="45" customHeight="1">
+      <c r="A49" s="54" t="inlineStr">
+        <is>
+          <t>14.</t>
+        </is>
+      </c>
+      <c r="B49" s="55" t="inlineStr">
+        <is>
+          <t>Сверка с соседними отчётами на 01.10.2026: «Просроченная задолженность» ИТОГО = ФО-02, ФО-27, ФО-57 (10 347,215 тыс. сом); остаток основного долга кредитов с просрочкой 41 417,000 + КЗ-06 1 800,000 (группа 1.2 без просрочки) = остаток проблемных ФО-28 43 217,000.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="29">
+  <mergeCells count="30">
     <mergeCell ref="B47:C47"/>
     <mergeCell ref="B16:C16"/>
     <mergeCell ref="B7:C7"/>
@@ -3572,6 +3584,7 @@
     <mergeCell ref="B10:C10"/>
     <mergeCell ref="B40:C40"/>
     <mergeCell ref="B9:C9"/>
+    <mergeCell ref="B49:C49"/>
     <mergeCell ref="B6:C6"/>
     <mergeCell ref="B15:C15"/>
     <mergeCell ref="B5:C5"/>
